--- a/internal/migration/Defab Thrippunithura/Dupatta.xlsx
+++ b/internal/migration/Defab Thrippunithura/Dupatta.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28827"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="6" rupBuild="4505"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Stok Report 2025-2026\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA98B8D4-4EA8-401D-87C5-FEC48FF23126}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="90" yWindow="0" windowWidth="28530" windowHeight="15465" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -18,9 +12,9 @@
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
     <sheet name="Sheet4" sheetId="4" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="162913"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+  <calcPr calcId="124519"/>
+  <extLst xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main">
+    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
   </extLst>
@@ -28,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="361" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="377" uniqueCount="86">
   <si>
     <t>Sl.No</t>
   </si>
@@ -275,12 +269,24 @@
   <si>
     <t>kt chk zri</t>
   </si>
+  <si>
+    <t>NEW MRP EXCLUDING GST</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TAXABLE </t>
+  </si>
+  <si>
+    <t>TAX</t>
+  </si>
+  <si>
+    <t>MRP</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -309,8 +315,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -371,7 +378,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Calibri Light"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -406,7 +413,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -583,24 +590,26 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E110"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:J110"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="7.28515625" customWidth="1"/>
     <col min="2" max="2" width="19.28515625" customWidth="1"/>
     <col min="3" max="3" width="11.5703125" customWidth="1"/>
     <col min="4" max="4" width="10.85546875" customWidth="1"/>
+    <col min="6" max="6" width="28.28515625" customWidth="1"/>
+    <col min="10" max="10" width="5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -616,8 +625,20 @@
       <c r="E1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F1" t="s">
+        <v>82</v>
+      </c>
+      <c r="H1" t="s">
+        <v>83</v>
+      </c>
+      <c r="I1" t="s">
+        <v>84</v>
+      </c>
+      <c r="J1" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10">
       <c r="B2" t="s">
         <v>5</v>
       </c>
@@ -627,8 +648,24 @@
       <c r="D2">
         <v>265</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F2">
+        <f>ROUND(IF(D2&gt;2500, D2/1.18, D2/1.05),2)</f>
+        <v>252.38</v>
+      </c>
+      <c r="H2">
+        <f t="shared" ref="H2:H65" si="0">D2/1.05</f>
+        <v>252.38095238095238</v>
+      </c>
+      <c r="I2">
+        <f t="shared" ref="I2:I65" si="1">D2-F2</f>
+        <v>12.620000000000005</v>
+      </c>
+      <c r="J2" s="1">
+        <f t="shared" ref="J2:J65" si="2">SUM(H2:I2)</f>
+        <v>265.00095238095241</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
       <c r="B3" t="s">
         <v>5</v>
       </c>
@@ -641,8 +678,24 @@
       <c r="E3">
         <v>13</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F3">
+        <f t="shared" ref="F3:F66" si="3">ROUND(IF(D3&gt;2500, D3/1.18, D3/1.05),2)</f>
+        <v>261.89999999999998</v>
+      </c>
+      <c r="H3">
+        <f t="shared" si="0"/>
+        <v>261.90476190476187</v>
+      </c>
+      <c r="I3">
+        <f t="shared" si="1"/>
+        <v>13.100000000000023</v>
+      </c>
+      <c r="J3" s="1">
+        <f t="shared" si="2"/>
+        <v>275.00476190476189</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
       <c r="B4" t="s">
         <v>5</v>
       </c>
@@ -655,8 +708,24 @@
       <c r="E4">
         <v>19</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F4">
+        <f t="shared" si="3"/>
+        <v>404.76</v>
+      </c>
+      <c r="H4">
+        <f t="shared" si="0"/>
+        <v>404.76190476190476</v>
+      </c>
+      <c r="I4">
+        <f t="shared" si="1"/>
+        <v>20.240000000000009</v>
+      </c>
+      <c r="J4" s="1">
+        <f t="shared" si="2"/>
+        <v>425.00190476190477</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
       <c r="B5" t="s">
         <v>6</v>
       </c>
@@ -666,8 +735,24 @@
       <c r="D5">
         <v>350</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F5">
+        <f t="shared" si="3"/>
+        <v>333.33</v>
+      </c>
+      <c r="H5">
+        <f t="shared" si="0"/>
+        <v>333.33333333333331</v>
+      </c>
+      <c r="I5">
+        <f t="shared" si="1"/>
+        <v>16.670000000000016</v>
+      </c>
+      <c r="J5" s="1">
+        <f t="shared" si="2"/>
+        <v>350.00333333333333</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
       <c r="B6" t="s">
         <v>5</v>
       </c>
@@ -680,8 +765,24 @@
       <c r="E6">
         <v>3</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F6">
+        <f t="shared" si="3"/>
+        <v>252.38</v>
+      </c>
+      <c r="H6">
+        <f t="shared" si="0"/>
+        <v>252.38095238095238</v>
+      </c>
+      <c r="I6">
+        <f t="shared" si="1"/>
+        <v>12.620000000000005</v>
+      </c>
+      <c r="J6" s="1">
+        <f t="shared" si="2"/>
+        <v>265.00095238095241</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
       <c r="B7" t="s">
         <v>6</v>
       </c>
@@ -694,8 +795,24 @@
       <c r="E7">
         <v>11</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F7">
+        <f t="shared" si="3"/>
+        <v>404.76</v>
+      </c>
+      <c r="H7">
+        <f t="shared" si="0"/>
+        <v>404.76190476190476</v>
+      </c>
+      <c r="I7">
+        <f t="shared" si="1"/>
+        <v>20.240000000000009</v>
+      </c>
+      <c r="J7" s="1">
+        <f t="shared" si="2"/>
+        <v>425.00190476190477</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10">
       <c r="B8" t="s">
         <v>6</v>
       </c>
@@ -708,8 +825,24 @@
       <c r="E8">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F8">
+        <f t="shared" si="3"/>
+        <v>261.89999999999998</v>
+      </c>
+      <c r="H8">
+        <f t="shared" si="0"/>
+        <v>261.90476190476187</v>
+      </c>
+      <c r="I8">
+        <f t="shared" si="1"/>
+        <v>13.100000000000023</v>
+      </c>
+      <c r="J8" s="1">
+        <f t="shared" si="2"/>
+        <v>275.00476190476189</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
       <c r="B9" t="s">
         <v>6</v>
       </c>
@@ -722,8 +855,24 @@
       <c r="E9">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F9">
+        <f t="shared" si="3"/>
+        <v>947.62</v>
+      </c>
+      <c r="H9">
+        <f t="shared" si="0"/>
+        <v>947.61904761904759</v>
+      </c>
+      <c r="I9">
+        <f t="shared" si="1"/>
+        <v>47.379999999999995</v>
+      </c>
+      <c r="J9" s="1">
+        <f t="shared" si="2"/>
+        <v>994.99904761904759</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10">
       <c r="B10" t="s">
         <v>7</v>
       </c>
@@ -733,8 +882,24 @@
       <c r="D10">
         <v>395</v>
       </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F10">
+        <f t="shared" si="3"/>
+        <v>376.19</v>
+      </c>
+      <c r="H10">
+        <f t="shared" si="0"/>
+        <v>376.19047619047615</v>
+      </c>
+      <c r="I10">
+        <f t="shared" si="1"/>
+        <v>18.810000000000002</v>
+      </c>
+      <c r="J10" s="1">
+        <f t="shared" si="2"/>
+        <v>395.00047619047615</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10">
       <c r="B11" t="s">
         <v>8</v>
       </c>
@@ -744,8 +909,24 @@
       <c r="D11">
         <v>365</v>
       </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F11">
+        <f t="shared" si="3"/>
+        <v>347.62</v>
+      </c>
+      <c r="H11">
+        <f t="shared" si="0"/>
+        <v>347.61904761904759</v>
+      </c>
+      <c r="I11">
+        <f t="shared" si="1"/>
+        <v>17.379999999999995</v>
+      </c>
+      <c r="J11" s="1">
+        <f t="shared" si="2"/>
+        <v>364.99904761904759</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10">
       <c r="B12" t="s">
         <v>9</v>
       </c>
@@ -755,8 +936,24 @@
       <c r="D12">
         <v>375</v>
       </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F12">
+        <f t="shared" si="3"/>
+        <v>357.14</v>
+      </c>
+      <c r="H12">
+        <f t="shared" si="0"/>
+        <v>357.14285714285711</v>
+      </c>
+      <c r="I12">
+        <f t="shared" si="1"/>
+        <v>17.860000000000014</v>
+      </c>
+      <c r="J12" s="1">
+        <f t="shared" si="2"/>
+        <v>375.00285714285712</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10">
       <c r="B13" t="s">
         <v>7</v>
       </c>
@@ -766,8 +963,24 @@
       <c r="D13">
         <v>425</v>
       </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F13">
+        <f t="shared" si="3"/>
+        <v>404.76</v>
+      </c>
+      <c r="H13">
+        <f t="shared" si="0"/>
+        <v>404.76190476190476</v>
+      </c>
+      <c r="I13">
+        <f t="shared" si="1"/>
+        <v>20.240000000000009</v>
+      </c>
+      <c r="J13" s="1">
+        <f t="shared" si="2"/>
+        <v>425.00190476190477</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10">
       <c r="B14" t="s">
         <v>10</v>
       </c>
@@ -777,8 +990,24 @@
       <c r="D14">
         <v>295</v>
       </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F14">
+        <f t="shared" si="3"/>
+        <v>280.95</v>
+      </c>
+      <c r="H14">
+        <f t="shared" si="0"/>
+        <v>280.95238095238096</v>
+      </c>
+      <c r="I14">
+        <f t="shared" si="1"/>
+        <v>14.050000000000011</v>
+      </c>
+      <c r="J14" s="1">
+        <f t="shared" si="2"/>
+        <v>295.00238095238097</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10">
       <c r="B15" t="s">
         <v>11</v>
       </c>
@@ -788,8 +1017,24 @@
       <c r="D15">
         <v>875</v>
       </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F15">
+        <f t="shared" si="3"/>
+        <v>833.33</v>
+      </c>
+      <c r="H15">
+        <f t="shared" si="0"/>
+        <v>833.33333333333326</v>
+      </c>
+      <c r="I15">
+        <f t="shared" si="1"/>
+        <v>41.669999999999959</v>
+      </c>
+      <c r="J15" s="1">
+        <f t="shared" si="2"/>
+        <v>875.00333333333322</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10">
       <c r="B16" t="s">
         <v>11</v>
       </c>
@@ -799,8 +1044,24 @@
       <c r="D16">
         <v>875</v>
       </c>
-    </row>
-    <row r="17" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="F16">
+        <f t="shared" si="3"/>
+        <v>833.33</v>
+      </c>
+      <c r="H16">
+        <f t="shared" si="0"/>
+        <v>833.33333333333326</v>
+      </c>
+      <c r="I16">
+        <f t="shared" si="1"/>
+        <v>41.669999999999959</v>
+      </c>
+      <c r="J16" s="1">
+        <f t="shared" si="2"/>
+        <v>875.00333333333322</v>
+      </c>
+    </row>
+    <row r="17" spans="2:10">
       <c r="B17" t="s">
         <v>12</v>
       </c>
@@ -810,8 +1071,24 @@
       <c r="D17">
         <v>595</v>
       </c>
-    </row>
-    <row r="18" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="F17">
+        <f t="shared" si="3"/>
+        <v>566.66999999999996</v>
+      </c>
+      <c r="H17">
+        <f t="shared" si="0"/>
+        <v>566.66666666666663</v>
+      </c>
+      <c r="I17">
+        <f t="shared" si="1"/>
+        <v>28.330000000000041</v>
+      </c>
+      <c r="J17" s="1">
+        <f t="shared" si="2"/>
+        <v>594.99666666666667</v>
+      </c>
+    </row>
+    <row r="18" spans="2:10">
       <c r="B18" t="s">
         <v>8</v>
       </c>
@@ -821,8 +1098,24 @@
       <c r="D18">
         <v>545</v>
       </c>
-    </row>
-    <row r="19" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="F18">
+        <f t="shared" si="3"/>
+        <v>519.04999999999995</v>
+      </c>
+      <c r="H18">
+        <f t="shared" si="0"/>
+        <v>519.04761904761904</v>
+      </c>
+      <c r="I18">
+        <f t="shared" si="1"/>
+        <v>25.950000000000045</v>
+      </c>
+      <c r="J18" s="1">
+        <f t="shared" si="2"/>
+        <v>544.99761904761908</v>
+      </c>
+    </row>
+    <row r="19" spans="2:10">
       <c r="B19" t="s">
         <v>13</v>
       </c>
@@ -832,8 +1125,24 @@
       <c r="D19">
         <v>265</v>
       </c>
-    </row>
-    <row r="20" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="F19">
+        <f t="shared" si="3"/>
+        <v>252.38</v>
+      </c>
+      <c r="H19">
+        <f t="shared" si="0"/>
+        <v>252.38095238095238</v>
+      </c>
+      <c r="I19">
+        <f t="shared" si="1"/>
+        <v>12.620000000000005</v>
+      </c>
+      <c r="J19" s="1">
+        <f t="shared" si="2"/>
+        <v>265.00095238095241</v>
+      </c>
+    </row>
+    <row r="20" spans="2:10">
       <c r="B20" t="s">
         <v>14</v>
       </c>
@@ -843,8 +1152,24 @@
       <c r="D20">
         <v>365</v>
       </c>
-    </row>
-    <row r="21" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="F20">
+        <f t="shared" si="3"/>
+        <v>347.62</v>
+      </c>
+      <c r="H20">
+        <f t="shared" si="0"/>
+        <v>347.61904761904759</v>
+      </c>
+      <c r="I20">
+        <f t="shared" si="1"/>
+        <v>17.379999999999995</v>
+      </c>
+      <c r="J20" s="1">
+        <f t="shared" si="2"/>
+        <v>364.99904761904759</v>
+      </c>
+    </row>
+    <row r="21" spans="2:10">
       <c r="B21" t="s">
         <v>7</v>
       </c>
@@ -854,8 +1179,24 @@
       <c r="D21">
         <v>395</v>
       </c>
-    </row>
-    <row r="22" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="F21">
+        <f t="shared" si="3"/>
+        <v>376.19</v>
+      </c>
+      <c r="H21">
+        <f t="shared" si="0"/>
+        <v>376.19047619047615</v>
+      </c>
+      <c r="I21">
+        <f t="shared" si="1"/>
+        <v>18.810000000000002</v>
+      </c>
+      <c r="J21" s="1">
+        <f t="shared" si="2"/>
+        <v>395.00047619047615</v>
+      </c>
+    </row>
+    <row r="22" spans="2:10">
       <c r="B22" t="s">
         <v>14</v>
       </c>
@@ -865,8 +1206,24 @@
       <c r="D22">
         <v>595</v>
       </c>
-    </row>
-    <row r="23" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="F22">
+        <f t="shared" si="3"/>
+        <v>566.66999999999996</v>
+      </c>
+      <c r="H22">
+        <f t="shared" si="0"/>
+        <v>566.66666666666663</v>
+      </c>
+      <c r="I22">
+        <f t="shared" si="1"/>
+        <v>28.330000000000041</v>
+      </c>
+      <c r="J22" s="1">
+        <f t="shared" si="2"/>
+        <v>594.99666666666667</v>
+      </c>
+    </row>
+    <row r="23" spans="2:10">
       <c r="B23" t="s">
         <v>15</v>
       </c>
@@ -876,8 +1233,24 @@
       <c r="D23">
         <v>365</v>
       </c>
-    </row>
-    <row r="24" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="F23">
+        <f t="shared" si="3"/>
+        <v>347.62</v>
+      </c>
+      <c r="H23">
+        <f t="shared" si="0"/>
+        <v>347.61904761904759</v>
+      </c>
+      <c r="I23">
+        <f t="shared" si="1"/>
+        <v>17.379999999999995</v>
+      </c>
+      <c r="J23" s="1">
+        <f t="shared" si="2"/>
+        <v>364.99904761904759</v>
+      </c>
+    </row>
+    <row r="24" spans="2:10">
       <c r="B24" t="s">
         <v>15</v>
       </c>
@@ -887,8 +1260,24 @@
       <c r="D24">
         <v>365</v>
       </c>
-    </row>
-    <row r="25" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="F24">
+        <f t="shared" si="3"/>
+        <v>347.62</v>
+      </c>
+      <c r="H24">
+        <f t="shared" si="0"/>
+        <v>347.61904761904759</v>
+      </c>
+      <c r="I24">
+        <f t="shared" si="1"/>
+        <v>17.379999999999995</v>
+      </c>
+      <c r="J24" s="1">
+        <f t="shared" si="2"/>
+        <v>364.99904761904759</v>
+      </c>
+    </row>
+    <row r="25" spans="2:10">
       <c r="B25" t="s">
         <v>6</v>
       </c>
@@ -898,8 +1287,24 @@
       <c r="D25">
         <v>265</v>
       </c>
-    </row>
-    <row r="26" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="F25">
+        <f t="shared" si="3"/>
+        <v>252.38</v>
+      </c>
+      <c r="H25">
+        <f t="shared" si="0"/>
+        <v>252.38095238095238</v>
+      </c>
+      <c r="I25">
+        <f t="shared" si="1"/>
+        <v>12.620000000000005</v>
+      </c>
+      <c r="J25" s="1">
+        <f t="shared" si="2"/>
+        <v>265.00095238095241</v>
+      </c>
+    </row>
+    <row r="26" spans="2:10">
       <c r="B26" t="s">
         <v>7</v>
       </c>
@@ -909,8 +1314,24 @@
       <c r="D26">
         <v>395</v>
       </c>
-    </row>
-    <row r="27" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="F26">
+        <f t="shared" si="3"/>
+        <v>376.19</v>
+      </c>
+      <c r="H26">
+        <f t="shared" si="0"/>
+        <v>376.19047619047615</v>
+      </c>
+      <c r="I26">
+        <f t="shared" si="1"/>
+        <v>18.810000000000002</v>
+      </c>
+      <c r="J26" s="1">
+        <f t="shared" si="2"/>
+        <v>395.00047619047615</v>
+      </c>
+    </row>
+    <row r="27" spans="2:10">
       <c r="B27" t="s">
         <v>16</v>
       </c>
@@ -920,8 +1341,24 @@
       <c r="D27">
         <v>375</v>
       </c>
-    </row>
-    <row r="28" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="F27">
+        <f t="shared" si="3"/>
+        <v>357.14</v>
+      </c>
+      <c r="H27">
+        <f t="shared" si="0"/>
+        <v>357.14285714285711</v>
+      </c>
+      <c r="I27">
+        <f t="shared" si="1"/>
+        <v>17.860000000000014</v>
+      </c>
+      <c r="J27" s="1">
+        <f t="shared" si="2"/>
+        <v>375.00285714285712</v>
+      </c>
+    </row>
+    <row r="28" spans="2:10">
       <c r="B28" t="s">
         <v>17</v>
       </c>
@@ -931,8 +1368,24 @@
       <c r="D28">
         <v>365</v>
       </c>
-    </row>
-    <row r="29" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="F28">
+        <f t="shared" si="3"/>
+        <v>347.62</v>
+      </c>
+      <c r="H28">
+        <f t="shared" si="0"/>
+        <v>347.61904761904759</v>
+      </c>
+      <c r="I28">
+        <f t="shared" si="1"/>
+        <v>17.379999999999995</v>
+      </c>
+      <c r="J28" s="1">
+        <f t="shared" si="2"/>
+        <v>364.99904761904759</v>
+      </c>
+    </row>
+    <row r="29" spans="2:10">
       <c r="B29" t="s">
         <v>17</v>
       </c>
@@ -942,8 +1395,24 @@
       <c r="D29">
         <v>365</v>
       </c>
-    </row>
-    <row r="30" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="F29">
+        <f t="shared" si="3"/>
+        <v>347.62</v>
+      </c>
+      <c r="H29">
+        <f t="shared" si="0"/>
+        <v>347.61904761904759</v>
+      </c>
+      <c r="I29">
+        <f t="shared" si="1"/>
+        <v>17.379999999999995</v>
+      </c>
+      <c r="J29" s="1">
+        <f t="shared" si="2"/>
+        <v>364.99904761904759</v>
+      </c>
+    </row>
+    <row r="30" spans="2:10">
       <c r="B30" t="s">
         <v>7</v>
       </c>
@@ -953,8 +1422,24 @@
       <c r="D30">
         <v>425</v>
       </c>
-    </row>
-    <row r="31" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="F30">
+        <f t="shared" si="3"/>
+        <v>404.76</v>
+      </c>
+      <c r="H30">
+        <f t="shared" si="0"/>
+        <v>404.76190476190476</v>
+      </c>
+      <c r="I30">
+        <f t="shared" si="1"/>
+        <v>20.240000000000009</v>
+      </c>
+      <c r="J30" s="1">
+        <f t="shared" si="2"/>
+        <v>425.00190476190477</v>
+      </c>
+    </row>
+    <row r="31" spans="2:10">
       <c r="B31" t="s">
         <v>17</v>
       </c>
@@ -964,8 +1449,24 @@
       <c r="D31">
         <v>365</v>
       </c>
-    </row>
-    <row r="32" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="F31">
+        <f t="shared" si="3"/>
+        <v>347.62</v>
+      </c>
+      <c r="H31">
+        <f t="shared" si="0"/>
+        <v>347.61904761904759</v>
+      </c>
+      <c r="I31">
+        <f t="shared" si="1"/>
+        <v>17.379999999999995</v>
+      </c>
+      <c r="J31" s="1">
+        <f t="shared" si="2"/>
+        <v>364.99904761904759</v>
+      </c>
+    </row>
+    <row r="32" spans="2:10">
       <c r="B32" t="s">
         <v>7</v>
       </c>
@@ -975,8 +1476,24 @@
       <c r="D32">
         <v>395</v>
       </c>
-    </row>
-    <row r="33" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F32">
+        <f t="shared" si="3"/>
+        <v>376.19</v>
+      </c>
+      <c r="H32">
+        <f t="shared" si="0"/>
+        <v>376.19047619047615</v>
+      </c>
+      <c r="I32">
+        <f t="shared" si="1"/>
+        <v>18.810000000000002</v>
+      </c>
+      <c r="J32" s="1">
+        <f t="shared" si="2"/>
+        <v>395.00047619047615</v>
+      </c>
+    </row>
+    <row r="33" spans="2:10">
       <c r="B33" t="s">
         <v>8</v>
       </c>
@@ -986,8 +1503,24 @@
       <c r="D33">
         <v>365</v>
       </c>
-    </row>
-    <row r="34" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F33">
+        <f t="shared" si="3"/>
+        <v>347.62</v>
+      </c>
+      <c r="H33">
+        <f t="shared" si="0"/>
+        <v>347.61904761904759</v>
+      </c>
+      <c r="I33">
+        <f t="shared" si="1"/>
+        <v>17.379999999999995</v>
+      </c>
+      <c r="J33" s="1">
+        <f t="shared" si="2"/>
+        <v>364.99904761904759</v>
+      </c>
+    </row>
+    <row r="34" spans="2:10">
       <c r="B34" t="s">
         <v>16</v>
       </c>
@@ -997,8 +1530,24 @@
       <c r="D34">
         <v>375</v>
       </c>
-    </row>
-    <row r="35" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F34">
+        <f t="shared" si="3"/>
+        <v>357.14</v>
+      </c>
+      <c r="H34">
+        <f t="shared" si="0"/>
+        <v>357.14285714285711</v>
+      </c>
+      <c r="I34">
+        <f t="shared" si="1"/>
+        <v>17.860000000000014</v>
+      </c>
+      <c r="J34" s="1">
+        <f t="shared" si="2"/>
+        <v>375.00285714285712</v>
+      </c>
+    </row>
+    <row r="35" spans="2:10">
       <c r="B35" t="s">
         <v>15</v>
       </c>
@@ -1008,8 +1557,24 @@
       <c r="D35">
         <v>365</v>
       </c>
-    </row>
-    <row r="36" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F35">
+        <f t="shared" si="3"/>
+        <v>347.62</v>
+      </c>
+      <c r="H35">
+        <f t="shared" si="0"/>
+        <v>347.61904761904759</v>
+      </c>
+      <c r="I35">
+        <f t="shared" si="1"/>
+        <v>17.379999999999995</v>
+      </c>
+      <c r="J35" s="1">
+        <f t="shared" si="2"/>
+        <v>364.99904761904759</v>
+      </c>
+    </row>
+    <row r="36" spans="2:10">
       <c r="B36" t="s">
         <v>18</v>
       </c>
@@ -1022,8 +1587,24 @@
       <c r="E36">
         <v>2</v>
       </c>
-    </row>
-    <row r="37" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F36">
+        <f t="shared" si="3"/>
+        <v>1738.1</v>
+      </c>
+      <c r="H36">
+        <f t="shared" si="0"/>
+        <v>1738.0952380952381</v>
+      </c>
+      <c r="I36">
+        <f t="shared" si="1"/>
+        <v>86.900000000000091</v>
+      </c>
+      <c r="J36" s="1">
+        <f t="shared" si="2"/>
+        <v>1824.9952380952382</v>
+      </c>
+    </row>
+    <row r="37" spans="2:10">
       <c r="B37" t="s">
         <v>16</v>
       </c>
@@ -1033,8 +1614,24 @@
       <c r="D37">
         <v>375</v>
       </c>
-    </row>
-    <row r="38" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F37">
+        <f t="shared" si="3"/>
+        <v>357.14</v>
+      </c>
+      <c r="H37">
+        <f t="shared" si="0"/>
+        <v>357.14285714285711</v>
+      </c>
+      <c r="I37">
+        <f t="shared" si="1"/>
+        <v>17.860000000000014</v>
+      </c>
+      <c r="J37" s="1">
+        <f t="shared" si="2"/>
+        <v>375.00285714285712</v>
+      </c>
+    </row>
+    <row r="38" spans="2:10">
       <c r="B38" t="s">
         <v>8</v>
       </c>
@@ -1044,8 +1641,24 @@
       <c r="D38">
         <v>365</v>
       </c>
-    </row>
-    <row r="39" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F38">
+        <f t="shared" si="3"/>
+        <v>347.62</v>
+      </c>
+      <c r="H38">
+        <f t="shared" si="0"/>
+        <v>347.61904761904759</v>
+      </c>
+      <c r="I38">
+        <f t="shared" si="1"/>
+        <v>17.379999999999995</v>
+      </c>
+      <c r="J38" s="1">
+        <f t="shared" si="2"/>
+        <v>364.99904761904759</v>
+      </c>
+    </row>
+    <row r="39" spans="2:10">
       <c r="B39" t="s">
         <v>17</v>
       </c>
@@ -1055,8 +1668,24 @@
       <c r="D39">
         <v>365</v>
       </c>
-    </row>
-    <row r="40" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F39">
+        <f t="shared" si="3"/>
+        <v>347.62</v>
+      </c>
+      <c r="H39">
+        <f t="shared" si="0"/>
+        <v>347.61904761904759</v>
+      </c>
+      <c r="I39">
+        <f t="shared" si="1"/>
+        <v>17.379999999999995</v>
+      </c>
+      <c r="J39" s="1">
+        <f t="shared" si="2"/>
+        <v>364.99904761904759</v>
+      </c>
+    </row>
+    <row r="40" spans="2:10">
       <c r="B40" t="s">
         <v>8</v>
       </c>
@@ -1066,8 +1695,24 @@
       <c r="D40">
         <v>365</v>
       </c>
-    </row>
-    <row r="41" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F40">
+        <f t="shared" si="3"/>
+        <v>347.62</v>
+      </c>
+      <c r="H40">
+        <f t="shared" si="0"/>
+        <v>347.61904761904759</v>
+      </c>
+      <c r="I40">
+        <f t="shared" si="1"/>
+        <v>17.379999999999995</v>
+      </c>
+      <c r="J40" s="1">
+        <f t="shared" si="2"/>
+        <v>364.99904761904759</v>
+      </c>
+    </row>
+    <row r="41" spans="2:10">
       <c r="B41" t="s">
         <v>19</v>
       </c>
@@ -1077,8 +1722,24 @@
       <c r="D41">
         <v>675</v>
       </c>
-    </row>
-    <row r="42" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F41">
+        <f t="shared" si="3"/>
+        <v>642.86</v>
+      </c>
+      <c r="H41">
+        <f t="shared" si="0"/>
+        <v>642.85714285714278</v>
+      </c>
+      <c r="I41">
+        <f t="shared" si="1"/>
+        <v>32.139999999999986</v>
+      </c>
+      <c r="J41" s="1">
+        <f t="shared" si="2"/>
+        <v>674.99714285714276</v>
+      </c>
+    </row>
+    <row r="42" spans="2:10">
       <c r="B42" t="s">
         <v>8</v>
       </c>
@@ -1088,8 +1749,24 @@
       <c r="D42">
         <v>365</v>
       </c>
-    </row>
-    <row r="43" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F42">
+        <f t="shared" si="3"/>
+        <v>347.62</v>
+      </c>
+      <c r="H42">
+        <f t="shared" si="0"/>
+        <v>347.61904761904759</v>
+      </c>
+      <c r="I42">
+        <f t="shared" si="1"/>
+        <v>17.379999999999995</v>
+      </c>
+      <c r="J42" s="1">
+        <f t="shared" si="2"/>
+        <v>364.99904761904759</v>
+      </c>
+    </row>
+    <row r="43" spans="2:10">
       <c r="B43" t="s">
         <v>13</v>
       </c>
@@ -1099,8 +1776,24 @@
       <c r="D43">
         <v>295</v>
       </c>
-    </row>
-    <row r="44" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F43">
+        <f t="shared" si="3"/>
+        <v>280.95</v>
+      </c>
+      <c r="H43">
+        <f t="shared" si="0"/>
+        <v>280.95238095238096</v>
+      </c>
+      <c r="I43">
+        <f t="shared" si="1"/>
+        <v>14.050000000000011</v>
+      </c>
+      <c r="J43" s="1">
+        <f t="shared" si="2"/>
+        <v>295.00238095238097</v>
+      </c>
+    </row>
+    <row r="44" spans="2:10">
       <c r="B44" t="s">
         <v>16</v>
       </c>
@@ -1110,8 +1803,24 @@
       <c r="D44">
         <v>375</v>
       </c>
-    </row>
-    <row r="45" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F44">
+        <f t="shared" si="3"/>
+        <v>357.14</v>
+      </c>
+      <c r="H44">
+        <f t="shared" si="0"/>
+        <v>357.14285714285711</v>
+      </c>
+      <c r="I44">
+        <f t="shared" si="1"/>
+        <v>17.860000000000014</v>
+      </c>
+      <c r="J44" s="1">
+        <f t="shared" si="2"/>
+        <v>375.00285714285712</v>
+      </c>
+    </row>
+    <row r="45" spans="2:10">
       <c r="B45" t="s">
         <v>15</v>
       </c>
@@ -1121,8 +1830,24 @@
       <c r="D45">
         <v>365</v>
       </c>
-    </row>
-    <row r="46" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F45">
+        <f t="shared" si="3"/>
+        <v>347.62</v>
+      </c>
+      <c r="H45">
+        <f t="shared" si="0"/>
+        <v>347.61904761904759</v>
+      </c>
+      <c r="I45">
+        <f t="shared" si="1"/>
+        <v>17.379999999999995</v>
+      </c>
+      <c r="J45" s="1">
+        <f t="shared" si="2"/>
+        <v>364.99904761904759</v>
+      </c>
+    </row>
+    <row r="46" spans="2:10">
       <c r="B46" t="s">
         <v>7</v>
       </c>
@@ -1132,8 +1857,24 @@
       <c r="D46">
         <v>425</v>
       </c>
-    </row>
-    <row r="47" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F46">
+        <f t="shared" si="3"/>
+        <v>404.76</v>
+      </c>
+      <c r="H46">
+        <f t="shared" si="0"/>
+        <v>404.76190476190476</v>
+      </c>
+      <c r="I46">
+        <f t="shared" si="1"/>
+        <v>20.240000000000009</v>
+      </c>
+      <c r="J46" s="1">
+        <f t="shared" si="2"/>
+        <v>425.00190476190477</v>
+      </c>
+    </row>
+    <row r="47" spans="2:10">
       <c r="B47" t="s">
         <v>5</v>
       </c>
@@ -1143,8 +1884,24 @@
       <c r="D47">
         <v>295</v>
       </c>
-    </row>
-    <row r="48" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F47">
+        <f t="shared" si="3"/>
+        <v>280.95</v>
+      </c>
+      <c r="H47">
+        <f t="shared" si="0"/>
+        <v>280.95238095238096</v>
+      </c>
+      <c r="I47">
+        <f t="shared" si="1"/>
+        <v>14.050000000000011</v>
+      </c>
+      <c r="J47" s="1">
+        <f t="shared" si="2"/>
+        <v>295.00238095238097</v>
+      </c>
+    </row>
+    <row r="48" spans="2:10">
       <c r="B48" t="s">
         <v>7</v>
       </c>
@@ -1154,8 +1911,24 @@
       <c r="D48">
         <v>395</v>
       </c>
-    </row>
-    <row r="49" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F48">
+        <f t="shared" si="3"/>
+        <v>376.19</v>
+      </c>
+      <c r="H48">
+        <f t="shared" si="0"/>
+        <v>376.19047619047615</v>
+      </c>
+      <c r="I48">
+        <f t="shared" si="1"/>
+        <v>18.810000000000002</v>
+      </c>
+      <c r="J48" s="1">
+        <f t="shared" si="2"/>
+        <v>395.00047619047615</v>
+      </c>
+    </row>
+    <row r="49" spans="2:10">
       <c r="B49" t="s">
         <v>17</v>
       </c>
@@ -1165,8 +1938,24 @@
       <c r="D49">
         <v>305</v>
       </c>
-    </row>
-    <row r="50" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F49">
+        <f t="shared" si="3"/>
+        <v>290.48</v>
+      </c>
+      <c r="H49">
+        <f t="shared" si="0"/>
+        <v>290.47619047619048</v>
+      </c>
+      <c r="I49">
+        <f t="shared" si="1"/>
+        <v>14.519999999999982</v>
+      </c>
+      <c r="J49" s="1">
+        <f t="shared" si="2"/>
+        <v>304.99619047619046</v>
+      </c>
+    </row>
+    <row r="50" spans="2:10">
       <c r="B50" t="s">
         <v>20</v>
       </c>
@@ -1176,8 +1965,24 @@
       <c r="D50">
         <v>365</v>
       </c>
-    </row>
-    <row r="51" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F50">
+        <f t="shared" si="3"/>
+        <v>347.62</v>
+      </c>
+      <c r="H50">
+        <f t="shared" si="0"/>
+        <v>347.61904761904759</v>
+      </c>
+      <c r="I50">
+        <f t="shared" si="1"/>
+        <v>17.379999999999995</v>
+      </c>
+      <c r="J50" s="1">
+        <f t="shared" si="2"/>
+        <v>364.99904761904759</v>
+      </c>
+    </row>
+    <row r="51" spans="2:10">
       <c r="B51" t="s">
         <v>7</v>
       </c>
@@ -1187,8 +1992,24 @@
       <c r="D51">
         <v>395</v>
       </c>
-    </row>
-    <row r="52" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F51">
+        <f t="shared" si="3"/>
+        <v>376.19</v>
+      </c>
+      <c r="H51">
+        <f t="shared" si="0"/>
+        <v>376.19047619047615</v>
+      </c>
+      <c r="I51">
+        <f t="shared" si="1"/>
+        <v>18.810000000000002</v>
+      </c>
+      <c r="J51" s="1">
+        <f t="shared" si="2"/>
+        <v>395.00047619047615</v>
+      </c>
+    </row>
+    <row r="52" spans="2:10">
       <c r="B52" t="s">
         <v>19</v>
       </c>
@@ -1198,8 +2019,24 @@
       <c r="D52">
         <v>675</v>
       </c>
-    </row>
-    <row r="53" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F52">
+        <f t="shared" si="3"/>
+        <v>642.86</v>
+      </c>
+      <c r="H52">
+        <f t="shared" si="0"/>
+        <v>642.85714285714278</v>
+      </c>
+      <c r="I52">
+        <f t="shared" si="1"/>
+        <v>32.139999999999986</v>
+      </c>
+      <c r="J52" s="1">
+        <f t="shared" si="2"/>
+        <v>674.99714285714276</v>
+      </c>
+    </row>
+    <row r="53" spans="2:10">
       <c r="B53" t="s">
         <v>16</v>
       </c>
@@ -1209,8 +2046,24 @@
       <c r="D53">
         <v>375</v>
       </c>
-    </row>
-    <row r="54" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F53">
+        <f t="shared" si="3"/>
+        <v>357.14</v>
+      </c>
+      <c r="H53">
+        <f t="shared" si="0"/>
+        <v>357.14285714285711</v>
+      </c>
+      <c r="I53">
+        <f t="shared" si="1"/>
+        <v>17.860000000000014</v>
+      </c>
+      <c r="J53" s="1">
+        <f t="shared" si="2"/>
+        <v>375.00285714285712</v>
+      </c>
+    </row>
+    <row r="54" spans="2:10">
       <c r="B54" t="s">
         <v>8</v>
       </c>
@@ -1220,8 +2073,24 @@
       <c r="D54">
         <v>365</v>
       </c>
-    </row>
-    <row r="55" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F54">
+        <f t="shared" si="3"/>
+        <v>347.62</v>
+      </c>
+      <c r="H54">
+        <f t="shared" si="0"/>
+        <v>347.61904761904759</v>
+      </c>
+      <c r="I54">
+        <f t="shared" si="1"/>
+        <v>17.379999999999995</v>
+      </c>
+      <c r="J54" s="1">
+        <f t="shared" si="2"/>
+        <v>364.99904761904759</v>
+      </c>
+    </row>
+    <row r="55" spans="2:10">
       <c r="B55" t="s">
         <v>21</v>
       </c>
@@ -1231,8 +2100,24 @@
       <c r="D55">
         <v>375</v>
       </c>
-    </row>
-    <row r="56" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F55">
+        <f t="shared" si="3"/>
+        <v>357.14</v>
+      </c>
+      <c r="H55">
+        <f t="shared" si="0"/>
+        <v>357.14285714285711</v>
+      </c>
+      <c r="I55">
+        <f t="shared" si="1"/>
+        <v>17.860000000000014</v>
+      </c>
+      <c r="J55" s="1">
+        <f t="shared" si="2"/>
+        <v>375.00285714285712</v>
+      </c>
+    </row>
+    <row r="56" spans="2:10">
       <c r="B56" t="s">
         <v>11</v>
       </c>
@@ -1245,8 +2130,24 @@
       <c r="E56">
         <v>2</v>
       </c>
-    </row>
-    <row r="57" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F56">
+        <f t="shared" si="3"/>
+        <v>833.33</v>
+      </c>
+      <c r="H56">
+        <f t="shared" si="0"/>
+        <v>833.33333333333326</v>
+      </c>
+      <c r="I56">
+        <f t="shared" si="1"/>
+        <v>41.669999999999959</v>
+      </c>
+      <c r="J56" s="1">
+        <f t="shared" si="2"/>
+        <v>875.00333333333322</v>
+      </c>
+    </row>
+    <row r="57" spans="2:10">
       <c r="B57" t="s">
         <v>7</v>
       </c>
@@ -1256,8 +2157,24 @@
       <c r="D57">
         <v>395</v>
       </c>
-    </row>
-    <row r="58" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F57">
+        <f t="shared" si="3"/>
+        <v>376.19</v>
+      </c>
+      <c r="H57">
+        <f t="shared" si="0"/>
+        <v>376.19047619047615</v>
+      </c>
+      <c r="I57">
+        <f t="shared" si="1"/>
+        <v>18.810000000000002</v>
+      </c>
+      <c r="J57" s="1">
+        <f t="shared" si="2"/>
+        <v>395.00047619047615</v>
+      </c>
+    </row>
+    <row r="58" spans="2:10">
       <c r="B58" t="s">
         <v>7</v>
       </c>
@@ -1267,8 +2184,24 @@
       <c r="D58">
         <v>395</v>
       </c>
-    </row>
-    <row r="59" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F58">
+        <f t="shared" si="3"/>
+        <v>376.19</v>
+      </c>
+      <c r="H58">
+        <f t="shared" si="0"/>
+        <v>376.19047619047615</v>
+      </c>
+      <c r="I58">
+        <f t="shared" si="1"/>
+        <v>18.810000000000002</v>
+      </c>
+      <c r="J58" s="1">
+        <f t="shared" si="2"/>
+        <v>395.00047619047615</v>
+      </c>
+    </row>
+    <row r="59" spans="2:10">
       <c r="B59" t="s">
         <v>22</v>
       </c>
@@ -1278,8 +2211,24 @@
       <c r="D59">
         <v>595</v>
       </c>
-    </row>
-    <row r="60" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F59">
+        <f t="shared" si="3"/>
+        <v>566.66999999999996</v>
+      </c>
+      <c r="H59">
+        <f t="shared" si="0"/>
+        <v>566.66666666666663</v>
+      </c>
+      <c r="I59">
+        <f t="shared" si="1"/>
+        <v>28.330000000000041</v>
+      </c>
+      <c r="J59" s="1">
+        <f t="shared" si="2"/>
+        <v>594.99666666666667</v>
+      </c>
+    </row>
+    <row r="60" spans="2:10">
       <c r="B60" t="s">
         <v>23</v>
       </c>
@@ -1289,8 +2238,24 @@
       <c r="D60">
         <v>1325</v>
       </c>
-    </row>
-    <row r="61" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F60">
+        <f t="shared" si="3"/>
+        <v>1261.9000000000001</v>
+      </c>
+      <c r="H60">
+        <f t="shared" si="0"/>
+        <v>1261.9047619047619</v>
+      </c>
+      <c r="I60">
+        <f t="shared" si="1"/>
+        <v>63.099999999999909</v>
+      </c>
+      <c r="J60" s="1">
+        <f t="shared" si="2"/>
+        <v>1325.0047619047618</v>
+      </c>
+    </row>
+    <row r="61" spans="2:10">
       <c r="B61" t="s">
         <v>23</v>
       </c>
@@ -1303,8 +2268,24 @@
       <c r="E61">
         <v>10</v>
       </c>
-    </row>
-    <row r="62" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F61">
+        <f t="shared" si="3"/>
+        <v>1380.95</v>
+      </c>
+      <c r="H61">
+        <f t="shared" si="0"/>
+        <v>1380.952380952381</v>
+      </c>
+      <c r="I61">
+        <f t="shared" si="1"/>
+        <v>69.049999999999955</v>
+      </c>
+      <c r="J61" s="1">
+        <f t="shared" si="2"/>
+        <v>1450.0023809523809</v>
+      </c>
+    </row>
+    <row r="62" spans="2:10">
       <c r="B62" t="s">
         <v>24</v>
       </c>
@@ -1314,8 +2295,24 @@
       <c r="D62">
         <v>1995</v>
       </c>
-    </row>
-    <row r="63" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F62">
+        <f t="shared" si="3"/>
+        <v>1900</v>
+      </c>
+      <c r="H62">
+        <f t="shared" si="0"/>
+        <v>1900</v>
+      </c>
+      <c r="I62">
+        <f t="shared" si="1"/>
+        <v>95</v>
+      </c>
+      <c r="J62" s="1">
+        <f t="shared" si="2"/>
+        <v>1995</v>
+      </c>
+    </row>
+    <row r="63" spans="2:10">
       <c r="B63" t="s">
         <v>25</v>
       </c>
@@ -1328,8 +2325,24 @@
       <c r="E63">
         <v>2</v>
       </c>
-    </row>
-    <row r="64" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F63">
+        <f t="shared" si="3"/>
+        <v>1690.48</v>
+      </c>
+      <c r="H63">
+        <f t="shared" si="0"/>
+        <v>1690.4761904761904</v>
+      </c>
+      <c r="I63">
+        <f t="shared" si="1"/>
+        <v>84.519999999999982</v>
+      </c>
+      <c r="J63" s="1">
+        <f t="shared" si="2"/>
+        <v>1774.9961904761903</v>
+      </c>
+    </row>
+    <row r="64" spans="2:10">
       <c r="B64" t="s">
         <v>24</v>
       </c>
@@ -1342,8 +2355,24 @@
       <c r="E64">
         <v>6</v>
       </c>
-    </row>
-    <row r="65" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F64">
+        <f t="shared" si="3"/>
+        <v>1900</v>
+      </c>
+      <c r="H64">
+        <f t="shared" si="0"/>
+        <v>1900</v>
+      </c>
+      <c r="I64">
+        <f t="shared" si="1"/>
+        <v>95</v>
+      </c>
+      <c r="J64" s="1">
+        <f t="shared" si="2"/>
+        <v>1995</v>
+      </c>
+    </row>
+    <row r="65" spans="2:10">
       <c r="B65" t="s">
         <v>26</v>
       </c>
@@ -1356,8 +2385,24 @@
       <c r="E65">
         <v>2</v>
       </c>
-    </row>
-    <row r="66" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F65">
+        <f t="shared" si="3"/>
+        <v>947.62</v>
+      </c>
+      <c r="H65">
+        <f t="shared" si="0"/>
+        <v>947.61904761904759</v>
+      </c>
+      <c r="I65">
+        <f t="shared" si="1"/>
+        <v>47.379999999999995</v>
+      </c>
+      <c r="J65" s="1">
+        <f t="shared" si="2"/>
+        <v>994.99904761904759</v>
+      </c>
+    </row>
+    <row r="66" spans="2:10">
       <c r="B66" t="s">
         <v>5</v>
       </c>
@@ -1370,8 +2415,24 @@
       <c r="E66">
         <v>11</v>
       </c>
-    </row>
-    <row r="67" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F66">
+        <f t="shared" si="3"/>
+        <v>280.95</v>
+      </c>
+      <c r="H66">
+        <f t="shared" ref="H66:H108" si="4">D66/1.05</f>
+        <v>280.95238095238096</v>
+      </c>
+      <c r="I66">
+        <f t="shared" ref="I66:I108" si="5">D66-F66</f>
+        <v>14.050000000000011</v>
+      </c>
+      <c r="J66" s="1">
+        <f t="shared" ref="J66:J108" si="6">SUM(H66:I66)</f>
+        <v>295.00238095238097</v>
+      </c>
+    </row>
+    <row r="67" spans="2:10">
       <c r="B67" t="s">
         <v>6</v>
       </c>
@@ -1381,8 +2442,24 @@
       <c r="D67">
         <v>575</v>
       </c>
-    </row>
-    <row r="68" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F67">
+        <f t="shared" ref="F67:F110" si="7">ROUND(IF(D67&gt;2500, D67/1.18, D67/1.05),2)</f>
+        <v>547.62</v>
+      </c>
+      <c r="H67">
+        <f t="shared" si="4"/>
+        <v>547.61904761904759</v>
+      </c>
+      <c r="I67">
+        <f t="shared" si="5"/>
+        <v>27.379999999999995</v>
+      </c>
+      <c r="J67" s="1">
+        <f t="shared" si="6"/>
+        <v>574.99904761904759</v>
+      </c>
+    </row>
+    <row r="68" spans="2:10">
       <c r="B68" t="s">
         <v>27</v>
       </c>
@@ -1392,8 +2469,24 @@
       <c r="D68">
         <v>675</v>
       </c>
-    </row>
-    <row r="69" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F68">
+        <f t="shared" si="7"/>
+        <v>642.86</v>
+      </c>
+      <c r="H68">
+        <f t="shared" si="4"/>
+        <v>642.85714285714278</v>
+      </c>
+      <c r="I68">
+        <f t="shared" si="5"/>
+        <v>32.139999999999986</v>
+      </c>
+      <c r="J68" s="1">
+        <f t="shared" si="6"/>
+        <v>674.99714285714276</v>
+      </c>
+    </row>
+    <row r="69" spans="2:10">
       <c r="B69" t="s">
         <v>16</v>
       </c>
@@ -1403,8 +2496,24 @@
       <c r="D69">
         <v>845</v>
       </c>
-    </row>
-    <row r="70" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F69">
+        <f t="shared" si="7"/>
+        <v>804.76</v>
+      </c>
+      <c r="H69">
+        <f t="shared" si="4"/>
+        <v>804.7619047619047</v>
+      </c>
+      <c r="I69">
+        <f t="shared" si="5"/>
+        <v>40.240000000000009</v>
+      </c>
+      <c r="J69" s="1">
+        <f t="shared" si="6"/>
+        <v>845.00190476190471</v>
+      </c>
+    </row>
+    <row r="70" spans="2:10">
       <c r="B70" t="s">
         <v>28</v>
       </c>
@@ -1414,8 +2523,24 @@
       <c r="D70">
         <v>675</v>
       </c>
-    </row>
-    <row r="71" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F70">
+        <f t="shared" si="7"/>
+        <v>642.86</v>
+      </c>
+      <c r="H70">
+        <f t="shared" si="4"/>
+        <v>642.85714285714278</v>
+      </c>
+      <c r="I70">
+        <f t="shared" si="5"/>
+        <v>32.139999999999986</v>
+      </c>
+      <c r="J70" s="1">
+        <f t="shared" si="6"/>
+        <v>674.99714285714276</v>
+      </c>
+    </row>
+    <row r="71" spans="2:10">
       <c r="B71" t="s">
         <v>28</v>
       </c>
@@ -1425,8 +2550,24 @@
       <c r="D71">
         <v>295</v>
       </c>
-    </row>
-    <row r="72" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F71">
+        <f t="shared" si="7"/>
+        <v>280.95</v>
+      </c>
+      <c r="H71">
+        <f t="shared" si="4"/>
+        <v>280.95238095238096</v>
+      </c>
+      <c r="I71">
+        <f t="shared" si="5"/>
+        <v>14.050000000000011</v>
+      </c>
+      <c r="J71" s="1">
+        <f t="shared" si="6"/>
+        <v>295.00238095238097</v>
+      </c>
+    </row>
+    <row r="72" spans="2:10">
       <c r="B72" t="s">
         <v>28</v>
       </c>
@@ -1436,8 +2577,24 @@
       <c r="D72">
         <v>675</v>
       </c>
-    </row>
-    <row r="73" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F72">
+        <f t="shared" si="7"/>
+        <v>642.86</v>
+      </c>
+      <c r="H72">
+        <f t="shared" si="4"/>
+        <v>642.85714285714278</v>
+      </c>
+      <c r="I72">
+        <f t="shared" si="5"/>
+        <v>32.139999999999986</v>
+      </c>
+      <c r="J72" s="1">
+        <f t="shared" si="6"/>
+        <v>674.99714285714276</v>
+      </c>
+    </row>
+    <row r="73" spans="2:10">
       <c r="B73" t="s">
         <v>28</v>
       </c>
@@ -1450,8 +2607,24 @@
       <c r="E73">
         <v>10</v>
       </c>
-    </row>
-    <row r="74" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F73">
+        <f t="shared" si="7"/>
+        <v>1071.43</v>
+      </c>
+      <c r="H73">
+        <f t="shared" si="4"/>
+        <v>1071.4285714285713</v>
+      </c>
+      <c r="I73">
+        <f t="shared" si="5"/>
+        <v>53.569999999999936</v>
+      </c>
+      <c r="J73" s="1">
+        <f t="shared" si="6"/>
+        <v>1124.9985714285713</v>
+      </c>
+    </row>
+    <row r="74" spans="2:10">
       <c r="B74" t="s">
         <v>28</v>
       </c>
@@ -1464,8 +2637,24 @@
       <c r="E74">
         <v>15</v>
       </c>
-    </row>
-    <row r="75" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F74">
+        <f t="shared" si="7"/>
+        <v>280.95</v>
+      </c>
+      <c r="H74">
+        <f t="shared" si="4"/>
+        <v>280.95238095238096</v>
+      </c>
+      <c r="I74">
+        <f t="shared" si="5"/>
+        <v>14.050000000000011</v>
+      </c>
+      <c r="J74" s="1">
+        <f t="shared" si="6"/>
+        <v>295.00238095238097</v>
+      </c>
+    </row>
+    <row r="75" spans="2:10">
       <c r="B75" t="s">
         <v>29</v>
       </c>
@@ -1478,8 +2667,24 @@
       <c r="E75">
         <v>12</v>
       </c>
-    </row>
-    <row r="76" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F75">
+        <f t="shared" si="7"/>
+        <v>547.62</v>
+      </c>
+      <c r="H75">
+        <f t="shared" si="4"/>
+        <v>547.61904761904759</v>
+      </c>
+      <c r="I75">
+        <f t="shared" si="5"/>
+        <v>27.379999999999995</v>
+      </c>
+      <c r="J75" s="1">
+        <f t="shared" si="6"/>
+        <v>574.99904761904759</v>
+      </c>
+    </row>
+    <row r="76" spans="2:10">
       <c r="B76" t="s">
         <v>30</v>
       </c>
@@ -1489,8 +2694,24 @@
       <c r="D76">
         <v>1050</v>
       </c>
-    </row>
-    <row r="77" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F76">
+        <f t="shared" si="7"/>
+        <v>1000</v>
+      </c>
+      <c r="H76">
+        <f t="shared" si="4"/>
+        <v>1000</v>
+      </c>
+      <c r="I76">
+        <f t="shared" si="5"/>
+        <v>50</v>
+      </c>
+      <c r="J76" s="1">
+        <f t="shared" si="6"/>
+        <v>1050</v>
+      </c>
+    </row>
+    <row r="77" spans="2:10">
       <c r="B77" t="s">
         <v>31</v>
       </c>
@@ -1500,8 +2721,24 @@
       <c r="D77">
         <v>1050</v>
       </c>
-    </row>
-    <row r="78" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F77">
+        <f t="shared" si="7"/>
+        <v>1000</v>
+      </c>
+      <c r="H77">
+        <f t="shared" si="4"/>
+        <v>1000</v>
+      </c>
+      <c r="I77">
+        <f t="shared" si="5"/>
+        <v>50</v>
+      </c>
+      <c r="J77" s="1">
+        <f t="shared" si="6"/>
+        <v>1050</v>
+      </c>
+    </row>
+    <row r="78" spans="2:10">
       <c r="B78" t="s">
         <v>28</v>
       </c>
@@ -1511,8 +2748,24 @@
       <c r="D78">
         <v>295</v>
       </c>
-    </row>
-    <row r="79" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F78">
+        <f t="shared" si="7"/>
+        <v>280.95</v>
+      </c>
+      <c r="H78">
+        <f t="shared" si="4"/>
+        <v>280.95238095238096</v>
+      </c>
+      <c r="I78">
+        <f t="shared" si="5"/>
+        <v>14.050000000000011</v>
+      </c>
+      <c r="J78" s="1">
+        <f t="shared" si="6"/>
+        <v>295.00238095238097</v>
+      </c>
+    </row>
+    <row r="79" spans="2:10">
       <c r="B79" t="s">
         <v>30</v>
       </c>
@@ -1522,8 +2775,24 @@
       <c r="D79">
         <v>995</v>
       </c>
-    </row>
-    <row r="80" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F79">
+        <f t="shared" si="7"/>
+        <v>947.62</v>
+      </c>
+      <c r="H79">
+        <f t="shared" si="4"/>
+        <v>947.61904761904759</v>
+      </c>
+      <c r="I79">
+        <f t="shared" si="5"/>
+        <v>47.379999999999995</v>
+      </c>
+      <c r="J79" s="1">
+        <f t="shared" si="6"/>
+        <v>994.99904761904759</v>
+      </c>
+    </row>
+    <row r="80" spans="2:10">
       <c r="B80" t="s">
         <v>13</v>
       </c>
@@ -1533,8 +2802,24 @@
       <c r="D80">
         <v>1050</v>
       </c>
-    </row>
-    <row r="81" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F80">
+        <f t="shared" si="7"/>
+        <v>1000</v>
+      </c>
+      <c r="H80">
+        <f t="shared" si="4"/>
+        <v>1000</v>
+      </c>
+      <c r="I80">
+        <f t="shared" si="5"/>
+        <v>50</v>
+      </c>
+      <c r="J80" s="1">
+        <f t="shared" si="6"/>
+        <v>1050</v>
+      </c>
+    </row>
+    <row r="81" spans="2:10">
       <c r="B81" t="s">
         <v>21</v>
       </c>
@@ -1544,8 +2829,24 @@
       <c r="D81">
         <v>685</v>
       </c>
-    </row>
-    <row r="82" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F81">
+        <f t="shared" si="7"/>
+        <v>652.38</v>
+      </c>
+      <c r="H81">
+        <f t="shared" si="4"/>
+        <v>652.38095238095241</v>
+      </c>
+      <c r="I81">
+        <f t="shared" si="5"/>
+        <v>32.620000000000005</v>
+      </c>
+      <c r="J81" s="1">
+        <f t="shared" si="6"/>
+        <v>685.00095238095241</v>
+      </c>
+    </row>
+    <row r="82" spans="2:10">
       <c r="B82" t="s">
         <v>21</v>
       </c>
@@ -1558,8 +2859,24 @@
       <c r="E82">
         <v>6</v>
       </c>
-    </row>
-    <row r="83" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F82">
+        <f t="shared" si="7"/>
+        <v>804.76</v>
+      </c>
+      <c r="H82">
+        <f t="shared" si="4"/>
+        <v>804.7619047619047</v>
+      </c>
+      <c r="I82">
+        <f t="shared" si="5"/>
+        <v>40.240000000000009</v>
+      </c>
+      <c r="J82" s="1">
+        <f t="shared" si="6"/>
+        <v>845.00190476190471</v>
+      </c>
+    </row>
+    <row r="83" spans="2:10">
       <c r="B83" t="s">
         <v>21</v>
       </c>
@@ -1569,8 +2886,24 @@
       <c r="D83">
         <v>535</v>
       </c>
-    </row>
-    <row r="84" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F83">
+        <f t="shared" si="7"/>
+        <v>509.52</v>
+      </c>
+      <c r="H83">
+        <f t="shared" si="4"/>
+        <v>509.52380952380952</v>
+      </c>
+      <c r="I83">
+        <f t="shared" si="5"/>
+        <v>25.480000000000018</v>
+      </c>
+      <c r="J83" s="1">
+        <f t="shared" si="6"/>
+        <v>535.00380952380954</v>
+      </c>
+    </row>
+    <row r="84" spans="2:10">
       <c r="B84" t="s">
         <v>5</v>
       </c>
@@ -1580,8 +2913,24 @@
       <c r="D84">
         <v>295</v>
       </c>
-    </row>
-    <row r="85" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F84">
+        <f t="shared" si="7"/>
+        <v>280.95</v>
+      </c>
+      <c r="H84">
+        <f t="shared" si="4"/>
+        <v>280.95238095238096</v>
+      </c>
+      <c r="I84">
+        <f t="shared" si="5"/>
+        <v>14.050000000000011</v>
+      </c>
+      <c r="J84" s="1">
+        <f t="shared" si="6"/>
+        <v>295.00238095238097</v>
+      </c>
+    </row>
+    <row r="85" spans="2:10">
       <c r="B85" t="s">
         <v>32</v>
       </c>
@@ -1591,8 +2940,24 @@
       <c r="D85">
         <v>340</v>
       </c>
-    </row>
-    <row r="86" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F85">
+        <f t="shared" si="7"/>
+        <v>323.81</v>
+      </c>
+      <c r="H85">
+        <f t="shared" si="4"/>
+        <v>323.8095238095238</v>
+      </c>
+      <c r="I85">
+        <f t="shared" si="5"/>
+        <v>16.189999999999998</v>
+      </c>
+      <c r="J85" s="1">
+        <f t="shared" si="6"/>
+        <v>339.99952380952379</v>
+      </c>
+    </row>
+    <row r="86" spans="2:10">
       <c r="B86" t="s">
         <v>33</v>
       </c>
@@ -1602,8 +2967,24 @@
       <c r="D86">
         <v>375</v>
       </c>
-    </row>
-    <row r="87" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F86">
+        <f t="shared" si="7"/>
+        <v>357.14</v>
+      </c>
+      <c r="H86">
+        <f t="shared" si="4"/>
+        <v>357.14285714285711</v>
+      </c>
+      <c r="I86">
+        <f t="shared" si="5"/>
+        <v>17.860000000000014</v>
+      </c>
+      <c r="J86" s="1">
+        <f t="shared" si="6"/>
+        <v>375.00285714285712</v>
+      </c>
+    </row>
+    <row r="87" spans="2:10">
       <c r="B87" t="s">
         <v>33</v>
       </c>
@@ -1613,8 +2994,24 @@
       <c r="D87">
         <v>365</v>
       </c>
-    </row>
-    <row r="88" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F87">
+        <f t="shared" si="7"/>
+        <v>347.62</v>
+      </c>
+      <c r="H87">
+        <f t="shared" si="4"/>
+        <v>347.61904761904759</v>
+      </c>
+      <c r="I87">
+        <f t="shared" si="5"/>
+        <v>17.379999999999995</v>
+      </c>
+      <c r="J87" s="1">
+        <f t="shared" si="6"/>
+        <v>364.99904761904759</v>
+      </c>
+    </row>
+    <row r="88" spans="2:10">
       <c r="B88" t="s">
         <v>33</v>
       </c>
@@ -1624,8 +3021,24 @@
       <c r="D88">
         <v>545</v>
       </c>
-    </row>
-    <row r="89" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F88">
+        <f t="shared" si="7"/>
+        <v>519.04999999999995</v>
+      </c>
+      <c r="H88">
+        <f t="shared" si="4"/>
+        <v>519.04761904761904</v>
+      </c>
+      <c r="I88">
+        <f t="shared" si="5"/>
+        <v>25.950000000000045</v>
+      </c>
+      <c r="J88" s="1">
+        <f t="shared" si="6"/>
+        <v>544.99761904761908</v>
+      </c>
+    </row>
+    <row r="89" spans="2:10">
       <c r="B89" t="s">
         <v>34</v>
       </c>
@@ -1635,8 +3048,24 @@
       <c r="D89">
         <v>275</v>
       </c>
-    </row>
-    <row r="90" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F89">
+        <f t="shared" si="7"/>
+        <v>261.89999999999998</v>
+      </c>
+      <c r="H89">
+        <f t="shared" si="4"/>
+        <v>261.90476190476187</v>
+      </c>
+      <c r="I89">
+        <f t="shared" si="5"/>
+        <v>13.100000000000023</v>
+      </c>
+      <c r="J89" s="1">
+        <f t="shared" si="6"/>
+        <v>275.00476190476189</v>
+      </c>
+    </row>
+    <row r="90" spans="2:10">
       <c r="B90" t="s">
         <v>33</v>
       </c>
@@ -1646,8 +3075,24 @@
       <c r="D90">
         <v>375</v>
       </c>
-    </row>
-    <row r="91" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F90">
+        <f t="shared" si="7"/>
+        <v>357.14</v>
+      </c>
+      <c r="H90">
+        <f t="shared" si="4"/>
+        <v>357.14285714285711</v>
+      </c>
+      <c r="I90">
+        <f t="shared" si="5"/>
+        <v>17.860000000000014</v>
+      </c>
+      <c r="J90" s="1">
+        <f t="shared" si="6"/>
+        <v>375.00285714285712</v>
+      </c>
+    </row>
+    <row r="91" spans="2:10">
       <c r="B91" t="s">
         <v>16</v>
       </c>
@@ -1657,8 +3102,24 @@
       <c r="D91">
         <v>365</v>
       </c>
-    </row>
-    <row r="92" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F91">
+        <f t="shared" si="7"/>
+        <v>347.62</v>
+      </c>
+      <c r="H91">
+        <f t="shared" si="4"/>
+        <v>347.61904761904759</v>
+      </c>
+      <c r="I91">
+        <f t="shared" si="5"/>
+        <v>17.379999999999995</v>
+      </c>
+      <c r="J91" s="1">
+        <f t="shared" si="6"/>
+        <v>364.99904761904759</v>
+      </c>
+    </row>
+    <row r="92" spans="2:10">
       <c r="B92" t="s">
         <v>35</v>
       </c>
@@ -1668,8 +3129,24 @@
       <c r="D92">
         <v>350</v>
       </c>
-    </row>
-    <row r="93" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F92">
+        <f t="shared" si="7"/>
+        <v>333.33</v>
+      </c>
+      <c r="H92">
+        <f t="shared" si="4"/>
+        <v>333.33333333333331</v>
+      </c>
+      <c r="I92">
+        <f t="shared" si="5"/>
+        <v>16.670000000000016</v>
+      </c>
+      <c r="J92" s="1">
+        <f t="shared" si="6"/>
+        <v>350.00333333333333</v>
+      </c>
+    </row>
+    <row r="93" spans="2:10">
       <c r="B93" t="s">
         <v>36</v>
       </c>
@@ -1679,8 +3156,24 @@
       <c r="D93">
         <v>295</v>
       </c>
-    </row>
-    <row r="94" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F93">
+        <f t="shared" si="7"/>
+        <v>280.95</v>
+      </c>
+      <c r="H93">
+        <f t="shared" si="4"/>
+        <v>280.95238095238096</v>
+      </c>
+      <c r="I93">
+        <f t="shared" si="5"/>
+        <v>14.050000000000011</v>
+      </c>
+      <c r="J93" s="1">
+        <f t="shared" si="6"/>
+        <v>295.00238095238097</v>
+      </c>
+    </row>
+    <row r="94" spans="2:10">
       <c r="B94" t="s">
         <v>7</v>
       </c>
@@ -1690,8 +3183,24 @@
       <c r="D94">
         <v>395</v>
       </c>
-    </row>
-    <row r="95" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F94">
+        <f t="shared" si="7"/>
+        <v>376.19</v>
+      </c>
+      <c r="H94">
+        <f t="shared" si="4"/>
+        <v>376.19047619047615</v>
+      </c>
+      <c r="I94">
+        <f t="shared" si="5"/>
+        <v>18.810000000000002</v>
+      </c>
+      <c r="J94" s="1">
+        <f t="shared" si="6"/>
+        <v>395.00047619047615</v>
+      </c>
+    </row>
+    <row r="95" spans="2:10">
       <c r="B95" t="s">
         <v>11</v>
       </c>
@@ -1704,8 +3213,24 @@
       <c r="E95">
         <v>8</v>
       </c>
-    </row>
-    <row r="96" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F95">
+        <f t="shared" si="7"/>
+        <v>833.33</v>
+      </c>
+      <c r="H95">
+        <f t="shared" si="4"/>
+        <v>833.33333333333326</v>
+      </c>
+      <c r="I95">
+        <f t="shared" si="5"/>
+        <v>41.669999999999959</v>
+      </c>
+      <c r="J95" s="1">
+        <f t="shared" si="6"/>
+        <v>875.00333333333322</v>
+      </c>
+    </row>
+    <row r="96" spans="2:10">
       <c r="B96" t="s">
         <v>28</v>
       </c>
@@ -1715,8 +3240,24 @@
       <c r="D96">
         <v>675</v>
       </c>
-    </row>
-    <row r="97" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F96">
+        <f t="shared" si="7"/>
+        <v>642.86</v>
+      </c>
+      <c r="H96">
+        <f t="shared" si="4"/>
+        <v>642.85714285714278</v>
+      </c>
+      <c r="I96">
+        <f t="shared" si="5"/>
+        <v>32.139999999999986</v>
+      </c>
+      <c r="J96" s="1">
+        <f t="shared" si="6"/>
+        <v>674.99714285714276</v>
+      </c>
+    </row>
+    <row r="97" spans="2:10">
       <c r="B97" t="s">
         <v>15</v>
       </c>
@@ -1726,8 +3267,24 @@
       <c r="D97">
         <v>365</v>
       </c>
-    </row>
-    <row r="98" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F97">
+        <f t="shared" si="7"/>
+        <v>347.62</v>
+      </c>
+      <c r="H97">
+        <f t="shared" si="4"/>
+        <v>347.61904761904759</v>
+      </c>
+      <c r="I97">
+        <f t="shared" si="5"/>
+        <v>17.379999999999995</v>
+      </c>
+      <c r="J97" s="1">
+        <f t="shared" si="6"/>
+        <v>364.99904761904759</v>
+      </c>
+    </row>
+    <row r="98" spans="2:10">
       <c r="B98" t="s">
         <v>15</v>
       </c>
@@ -1737,8 +3294,24 @@
       <c r="D98">
         <v>275</v>
       </c>
-    </row>
-    <row r="99" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F98">
+        <f t="shared" si="7"/>
+        <v>261.89999999999998</v>
+      </c>
+      <c r="H98">
+        <f t="shared" si="4"/>
+        <v>261.90476190476187</v>
+      </c>
+      <c r="I98">
+        <f t="shared" si="5"/>
+        <v>13.100000000000023</v>
+      </c>
+      <c r="J98" s="1">
+        <f t="shared" si="6"/>
+        <v>275.00476190476189</v>
+      </c>
+    </row>
+    <row r="99" spans="2:10">
       <c r="B99" t="s">
         <v>15</v>
       </c>
@@ -1748,8 +3321,24 @@
       <c r="D99">
         <v>365</v>
       </c>
-    </row>
-    <row r="100" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F99">
+        <f t="shared" si="7"/>
+        <v>347.62</v>
+      </c>
+      <c r="H99">
+        <f t="shared" si="4"/>
+        <v>347.61904761904759</v>
+      </c>
+      <c r="I99">
+        <f t="shared" si="5"/>
+        <v>17.379999999999995</v>
+      </c>
+      <c r="J99" s="1">
+        <f t="shared" si="6"/>
+        <v>364.99904761904759</v>
+      </c>
+    </row>
+    <row r="100" spans="2:10">
       <c r="B100" t="s">
         <v>5</v>
       </c>
@@ -1759,8 +3348,24 @@
       <c r="D100">
         <v>265</v>
       </c>
-    </row>
-    <row r="101" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F100">
+        <f t="shared" si="7"/>
+        <v>252.38</v>
+      </c>
+      <c r="H100">
+        <f t="shared" si="4"/>
+        <v>252.38095238095238</v>
+      </c>
+      <c r="I100">
+        <f t="shared" si="5"/>
+        <v>12.620000000000005</v>
+      </c>
+      <c r="J100" s="1">
+        <f t="shared" si="6"/>
+        <v>265.00095238095241</v>
+      </c>
+    </row>
+    <row r="101" spans="2:10">
       <c r="B101" t="s">
         <v>6</v>
       </c>
@@ -1773,8 +3378,24 @@
       <c r="E101">
         <v>2</v>
       </c>
-    </row>
-    <row r="102" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F101">
+        <f t="shared" si="7"/>
+        <v>333.33</v>
+      </c>
+      <c r="H101">
+        <f t="shared" si="4"/>
+        <v>333.33333333333331</v>
+      </c>
+      <c r="I101">
+        <f t="shared" si="5"/>
+        <v>16.670000000000016</v>
+      </c>
+      <c r="J101" s="1">
+        <f t="shared" si="6"/>
+        <v>350.00333333333333</v>
+      </c>
+    </row>
+    <row r="102" spans="2:10">
       <c r="B102" t="s">
         <v>35</v>
       </c>
@@ -1784,8 +3405,24 @@
       <c r="D102">
         <v>545</v>
       </c>
-    </row>
-    <row r="103" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F102">
+        <f t="shared" si="7"/>
+        <v>519.04999999999995</v>
+      </c>
+      <c r="H102">
+        <f t="shared" si="4"/>
+        <v>519.04761904761904</v>
+      </c>
+      <c r="I102">
+        <f t="shared" si="5"/>
+        <v>25.950000000000045</v>
+      </c>
+      <c r="J102" s="1">
+        <f t="shared" si="6"/>
+        <v>544.99761904761908</v>
+      </c>
+    </row>
+    <row r="103" spans="2:10">
       <c r="B103" t="s">
         <v>37</v>
       </c>
@@ -1798,8 +3435,24 @@
       <c r="E103">
         <v>4</v>
       </c>
-    </row>
-    <row r="104" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F103">
+        <f t="shared" si="7"/>
+        <v>461.9</v>
+      </c>
+      <c r="H103">
+        <f t="shared" si="4"/>
+        <v>461.90476190476187</v>
+      </c>
+      <c r="I103">
+        <f t="shared" si="5"/>
+        <v>23.100000000000023</v>
+      </c>
+      <c r="J103" s="1">
+        <f t="shared" si="6"/>
+        <v>485.00476190476189</v>
+      </c>
+    </row>
+    <row r="104" spans="2:10">
       <c r="B104" t="s">
         <v>35</v>
       </c>
@@ -1809,8 +3462,24 @@
       <c r="D104">
         <v>545</v>
       </c>
-    </row>
-    <row r="105" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F104">
+        <f t="shared" si="7"/>
+        <v>519.04999999999995</v>
+      </c>
+      <c r="H104">
+        <f t="shared" si="4"/>
+        <v>519.04761904761904</v>
+      </c>
+      <c r="I104">
+        <f t="shared" si="5"/>
+        <v>25.950000000000045</v>
+      </c>
+      <c r="J104" s="1">
+        <f t="shared" si="6"/>
+        <v>544.99761904761908</v>
+      </c>
+    </row>
+    <row r="105" spans="2:10">
       <c r="B105" t="s">
         <v>15</v>
       </c>
@@ -1820,8 +3489,24 @@
       <c r="D105">
         <v>365</v>
       </c>
-    </row>
-    <row r="106" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F105">
+        <f t="shared" si="7"/>
+        <v>347.62</v>
+      </c>
+      <c r="H105">
+        <f t="shared" si="4"/>
+        <v>347.61904761904759</v>
+      </c>
+      <c r="I105">
+        <f t="shared" si="5"/>
+        <v>17.379999999999995</v>
+      </c>
+      <c r="J105" s="1">
+        <f t="shared" si="6"/>
+        <v>364.99904761904759</v>
+      </c>
+    </row>
+    <row r="106" spans="2:10">
       <c r="B106" t="s">
         <v>38</v>
       </c>
@@ -1831,8 +3516,24 @@
       <c r="D106">
         <v>485</v>
       </c>
-    </row>
-    <row r="107" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F106">
+        <f t="shared" si="7"/>
+        <v>461.9</v>
+      </c>
+      <c r="H106">
+        <f t="shared" si="4"/>
+        <v>461.90476190476187</v>
+      </c>
+      <c r="I106">
+        <f t="shared" si="5"/>
+        <v>23.100000000000023</v>
+      </c>
+      <c r="J106" s="1">
+        <f t="shared" si="6"/>
+        <v>485.00476190476189</v>
+      </c>
+    </row>
+    <row r="107" spans="2:10">
       <c r="B107" t="s">
         <v>5</v>
       </c>
@@ -1845,8 +3546,24 @@
       <c r="E107">
         <v>5</v>
       </c>
-    </row>
-    <row r="108" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F107">
+        <f t="shared" si="7"/>
+        <v>280.95</v>
+      </c>
+      <c r="H107">
+        <f t="shared" si="4"/>
+        <v>280.95238095238096</v>
+      </c>
+      <c r="I107">
+        <f t="shared" si="5"/>
+        <v>14.050000000000011</v>
+      </c>
+      <c r="J107" s="1">
+        <f t="shared" si="6"/>
+        <v>295.00238095238097</v>
+      </c>
+    </row>
+    <row r="108" spans="2:10">
       <c r="B108" t="s">
         <v>39</v>
       </c>
@@ -1856,8 +3573,24 @@
       <c r="D108">
         <v>375</v>
       </c>
-    </row>
-    <row r="109" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F108">
+        <f t="shared" si="7"/>
+        <v>357.14</v>
+      </c>
+      <c r="H108">
+        <f t="shared" si="4"/>
+        <v>357.14285714285711</v>
+      </c>
+      <c r="I108">
+        <f t="shared" si="5"/>
+        <v>17.860000000000014</v>
+      </c>
+      <c r="J108" s="1">
+        <f t="shared" si="6"/>
+        <v>375.00285714285712</v>
+      </c>
+    </row>
+    <row r="109" spans="2:10">
       <c r="B109" t="s">
         <v>5</v>
       </c>
@@ -1870,8 +3603,24 @@
       <c r="E109">
         <v>4</v>
       </c>
-    </row>
-    <row r="110" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F109">
+        <f t="shared" si="7"/>
+        <v>280.95</v>
+      </c>
+      <c r="H109">
+        <f>D109/1.05</f>
+        <v>280.95238095238096</v>
+      </c>
+      <c r="I109">
+        <f>D109-F109</f>
+        <v>14.050000000000011</v>
+      </c>
+      <c r="J109" s="1">
+        <f>SUM(H109:I109)</f>
+        <v>295.00238095238097</v>
+      </c>
+    </row>
+    <row r="110" spans="2:10">
       <c r="B110" t="s">
         <v>35</v>
       </c>
@@ -1880,6 +3629,22 @@
       </c>
       <c r="D110">
         <v>545</v>
+      </c>
+      <c r="F110">
+        <f>ROUND(IF(D110&gt;2500, D110/1.18, D110/1.05),2)</f>
+        <v>519.04999999999995</v>
+      </c>
+      <c r="H110">
+        <f>D110/1.05</f>
+        <v>519.04761904761904</v>
+      </c>
+      <c r="I110">
+        <f>D110-F110</f>
+        <v>25.950000000000045</v>
+      </c>
+      <c r="J110" s="1">
+        <f>SUM(H110:I110)</f>
+        <v>544.99761904761908</v>
       </c>
     </row>
   </sheetData>
@@ -1888,17 +3653,19 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8453A547-5B77-4BE4-9434-BC855747F9A7}">
-  <dimension ref="A1:E104"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:J104"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="7" customWidth="1"/>
     <col min="2" max="2" width="16.7109375" customWidth="1"/>
     <col min="3" max="3" width="11.85546875" customWidth="1"/>
     <col min="4" max="4" width="11" customWidth="1"/>
+    <col min="6" max="6" width="24" customWidth="1"/>
+    <col min="10" max="10" width="5.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1914,8 +3681,20 @@
       <c r="E1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F1" t="s">
+        <v>82</v>
+      </c>
+      <c r="H1" t="s">
+        <v>83</v>
+      </c>
+      <c r="I1" t="s">
+        <v>84</v>
+      </c>
+      <c r="J1" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10">
       <c r="B2" t="s">
         <v>40</v>
       </c>
@@ -1925,8 +3704,24 @@
       <c r="D2">
         <v>485</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F2">
+        <f>ROUND(IF(D2&gt;2500, D2/1.18, D2/1.05),2)</f>
+        <v>461.9</v>
+      </c>
+      <c r="H2">
+        <f>D2/1.05</f>
+        <v>461.90476190476187</v>
+      </c>
+      <c r="I2">
+        <f>D2-F2</f>
+        <v>23.100000000000023</v>
+      </c>
+      <c r="J2" s="1">
+        <f>SUM(H2:I2)</f>
+        <v>485.00476190476189</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
       <c r="B3" t="s">
         <v>41</v>
       </c>
@@ -1939,8 +3734,24 @@
       <c r="E3">
         <v>6</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F3">
+        <f t="shared" ref="F3:F66" si="0">ROUND(IF(D3&gt;2500, D3/1.18, D3/1.05),2)</f>
+        <v>947.62</v>
+      </c>
+      <c r="H3">
+        <f t="shared" ref="H3:H66" si="1">D3/1.05</f>
+        <v>947.61904761904759</v>
+      </c>
+      <c r="I3">
+        <f t="shared" ref="I3:I66" si="2">D3-F3</f>
+        <v>47.379999999999995</v>
+      </c>
+      <c r="J3" s="1">
+        <f t="shared" ref="J3:J66" si="3">SUM(H3:I3)</f>
+        <v>994.99904761904759</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
       <c r="B4" t="s">
         <v>40</v>
       </c>
@@ -1950,8 +3761,24 @@
       <c r="D4">
         <v>485</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F4">
+        <f t="shared" si="0"/>
+        <v>461.9</v>
+      </c>
+      <c r="H4">
+        <f t="shared" si="1"/>
+        <v>461.90476190476187</v>
+      </c>
+      <c r="I4">
+        <f t="shared" si="2"/>
+        <v>23.100000000000023</v>
+      </c>
+      <c r="J4" s="1">
+        <f t="shared" si="3"/>
+        <v>485.00476190476189</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
       <c r="B5" t="s">
         <v>40</v>
       </c>
@@ -1961,8 +3788,24 @@
       <c r="D5">
         <v>625</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F5">
+        <f t="shared" si="0"/>
+        <v>595.24</v>
+      </c>
+      <c r="H5">
+        <f t="shared" si="1"/>
+        <v>595.23809523809518</v>
+      </c>
+      <c r="I5">
+        <f t="shared" si="2"/>
+        <v>29.759999999999991</v>
+      </c>
+      <c r="J5" s="1">
+        <f t="shared" si="3"/>
+        <v>624.99809523809517</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
       <c r="B6" t="s">
         <v>40</v>
       </c>
@@ -1972,8 +3815,24 @@
       <c r="D6">
         <v>485</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F6">
+        <f t="shared" si="0"/>
+        <v>461.9</v>
+      </c>
+      <c r="H6">
+        <f t="shared" si="1"/>
+        <v>461.90476190476187</v>
+      </c>
+      <c r="I6">
+        <f t="shared" si="2"/>
+        <v>23.100000000000023</v>
+      </c>
+      <c r="J6" s="1">
+        <f t="shared" si="3"/>
+        <v>485.00476190476189</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
       <c r="B7" t="s">
         <v>40</v>
       </c>
@@ -1983,8 +3842,24 @@
       <c r="D7">
         <v>995</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F7">
+        <f t="shared" si="0"/>
+        <v>947.62</v>
+      </c>
+      <c r="H7">
+        <f t="shared" si="1"/>
+        <v>947.61904761904759</v>
+      </c>
+      <c r="I7">
+        <f t="shared" si="2"/>
+        <v>47.379999999999995</v>
+      </c>
+      <c r="J7" s="1">
+        <f t="shared" si="3"/>
+        <v>994.99904761904759</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10">
       <c r="B8" t="s">
         <v>40</v>
       </c>
@@ -1994,8 +3869,24 @@
       <c r="D8">
         <v>485</v>
       </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F8">
+        <f t="shared" si="0"/>
+        <v>461.9</v>
+      </c>
+      <c r="H8">
+        <f t="shared" si="1"/>
+        <v>461.90476190476187</v>
+      </c>
+      <c r="I8">
+        <f t="shared" si="2"/>
+        <v>23.100000000000023</v>
+      </c>
+      <c r="J8" s="1">
+        <f t="shared" si="3"/>
+        <v>485.00476190476189</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
       <c r="B9" t="s">
         <v>40</v>
       </c>
@@ -2005,8 +3896,24 @@
       <c r="D9">
         <v>485</v>
       </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F9">
+        <f t="shared" si="0"/>
+        <v>461.9</v>
+      </c>
+      <c r="H9">
+        <f t="shared" si="1"/>
+        <v>461.90476190476187</v>
+      </c>
+      <c r="I9">
+        <f t="shared" si="2"/>
+        <v>23.100000000000023</v>
+      </c>
+      <c r="J9" s="1">
+        <f t="shared" si="3"/>
+        <v>485.00476190476189</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10">
       <c r="B10" t="s">
         <v>40</v>
       </c>
@@ -2016,8 +3923,24 @@
       <c r="D10">
         <v>995</v>
       </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F10">
+        <f t="shared" si="0"/>
+        <v>947.62</v>
+      </c>
+      <c r="H10">
+        <f t="shared" si="1"/>
+        <v>947.61904761904759</v>
+      </c>
+      <c r="I10">
+        <f t="shared" si="2"/>
+        <v>47.379999999999995</v>
+      </c>
+      <c r="J10" s="1">
+        <f t="shared" si="3"/>
+        <v>994.99904761904759</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10">
       <c r="B11" t="s">
         <v>40</v>
       </c>
@@ -2027,8 +3950,24 @@
       <c r="D11">
         <v>1050</v>
       </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F11">
+        <f t="shared" si="0"/>
+        <v>1000</v>
+      </c>
+      <c r="H11">
+        <f t="shared" si="1"/>
+        <v>1000</v>
+      </c>
+      <c r="I11">
+        <f t="shared" si="2"/>
+        <v>50</v>
+      </c>
+      <c r="J11" s="1">
+        <f t="shared" si="3"/>
+        <v>1050</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10">
       <c r="B12" t="s">
         <v>42</v>
       </c>
@@ -2038,8 +3977,24 @@
       <c r="D12">
         <v>1825</v>
       </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F12">
+        <f t="shared" si="0"/>
+        <v>1738.1</v>
+      </c>
+      <c r="H12">
+        <f t="shared" si="1"/>
+        <v>1738.0952380952381</v>
+      </c>
+      <c r="I12">
+        <f t="shared" si="2"/>
+        <v>86.900000000000091</v>
+      </c>
+      <c r="J12" s="1">
+        <f t="shared" si="3"/>
+        <v>1824.9952380952382</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10">
       <c r="B13" t="s">
         <v>40</v>
       </c>
@@ -2049,8 +4004,24 @@
       <c r="D13">
         <v>825</v>
       </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F13">
+        <f t="shared" si="0"/>
+        <v>785.71</v>
+      </c>
+      <c r="H13">
+        <f t="shared" si="1"/>
+        <v>785.71428571428567</v>
+      </c>
+      <c r="I13">
+        <f t="shared" si="2"/>
+        <v>39.289999999999964</v>
+      </c>
+      <c r="J13" s="1">
+        <f t="shared" si="3"/>
+        <v>825.00428571428563</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10">
       <c r="B14" t="s">
         <v>40</v>
       </c>
@@ -2060,8 +4031,24 @@
       <c r="D14">
         <v>485</v>
       </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F14">
+        <f t="shared" si="0"/>
+        <v>461.9</v>
+      </c>
+      <c r="H14">
+        <f t="shared" si="1"/>
+        <v>461.90476190476187</v>
+      </c>
+      <c r="I14">
+        <f t="shared" si="2"/>
+        <v>23.100000000000023</v>
+      </c>
+      <c r="J14" s="1">
+        <f t="shared" si="3"/>
+        <v>485.00476190476189</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10">
       <c r="B15" t="s">
         <v>40</v>
       </c>
@@ -2071,8 +4058,24 @@
       <c r="D15">
         <v>485</v>
       </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F15">
+        <f t="shared" si="0"/>
+        <v>461.9</v>
+      </c>
+      <c r="H15">
+        <f t="shared" si="1"/>
+        <v>461.90476190476187</v>
+      </c>
+      <c r="I15">
+        <f t="shared" si="2"/>
+        <v>23.100000000000023</v>
+      </c>
+      <c r="J15" s="1">
+        <f t="shared" si="3"/>
+        <v>485.00476190476189</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10">
       <c r="B16" t="s">
         <v>40</v>
       </c>
@@ -2082,8 +4085,24 @@
       <c r="D16">
         <v>995</v>
       </c>
-    </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F16">
+        <f t="shared" si="0"/>
+        <v>947.62</v>
+      </c>
+      <c r="H16">
+        <f t="shared" si="1"/>
+        <v>947.61904761904759</v>
+      </c>
+      <c r="I16">
+        <f t="shared" si="2"/>
+        <v>47.379999999999995</v>
+      </c>
+      <c r="J16" s="1">
+        <f t="shared" si="3"/>
+        <v>994.99904761904759</v>
+      </c>
+    </row>
+    <row r="17" spans="2:10">
       <c r="B17" t="s">
         <v>40</v>
       </c>
@@ -2093,8 +4112,24 @@
       <c r="D17">
         <v>485</v>
       </c>
-    </row>
-    <row r="18" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F17">
+        <f t="shared" si="0"/>
+        <v>461.9</v>
+      </c>
+      <c r="H17">
+        <f t="shared" si="1"/>
+        <v>461.90476190476187</v>
+      </c>
+      <c r="I17">
+        <f t="shared" si="2"/>
+        <v>23.100000000000023</v>
+      </c>
+      <c r="J17" s="1">
+        <f t="shared" si="3"/>
+        <v>485.00476190476189</v>
+      </c>
+    </row>
+    <row r="18" spans="2:10">
       <c r="B18" t="s">
         <v>40</v>
       </c>
@@ -2107,8 +4142,24 @@
       <c r="E18">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F18">
+        <f t="shared" si="0"/>
+        <v>947.62</v>
+      </c>
+      <c r="H18">
+        <f t="shared" si="1"/>
+        <v>947.61904761904759</v>
+      </c>
+      <c r="I18">
+        <f t="shared" si="2"/>
+        <v>47.379999999999995</v>
+      </c>
+      <c r="J18" s="1">
+        <f t="shared" si="3"/>
+        <v>994.99904761904759</v>
+      </c>
+    </row>
+    <row r="19" spans="2:10">
       <c r="B19" t="s">
         <v>43</v>
       </c>
@@ -2118,8 +4169,24 @@
       <c r="D19">
         <v>1450</v>
       </c>
-    </row>
-    <row r="20" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F19">
+        <f t="shared" si="0"/>
+        <v>1380.95</v>
+      </c>
+      <c r="H19">
+        <f t="shared" si="1"/>
+        <v>1380.952380952381</v>
+      </c>
+      <c r="I19">
+        <f t="shared" si="2"/>
+        <v>69.049999999999955</v>
+      </c>
+      <c r="J19" s="1">
+        <f t="shared" si="3"/>
+        <v>1450.0023809523809</v>
+      </c>
+    </row>
+    <row r="20" spans="2:10">
       <c r="B20" t="s">
         <v>43</v>
       </c>
@@ -2129,8 +4196,24 @@
       <c r="D20">
         <v>1450</v>
       </c>
-    </row>
-    <row r="21" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F20">
+        <f t="shared" si="0"/>
+        <v>1380.95</v>
+      </c>
+      <c r="H20">
+        <f t="shared" si="1"/>
+        <v>1380.952380952381</v>
+      </c>
+      <c r="I20">
+        <f t="shared" si="2"/>
+        <v>69.049999999999955</v>
+      </c>
+      <c r="J20" s="1">
+        <f t="shared" si="3"/>
+        <v>1450.0023809523809</v>
+      </c>
+    </row>
+    <row r="21" spans="2:10">
       <c r="B21" t="s">
         <v>44</v>
       </c>
@@ -2140,8 +4223,24 @@
       <c r="D21">
         <v>1995</v>
       </c>
-    </row>
-    <row r="22" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F21">
+        <f t="shared" si="0"/>
+        <v>1900</v>
+      </c>
+      <c r="H21">
+        <f t="shared" si="1"/>
+        <v>1900</v>
+      </c>
+      <c r="I21">
+        <f t="shared" si="2"/>
+        <v>95</v>
+      </c>
+      <c r="J21" s="1">
+        <f t="shared" si="3"/>
+        <v>1995</v>
+      </c>
+    </row>
+    <row r="22" spans="2:10">
       <c r="B22" t="s">
         <v>45</v>
       </c>
@@ -2151,8 +4250,24 @@
       <c r="D22">
         <v>365</v>
       </c>
-    </row>
-    <row r="23" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F22">
+        <f t="shared" si="0"/>
+        <v>347.62</v>
+      </c>
+      <c r="H22">
+        <f t="shared" si="1"/>
+        <v>347.61904761904759</v>
+      </c>
+      <c r="I22">
+        <f t="shared" si="2"/>
+        <v>17.379999999999995</v>
+      </c>
+      <c r="J22" s="1">
+        <f t="shared" si="3"/>
+        <v>364.99904761904759</v>
+      </c>
+    </row>
+    <row r="23" spans="2:10">
       <c r="B23" t="s">
         <v>46</v>
       </c>
@@ -2162,8 +4277,24 @@
       <c r="D23">
         <v>425</v>
       </c>
-    </row>
-    <row r="24" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F23">
+        <f t="shared" si="0"/>
+        <v>404.76</v>
+      </c>
+      <c r="H23">
+        <f t="shared" si="1"/>
+        <v>404.76190476190476</v>
+      </c>
+      <c r="I23">
+        <f t="shared" si="2"/>
+        <v>20.240000000000009</v>
+      </c>
+      <c r="J23" s="1">
+        <f t="shared" si="3"/>
+        <v>425.00190476190477</v>
+      </c>
+    </row>
+    <row r="24" spans="2:10">
       <c r="B24" t="s">
         <v>47</v>
       </c>
@@ -2173,8 +4304,24 @@
       <c r="D24">
         <v>675</v>
       </c>
-    </row>
-    <row r="25" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F24">
+        <f t="shared" si="0"/>
+        <v>642.86</v>
+      </c>
+      <c r="H24">
+        <f t="shared" si="1"/>
+        <v>642.85714285714278</v>
+      </c>
+      <c r="I24">
+        <f t="shared" si="2"/>
+        <v>32.139999999999986</v>
+      </c>
+      <c r="J24" s="1">
+        <f t="shared" si="3"/>
+        <v>674.99714285714276</v>
+      </c>
+    </row>
+    <row r="25" spans="2:10">
       <c r="B25" t="s">
         <v>48</v>
       </c>
@@ -2187,8 +4334,24 @@
       <c r="E25">
         <v>2</v>
       </c>
-    </row>
-    <row r="26" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F25">
+        <f t="shared" si="0"/>
+        <v>338.1</v>
+      </c>
+      <c r="H25">
+        <f t="shared" si="1"/>
+        <v>338.09523809523807</v>
+      </c>
+      <c r="I25">
+        <f t="shared" si="2"/>
+        <v>16.899999999999977</v>
+      </c>
+      <c r="J25" s="1">
+        <f t="shared" si="3"/>
+        <v>354.99523809523805</v>
+      </c>
+    </row>
+    <row r="26" spans="2:10">
       <c r="B26" t="s">
         <v>49</v>
       </c>
@@ -2198,8 +4361,24 @@
       <c r="D26">
         <v>535</v>
       </c>
-    </row>
-    <row r="27" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F26">
+        <f t="shared" si="0"/>
+        <v>509.52</v>
+      </c>
+      <c r="H26">
+        <f t="shared" si="1"/>
+        <v>509.52380952380952</v>
+      </c>
+      <c r="I26">
+        <f t="shared" si="2"/>
+        <v>25.480000000000018</v>
+      </c>
+      <c r="J26" s="1">
+        <f t="shared" si="3"/>
+        <v>535.00380952380954</v>
+      </c>
+    </row>
+    <row r="27" spans="2:10">
       <c r="B27" t="s">
         <v>46</v>
       </c>
@@ -2212,8 +4391,24 @@
       <c r="E27">
         <v>2</v>
       </c>
-    </row>
-    <row r="28" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F27">
+        <f t="shared" si="0"/>
+        <v>404.76</v>
+      </c>
+      <c r="H27">
+        <f t="shared" si="1"/>
+        <v>404.76190476190476</v>
+      </c>
+      <c r="I27">
+        <f t="shared" si="2"/>
+        <v>20.240000000000009</v>
+      </c>
+      <c r="J27" s="1">
+        <f t="shared" si="3"/>
+        <v>425.00190476190477</v>
+      </c>
+    </row>
+    <row r="28" spans="2:10">
       <c r="B28" t="s">
         <v>48</v>
       </c>
@@ -2223,8 +4418,24 @@
       <c r="D28">
         <v>545</v>
       </c>
-    </row>
-    <row r="29" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F28">
+        <f t="shared" si="0"/>
+        <v>519.04999999999995</v>
+      </c>
+      <c r="H28">
+        <f t="shared" si="1"/>
+        <v>519.04761904761904</v>
+      </c>
+      <c r="I28">
+        <f t="shared" si="2"/>
+        <v>25.950000000000045</v>
+      </c>
+      <c r="J28" s="1">
+        <f t="shared" si="3"/>
+        <v>544.99761904761908</v>
+      </c>
+    </row>
+    <row r="29" spans="2:10">
       <c r="B29" t="s">
         <v>48</v>
       </c>
@@ -2234,8 +4445,24 @@
       <c r="D29">
         <v>365</v>
       </c>
-    </row>
-    <row r="30" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F29">
+        <f t="shared" si="0"/>
+        <v>347.62</v>
+      </c>
+      <c r="H29">
+        <f t="shared" si="1"/>
+        <v>347.61904761904759</v>
+      </c>
+      <c r="I29">
+        <f t="shared" si="2"/>
+        <v>17.379999999999995</v>
+      </c>
+      <c r="J29" s="1">
+        <f t="shared" si="3"/>
+        <v>364.99904761904759</v>
+      </c>
+    </row>
+    <row r="30" spans="2:10">
       <c r="B30" t="s">
         <v>50</v>
       </c>
@@ -2245,8 +4472,24 @@
       <c r="D30">
         <v>875</v>
       </c>
-    </row>
-    <row r="31" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F30">
+        <f t="shared" si="0"/>
+        <v>833.33</v>
+      </c>
+      <c r="H30">
+        <f t="shared" si="1"/>
+        <v>833.33333333333326</v>
+      </c>
+      <c r="I30">
+        <f t="shared" si="2"/>
+        <v>41.669999999999959</v>
+      </c>
+      <c r="J30" s="1">
+        <f t="shared" si="3"/>
+        <v>875.00333333333322</v>
+      </c>
+    </row>
+    <row r="31" spans="2:10">
       <c r="B31" t="s">
         <v>51</v>
       </c>
@@ -2256,8 +4499,24 @@
       <c r="D31">
         <v>295</v>
       </c>
-    </row>
-    <row r="32" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F31">
+        <f t="shared" si="0"/>
+        <v>280.95</v>
+      </c>
+      <c r="H31">
+        <f t="shared" si="1"/>
+        <v>280.95238095238096</v>
+      </c>
+      <c r="I31">
+        <f t="shared" si="2"/>
+        <v>14.050000000000011</v>
+      </c>
+      <c r="J31" s="1">
+        <f t="shared" si="3"/>
+        <v>295.00238095238097</v>
+      </c>
+    </row>
+    <row r="32" spans="2:10">
       <c r="B32" t="s">
         <v>48</v>
       </c>
@@ -2267,8 +4526,24 @@
       <c r="D32">
         <v>545</v>
       </c>
-    </row>
-    <row r="33" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F32">
+        <f t="shared" si="0"/>
+        <v>519.04999999999995</v>
+      </c>
+      <c r="H32">
+        <f t="shared" si="1"/>
+        <v>519.04761904761904</v>
+      </c>
+      <c r="I32">
+        <f t="shared" si="2"/>
+        <v>25.950000000000045</v>
+      </c>
+      <c r="J32" s="1">
+        <f t="shared" si="3"/>
+        <v>544.99761904761908</v>
+      </c>
+    </row>
+    <row r="33" spans="2:10">
       <c r="B33" t="s">
         <v>52</v>
       </c>
@@ -2278,8 +4553,24 @@
       <c r="D33">
         <v>375</v>
       </c>
-    </row>
-    <row r="34" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F33">
+        <f t="shared" si="0"/>
+        <v>357.14</v>
+      </c>
+      <c r="H33">
+        <f t="shared" si="1"/>
+        <v>357.14285714285711</v>
+      </c>
+      <c r="I33">
+        <f t="shared" si="2"/>
+        <v>17.860000000000014</v>
+      </c>
+      <c r="J33" s="1">
+        <f t="shared" si="3"/>
+        <v>375.00285714285712</v>
+      </c>
+    </row>
+    <row r="34" spans="2:10">
       <c r="B34" t="s">
         <v>53</v>
       </c>
@@ -2289,8 +4580,24 @@
       <c r="D34">
         <v>395</v>
       </c>
-    </row>
-    <row r="35" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F34">
+        <f t="shared" si="0"/>
+        <v>376.19</v>
+      </c>
+      <c r="H34">
+        <f t="shared" si="1"/>
+        <v>376.19047619047615</v>
+      </c>
+      <c r="I34">
+        <f t="shared" si="2"/>
+        <v>18.810000000000002</v>
+      </c>
+      <c r="J34" s="1">
+        <f t="shared" si="3"/>
+        <v>395.00047619047615</v>
+      </c>
+    </row>
+    <row r="35" spans="2:10">
       <c r="B35" t="s">
         <v>49</v>
       </c>
@@ -2300,8 +4607,24 @@
       <c r="D35">
         <v>395</v>
       </c>
-    </row>
-    <row r="36" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F35">
+        <f t="shared" si="0"/>
+        <v>376.19</v>
+      </c>
+      <c r="H35">
+        <f t="shared" si="1"/>
+        <v>376.19047619047615</v>
+      </c>
+      <c r="I35">
+        <f t="shared" si="2"/>
+        <v>18.810000000000002</v>
+      </c>
+      <c r="J35" s="1">
+        <f t="shared" si="3"/>
+        <v>395.00047619047615</v>
+      </c>
+    </row>
+    <row r="36" spans="2:10">
       <c r="B36" t="s">
         <v>46</v>
       </c>
@@ -2311,8 +4634,24 @@
       <c r="D36">
         <v>575</v>
       </c>
-    </row>
-    <row r="37" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F36">
+        <f t="shared" si="0"/>
+        <v>547.62</v>
+      </c>
+      <c r="H36">
+        <f t="shared" si="1"/>
+        <v>547.61904761904759</v>
+      </c>
+      <c r="I36">
+        <f t="shared" si="2"/>
+        <v>27.379999999999995</v>
+      </c>
+      <c r="J36" s="1">
+        <f t="shared" si="3"/>
+        <v>574.99904761904759</v>
+      </c>
+    </row>
+    <row r="37" spans="2:10">
       <c r="B37" t="s">
         <v>48</v>
       </c>
@@ -2322,8 +4661,24 @@
       <c r="D37">
         <v>545</v>
       </c>
-    </row>
-    <row r="38" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F37">
+        <f t="shared" si="0"/>
+        <v>519.04999999999995</v>
+      </c>
+      <c r="H37">
+        <f t="shared" si="1"/>
+        <v>519.04761904761904</v>
+      </c>
+      <c r="I37">
+        <f t="shared" si="2"/>
+        <v>25.950000000000045</v>
+      </c>
+      <c r="J37" s="1">
+        <f t="shared" si="3"/>
+        <v>544.99761904761908</v>
+      </c>
+    </row>
+    <row r="38" spans="2:10">
       <c r="B38" t="s">
         <v>46</v>
       </c>
@@ -2333,8 +4688,24 @@
       <c r="D38">
         <v>350</v>
       </c>
-    </row>
-    <row r="39" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F38">
+        <f t="shared" si="0"/>
+        <v>333.33</v>
+      </c>
+      <c r="H38">
+        <f t="shared" si="1"/>
+        <v>333.33333333333331</v>
+      </c>
+      <c r="I38">
+        <f t="shared" si="2"/>
+        <v>16.670000000000016</v>
+      </c>
+      <c r="J38" s="1">
+        <f t="shared" si="3"/>
+        <v>350.00333333333333</v>
+      </c>
+    </row>
+    <row r="39" spans="2:10">
       <c r="B39" t="s">
         <v>54</v>
       </c>
@@ -2344,8 +4715,24 @@
       <c r="D39">
         <v>425</v>
       </c>
-    </row>
-    <row r="40" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F39">
+        <f t="shared" si="0"/>
+        <v>404.76</v>
+      </c>
+      <c r="H39">
+        <f t="shared" si="1"/>
+        <v>404.76190476190476</v>
+      </c>
+      <c r="I39">
+        <f t="shared" si="2"/>
+        <v>20.240000000000009</v>
+      </c>
+      <c r="J39" s="1">
+        <f t="shared" si="3"/>
+        <v>425.00190476190477</v>
+      </c>
+    </row>
+    <row r="40" spans="2:10">
       <c r="B40" t="s">
         <v>51</v>
       </c>
@@ -2355,8 +4742,24 @@
       <c r="D40">
         <v>275</v>
       </c>
-    </row>
-    <row r="41" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F40">
+        <f t="shared" si="0"/>
+        <v>261.89999999999998</v>
+      </c>
+      <c r="H40">
+        <f t="shared" si="1"/>
+        <v>261.90476190476187</v>
+      </c>
+      <c r="I40">
+        <f t="shared" si="2"/>
+        <v>13.100000000000023</v>
+      </c>
+      <c r="J40" s="1">
+        <f t="shared" si="3"/>
+        <v>275.00476190476189</v>
+      </c>
+    </row>
+    <row r="41" spans="2:10">
       <c r="B41" t="s">
         <v>54</v>
       </c>
@@ -2366,8 +4769,24 @@
       <c r="D41">
         <v>425</v>
       </c>
-    </row>
-    <row r="42" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F41">
+        <f t="shared" si="0"/>
+        <v>404.76</v>
+      </c>
+      <c r="H41">
+        <f t="shared" si="1"/>
+        <v>404.76190476190476</v>
+      </c>
+      <c r="I41">
+        <f t="shared" si="2"/>
+        <v>20.240000000000009</v>
+      </c>
+      <c r="J41" s="1">
+        <f t="shared" si="3"/>
+        <v>425.00190476190477</v>
+      </c>
+    </row>
+    <row r="42" spans="2:10">
       <c r="B42" t="s">
         <v>55</v>
       </c>
@@ -2377,8 +4796,24 @@
       <c r="D42">
         <v>315</v>
       </c>
-    </row>
-    <row r="43" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F42">
+        <f t="shared" si="0"/>
+        <v>300</v>
+      </c>
+      <c r="H42">
+        <f t="shared" si="1"/>
+        <v>300</v>
+      </c>
+      <c r="I42">
+        <f t="shared" si="2"/>
+        <v>15</v>
+      </c>
+      <c r="J42" s="1">
+        <f t="shared" si="3"/>
+        <v>315</v>
+      </c>
+    </row>
+    <row r="43" spans="2:10">
       <c r="B43" t="s">
         <v>54</v>
       </c>
@@ -2391,8 +4826,24 @@
       <c r="E43">
         <v>12</v>
       </c>
-    </row>
-    <row r="44" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F43">
+        <f t="shared" si="0"/>
+        <v>404.76</v>
+      </c>
+      <c r="H43">
+        <f t="shared" si="1"/>
+        <v>404.76190476190476</v>
+      </c>
+      <c r="I43">
+        <f t="shared" si="2"/>
+        <v>20.240000000000009</v>
+      </c>
+      <c r="J43" s="1">
+        <f t="shared" si="3"/>
+        <v>425.00190476190477</v>
+      </c>
+    </row>
+    <row r="44" spans="2:10">
       <c r="B44" t="s">
         <v>56</v>
       </c>
@@ -2402,8 +4853,24 @@
       <c r="D44">
         <v>350</v>
       </c>
-    </row>
-    <row r="45" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F44">
+        <f t="shared" si="0"/>
+        <v>333.33</v>
+      </c>
+      <c r="H44">
+        <f t="shared" si="1"/>
+        <v>333.33333333333331</v>
+      </c>
+      <c r="I44">
+        <f t="shared" si="2"/>
+        <v>16.670000000000016</v>
+      </c>
+      <c r="J44" s="1">
+        <f t="shared" si="3"/>
+        <v>350.00333333333333</v>
+      </c>
+    </row>
+    <row r="45" spans="2:10">
       <c r="B45" t="s">
         <v>51</v>
       </c>
@@ -2413,8 +4880,24 @@
       <c r="D45">
         <v>275</v>
       </c>
-    </row>
-    <row r="46" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F45">
+        <f t="shared" si="0"/>
+        <v>261.89999999999998</v>
+      </c>
+      <c r="H45">
+        <f t="shared" si="1"/>
+        <v>261.90476190476187</v>
+      </c>
+      <c r="I45">
+        <f t="shared" si="2"/>
+        <v>13.100000000000023</v>
+      </c>
+      <c r="J45" s="1">
+        <f t="shared" si="3"/>
+        <v>275.00476190476189</v>
+      </c>
+    </row>
+    <row r="46" spans="2:10">
       <c r="B46" t="s">
         <v>54</v>
       </c>
@@ -2427,8 +4910,24 @@
       <c r="E46">
         <v>30</v>
       </c>
-    </row>
-    <row r="47" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F46">
+        <f t="shared" si="0"/>
+        <v>404.76</v>
+      </c>
+      <c r="H46">
+        <f t="shared" si="1"/>
+        <v>404.76190476190476</v>
+      </c>
+      <c r="I46">
+        <f t="shared" si="2"/>
+        <v>20.240000000000009</v>
+      </c>
+      <c r="J46" s="1">
+        <f t="shared" si="3"/>
+        <v>425.00190476190477</v>
+      </c>
+    </row>
+    <row r="47" spans="2:10">
       <c r="B47" t="s">
         <v>57</v>
       </c>
@@ -2441,8 +4940,24 @@
       <c r="E47">
         <v>7</v>
       </c>
-    </row>
-    <row r="48" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F47">
+        <f t="shared" si="0"/>
+        <v>333.33</v>
+      </c>
+      <c r="H47">
+        <f t="shared" si="1"/>
+        <v>333.33333333333331</v>
+      </c>
+      <c r="I47">
+        <f t="shared" si="2"/>
+        <v>16.670000000000016</v>
+      </c>
+      <c r="J47" s="1">
+        <f t="shared" si="3"/>
+        <v>350.00333333333333</v>
+      </c>
+    </row>
+    <row r="48" spans="2:10">
       <c r="B48" t="s">
         <v>58</v>
       </c>
@@ -2452,8 +4967,24 @@
       <c r="D48">
         <v>315</v>
       </c>
-    </row>
-    <row r="49" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F48">
+        <f t="shared" si="0"/>
+        <v>300</v>
+      </c>
+      <c r="H48">
+        <f t="shared" si="1"/>
+        <v>300</v>
+      </c>
+      <c r="I48">
+        <f t="shared" si="2"/>
+        <v>15</v>
+      </c>
+      <c r="J48" s="1">
+        <f t="shared" si="3"/>
+        <v>315</v>
+      </c>
+    </row>
+    <row r="49" spans="2:10">
       <c r="B49" t="s">
         <v>59</v>
       </c>
@@ -2463,8 +4994,24 @@
       <c r="D49">
         <v>365</v>
       </c>
-    </row>
-    <row r="50" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F49">
+        <f t="shared" si="0"/>
+        <v>347.62</v>
+      </c>
+      <c r="H49">
+        <f t="shared" si="1"/>
+        <v>347.61904761904759</v>
+      </c>
+      <c r="I49">
+        <f t="shared" si="2"/>
+        <v>17.379999999999995</v>
+      </c>
+      <c r="J49" s="1">
+        <f t="shared" si="3"/>
+        <v>364.99904761904759</v>
+      </c>
+    </row>
+    <row r="50" spans="2:10">
       <c r="B50" t="s">
         <v>60</v>
       </c>
@@ -2477,8 +5024,24 @@
       <c r="E50">
         <v>2</v>
       </c>
-    </row>
-    <row r="51" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F50">
+        <f t="shared" si="0"/>
+        <v>357.14</v>
+      </c>
+      <c r="H50">
+        <f t="shared" si="1"/>
+        <v>357.14285714285711</v>
+      </c>
+      <c r="I50">
+        <f t="shared" si="2"/>
+        <v>17.860000000000014</v>
+      </c>
+      <c r="J50" s="1">
+        <f t="shared" si="3"/>
+        <v>375.00285714285712</v>
+      </c>
+    </row>
+    <row r="51" spans="2:10">
       <c r="B51" t="s">
         <v>45</v>
       </c>
@@ -2488,8 +5051,24 @@
       <c r="D51">
         <v>975</v>
       </c>
-    </row>
-    <row r="52" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F51">
+        <f t="shared" si="0"/>
+        <v>928.57</v>
+      </c>
+      <c r="H51">
+        <f t="shared" si="1"/>
+        <v>928.57142857142856</v>
+      </c>
+      <c r="I51">
+        <f t="shared" si="2"/>
+        <v>46.42999999999995</v>
+      </c>
+      <c r="J51" s="1">
+        <f t="shared" si="3"/>
+        <v>975.00142857142851</v>
+      </c>
+    </row>
+    <row r="52" spans="2:10">
       <c r="B52" t="s">
         <v>54</v>
       </c>
@@ -2502,8 +5081,24 @@
       <c r="E52">
         <v>2</v>
       </c>
-    </row>
-    <row r="53" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F52">
+        <f t="shared" si="0"/>
+        <v>404.76</v>
+      </c>
+      <c r="H52">
+        <f t="shared" si="1"/>
+        <v>404.76190476190476</v>
+      </c>
+      <c r="I52">
+        <f t="shared" si="2"/>
+        <v>20.240000000000009</v>
+      </c>
+      <c r="J52" s="1">
+        <f t="shared" si="3"/>
+        <v>425.00190476190477</v>
+      </c>
+    </row>
+    <row r="53" spans="2:10">
       <c r="B53" t="s">
         <v>48</v>
       </c>
@@ -2513,8 +5108,24 @@
       <c r="D53">
         <v>545</v>
       </c>
-    </row>
-    <row r="54" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F53">
+        <f t="shared" si="0"/>
+        <v>519.04999999999995</v>
+      </c>
+      <c r="H53">
+        <f t="shared" si="1"/>
+        <v>519.04761904761904</v>
+      </c>
+      <c r="I53">
+        <f t="shared" si="2"/>
+        <v>25.950000000000045</v>
+      </c>
+      <c r="J53" s="1">
+        <f t="shared" si="3"/>
+        <v>544.99761904761908</v>
+      </c>
+    </row>
+    <row r="54" spans="2:10">
       <c r="B54" t="s">
         <v>61</v>
       </c>
@@ -2524,8 +5135,24 @@
       <c r="D54">
         <v>425</v>
       </c>
-    </row>
-    <row r="55" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F54">
+        <f t="shared" si="0"/>
+        <v>404.76</v>
+      </c>
+      <c r="H54">
+        <f t="shared" si="1"/>
+        <v>404.76190476190476</v>
+      </c>
+      <c r="I54">
+        <f t="shared" si="2"/>
+        <v>20.240000000000009</v>
+      </c>
+      <c r="J54" s="1">
+        <f t="shared" si="3"/>
+        <v>425.00190476190477</v>
+      </c>
+    </row>
+    <row r="55" spans="2:10">
       <c r="B55" t="s">
         <v>57</v>
       </c>
@@ -2535,8 +5162,24 @@
       <c r="D55">
         <v>545</v>
       </c>
-    </row>
-    <row r="56" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F55">
+        <f t="shared" si="0"/>
+        <v>519.04999999999995</v>
+      </c>
+      <c r="H55">
+        <f t="shared" si="1"/>
+        <v>519.04761904761904</v>
+      </c>
+      <c r="I55">
+        <f t="shared" si="2"/>
+        <v>25.950000000000045</v>
+      </c>
+      <c r="J55" s="1">
+        <f t="shared" si="3"/>
+        <v>544.99761904761908</v>
+      </c>
+    </row>
+    <row r="56" spans="2:10">
       <c r="B56" t="s">
         <v>48</v>
       </c>
@@ -2546,8 +5189,24 @@
       <c r="D56">
         <v>545</v>
       </c>
-    </row>
-    <row r="57" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F56">
+        <f t="shared" si="0"/>
+        <v>519.04999999999995</v>
+      </c>
+      <c r="H56">
+        <f t="shared" si="1"/>
+        <v>519.04761904761904</v>
+      </c>
+      <c r="I56">
+        <f t="shared" si="2"/>
+        <v>25.950000000000045</v>
+      </c>
+      <c r="J56" s="1">
+        <f t="shared" si="3"/>
+        <v>544.99761904761908</v>
+      </c>
+    </row>
+    <row r="57" spans="2:10">
       <c r="B57" t="s">
         <v>48</v>
       </c>
@@ -2557,8 +5216,24 @@
       <c r="D57">
         <v>545</v>
       </c>
-    </row>
-    <row r="58" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F57">
+        <f t="shared" si="0"/>
+        <v>519.04999999999995</v>
+      </c>
+      <c r="H57">
+        <f t="shared" si="1"/>
+        <v>519.04761904761904</v>
+      </c>
+      <c r="I57">
+        <f t="shared" si="2"/>
+        <v>25.950000000000045</v>
+      </c>
+      <c r="J57" s="1">
+        <f t="shared" si="3"/>
+        <v>544.99761904761908</v>
+      </c>
+    </row>
+    <row r="58" spans="2:10">
       <c r="B58" t="s">
         <v>62</v>
       </c>
@@ -2568,8 +5243,24 @@
       <c r="D58">
         <v>575</v>
       </c>
-    </row>
-    <row r="59" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F58">
+        <f t="shared" si="0"/>
+        <v>547.62</v>
+      </c>
+      <c r="H58">
+        <f t="shared" si="1"/>
+        <v>547.61904761904759</v>
+      </c>
+      <c r="I58">
+        <f t="shared" si="2"/>
+        <v>27.379999999999995</v>
+      </c>
+      <c r="J58" s="1">
+        <f t="shared" si="3"/>
+        <v>574.99904761904759</v>
+      </c>
+    </row>
+    <row r="59" spans="2:10">
       <c r="B59" t="s">
         <v>48</v>
       </c>
@@ -2579,8 +5270,24 @@
       <c r="D59">
         <v>545</v>
       </c>
-    </row>
-    <row r="60" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F59">
+        <f t="shared" si="0"/>
+        <v>519.04999999999995</v>
+      </c>
+      <c r="H59">
+        <f t="shared" si="1"/>
+        <v>519.04761904761904</v>
+      </c>
+      <c r="I59">
+        <f t="shared" si="2"/>
+        <v>25.950000000000045</v>
+      </c>
+      <c r="J59" s="1">
+        <f t="shared" si="3"/>
+        <v>544.99761904761908</v>
+      </c>
+    </row>
+    <row r="60" spans="2:10">
       <c r="B60" t="s">
         <v>40</v>
       </c>
@@ -2590,8 +5297,24 @@
       <c r="D60">
         <v>995</v>
       </c>
-    </row>
-    <row r="61" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F60">
+        <f t="shared" si="0"/>
+        <v>947.62</v>
+      </c>
+      <c r="H60">
+        <f t="shared" si="1"/>
+        <v>947.61904761904759</v>
+      </c>
+      <c r="I60">
+        <f t="shared" si="2"/>
+        <v>47.379999999999995</v>
+      </c>
+      <c r="J60" s="1">
+        <f t="shared" si="3"/>
+        <v>994.99904761904759</v>
+      </c>
+    </row>
+    <row r="61" spans="2:10">
       <c r="B61" t="s">
         <v>40</v>
       </c>
@@ -2604,8 +5327,24 @@
       <c r="E61">
         <v>2</v>
       </c>
-    </row>
-    <row r="62" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F61">
+        <f t="shared" si="0"/>
+        <v>461.9</v>
+      </c>
+      <c r="H61">
+        <f t="shared" si="1"/>
+        <v>461.90476190476187</v>
+      </c>
+      <c r="I61">
+        <f t="shared" si="2"/>
+        <v>23.100000000000023</v>
+      </c>
+      <c r="J61" s="1">
+        <f t="shared" si="3"/>
+        <v>485.00476190476189</v>
+      </c>
+    </row>
+    <row r="62" spans="2:10">
       <c r="B62" t="s">
         <v>40</v>
       </c>
@@ -2615,8 +5354,24 @@
       <c r="D62">
         <v>825</v>
       </c>
-    </row>
-    <row r="63" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F62">
+        <f t="shared" si="0"/>
+        <v>785.71</v>
+      </c>
+      <c r="H62">
+        <f t="shared" si="1"/>
+        <v>785.71428571428567</v>
+      </c>
+      <c r="I62">
+        <f t="shared" si="2"/>
+        <v>39.289999999999964</v>
+      </c>
+      <c r="J62" s="1">
+        <f t="shared" si="3"/>
+        <v>825.00428571428563</v>
+      </c>
+    </row>
+    <row r="63" spans="2:10">
       <c r="B63" t="s">
         <v>48</v>
       </c>
@@ -2626,8 +5381,24 @@
       <c r="D63">
         <v>545</v>
       </c>
-    </row>
-    <row r="64" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F63">
+        <f t="shared" si="0"/>
+        <v>519.04999999999995</v>
+      </c>
+      <c r="H63">
+        <f t="shared" si="1"/>
+        <v>519.04761904761904</v>
+      </c>
+      <c r="I63">
+        <f t="shared" si="2"/>
+        <v>25.950000000000045</v>
+      </c>
+      <c r="J63" s="1">
+        <f t="shared" si="3"/>
+        <v>544.99761904761908</v>
+      </c>
+    </row>
+    <row r="64" spans="2:10">
       <c r="B64" t="s">
         <v>48</v>
       </c>
@@ -2637,8 +5408,24 @@
       <c r="D64">
         <v>545</v>
       </c>
-    </row>
-    <row r="65" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F64">
+        <f t="shared" si="0"/>
+        <v>519.04999999999995</v>
+      </c>
+      <c r="H64">
+        <f t="shared" si="1"/>
+        <v>519.04761904761904</v>
+      </c>
+      <c r="I64">
+        <f t="shared" si="2"/>
+        <v>25.950000000000045</v>
+      </c>
+      <c r="J64" s="1">
+        <f t="shared" si="3"/>
+        <v>544.99761904761908</v>
+      </c>
+    </row>
+    <row r="65" spans="2:10">
       <c r="B65" t="s">
         <v>57</v>
       </c>
@@ -2648,8 +5435,24 @@
       <c r="D65">
         <v>425</v>
       </c>
-    </row>
-    <row r="66" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F65">
+        <f t="shared" si="0"/>
+        <v>404.76</v>
+      </c>
+      <c r="H65">
+        <f t="shared" si="1"/>
+        <v>404.76190476190476</v>
+      </c>
+      <c r="I65">
+        <f t="shared" si="2"/>
+        <v>20.240000000000009</v>
+      </c>
+      <c r="J65" s="1">
+        <f t="shared" si="3"/>
+        <v>425.00190476190477</v>
+      </c>
+    </row>
+    <row r="66" spans="2:10">
       <c r="B66" t="s">
         <v>48</v>
       </c>
@@ -2659,8 +5462,24 @@
       <c r="D66">
         <v>545</v>
       </c>
-    </row>
-    <row r="67" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F66">
+        <f t="shared" si="0"/>
+        <v>519.04999999999995</v>
+      </c>
+      <c r="H66">
+        <f t="shared" si="1"/>
+        <v>519.04761904761904</v>
+      </c>
+      <c r="I66">
+        <f t="shared" si="2"/>
+        <v>25.950000000000045</v>
+      </c>
+      <c r="J66" s="1">
+        <f t="shared" si="3"/>
+        <v>544.99761904761908</v>
+      </c>
+    </row>
+    <row r="67" spans="2:10">
       <c r="B67" t="s">
         <v>41</v>
       </c>
@@ -2673,8 +5492,24 @@
       <c r="E67">
         <v>2</v>
       </c>
-    </row>
-    <row r="68" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F67">
+        <f t="shared" ref="F67:F104" si="4">ROUND(IF(D67&gt;2500, D67/1.18, D67/1.05),2)</f>
+        <v>947.62</v>
+      </c>
+      <c r="H67">
+        <f t="shared" ref="H67:H104" si="5">D67/1.05</f>
+        <v>947.61904761904759</v>
+      </c>
+      <c r="I67">
+        <f t="shared" ref="I67:I104" si="6">D67-F67</f>
+        <v>47.379999999999995</v>
+      </c>
+      <c r="J67" s="1">
+        <f t="shared" ref="J67:J104" si="7">SUM(H67:I67)</f>
+        <v>994.99904761904759</v>
+      </c>
+    </row>
+    <row r="68" spans="2:10">
       <c r="B68" t="s">
         <v>48</v>
       </c>
@@ -2687,8 +5522,24 @@
       <c r="E68">
         <v>2</v>
       </c>
-    </row>
-    <row r="69" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F68">
+        <f t="shared" si="4"/>
+        <v>519.04999999999995</v>
+      </c>
+      <c r="H68">
+        <f t="shared" si="5"/>
+        <v>519.04761904761904</v>
+      </c>
+      <c r="I68">
+        <f t="shared" si="6"/>
+        <v>25.950000000000045</v>
+      </c>
+      <c r="J68" s="1">
+        <f t="shared" si="7"/>
+        <v>544.99761904761908</v>
+      </c>
+    </row>
+    <row r="69" spans="2:10">
       <c r="B69" t="s">
         <v>48</v>
       </c>
@@ -2698,8 +5549,24 @@
       <c r="D69">
         <v>545</v>
       </c>
-    </row>
-    <row r="70" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F69">
+        <f t="shared" si="4"/>
+        <v>519.04999999999995</v>
+      </c>
+      <c r="H69">
+        <f t="shared" si="5"/>
+        <v>519.04761904761904</v>
+      </c>
+      <c r="I69">
+        <f t="shared" si="6"/>
+        <v>25.950000000000045</v>
+      </c>
+      <c r="J69" s="1">
+        <f t="shared" si="7"/>
+        <v>544.99761904761908</v>
+      </c>
+    </row>
+    <row r="70" spans="2:10">
       <c r="B70" t="s">
         <v>48</v>
       </c>
@@ -2709,8 +5576,24 @@
       <c r="D70">
         <v>545</v>
       </c>
-    </row>
-    <row r="71" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F70">
+        <f t="shared" si="4"/>
+        <v>519.04999999999995</v>
+      </c>
+      <c r="H70">
+        <f t="shared" si="5"/>
+        <v>519.04761904761904</v>
+      </c>
+      <c r="I70">
+        <f t="shared" si="6"/>
+        <v>25.950000000000045</v>
+      </c>
+      <c r="J70" s="1">
+        <f t="shared" si="7"/>
+        <v>544.99761904761908</v>
+      </c>
+    </row>
+    <row r="71" spans="2:10">
       <c r="B71" t="s">
         <v>40</v>
       </c>
@@ -2720,8 +5603,24 @@
       <c r="D71">
         <v>995</v>
       </c>
-    </row>
-    <row r="72" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F71">
+        <f t="shared" si="4"/>
+        <v>947.62</v>
+      </c>
+      <c r="H71">
+        <f t="shared" si="5"/>
+        <v>947.61904761904759</v>
+      </c>
+      <c r="I71">
+        <f t="shared" si="6"/>
+        <v>47.379999999999995</v>
+      </c>
+      <c r="J71" s="1">
+        <f t="shared" si="7"/>
+        <v>994.99904761904759</v>
+      </c>
+    </row>
+    <row r="72" spans="2:10">
       <c r="B72" t="s">
         <v>48</v>
       </c>
@@ -2731,8 +5630,24 @@
       <c r="D72">
         <v>545</v>
       </c>
-    </row>
-    <row r="73" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F72">
+        <f t="shared" si="4"/>
+        <v>519.04999999999995</v>
+      </c>
+      <c r="H72">
+        <f t="shared" si="5"/>
+        <v>519.04761904761904</v>
+      </c>
+      <c r="I72">
+        <f t="shared" si="6"/>
+        <v>25.950000000000045</v>
+      </c>
+      <c r="J72" s="1">
+        <f t="shared" si="7"/>
+        <v>544.99761904761908</v>
+      </c>
+    </row>
+    <row r="73" spans="2:10">
       <c r="B73" t="s">
         <v>40</v>
       </c>
@@ -2742,8 +5657,24 @@
       <c r="D73">
         <v>825</v>
       </c>
-    </row>
-    <row r="74" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F73">
+        <f t="shared" si="4"/>
+        <v>785.71</v>
+      </c>
+      <c r="H73">
+        <f t="shared" si="5"/>
+        <v>785.71428571428567</v>
+      </c>
+      <c r="I73">
+        <f t="shared" si="6"/>
+        <v>39.289999999999964</v>
+      </c>
+      <c r="J73" s="1">
+        <f t="shared" si="7"/>
+        <v>825.00428571428563</v>
+      </c>
+    </row>
+    <row r="74" spans="2:10">
       <c r="B74" t="s">
         <v>48</v>
       </c>
@@ -2753,8 +5684,24 @@
       <c r="D74">
         <v>545</v>
       </c>
-    </row>
-    <row r="75" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F74">
+        <f t="shared" si="4"/>
+        <v>519.04999999999995</v>
+      </c>
+      <c r="H74">
+        <f t="shared" si="5"/>
+        <v>519.04761904761904</v>
+      </c>
+      <c r="I74">
+        <f t="shared" si="6"/>
+        <v>25.950000000000045</v>
+      </c>
+      <c r="J74" s="1">
+        <f t="shared" si="7"/>
+        <v>544.99761904761908</v>
+      </c>
+    </row>
+    <row r="75" spans="2:10">
       <c r="B75" t="s">
         <v>62</v>
       </c>
@@ -2764,8 +5711,24 @@
       <c r="D75">
         <v>295</v>
       </c>
-    </row>
-    <row r="76" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F75">
+        <f t="shared" si="4"/>
+        <v>280.95</v>
+      </c>
+      <c r="H75">
+        <f t="shared" si="5"/>
+        <v>280.95238095238096</v>
+      </c>
+      <c r="I75">
+        <f t="shared" si="6"/>
+        <v>14.050000000000011</v>
+      </c>
+      <c r="J75" s="1">
+        <f t="shared" si="7"/>
+        <v>295.00238095238097</v>
+      </c>
+    </row>
+    <row r="76" spans="2:10">
       <c r="B76" t="s">
         <v>40</v>
       </c>
@@ -2775,8 +5738,24 @@
       <c r="D76">
         <v>825</v>
       </c>
-    </row>
-    <row r="77" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F76">
+        <f t="shared" si="4"/>
+        <v>785.71</v>
+      </c>
+      <c r="H76">
+        <f t="shared" si="5"/>
+        <v>785.71428571428567</v>
+      </c>
+      <c r="I76">
+        <f t="shared" si="6"/>
+        <v>39.289999999999964</v>
+      </c>
+      <c r="J76" s="1">
+        <f t="shared" si="7"/>
+        <v>825.00428571428563</v>
+      </c>
+    </row>
+    <row r="77" spans="2:10">
       <c r="B77" t="s">
         <v>48</v>
       </c>
@@ -2786,8 +5765,24 @@
       <c r="D77">
         <v>545</v>
       </c>
-    </row>
-    <row r="78" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F77">
+        <f t="shared" si="4"/>
+        <v>519.04999999999995</v>
+      </c>
+      <c r="H77">
+        <f t="shared" si="5"/>
+        <v>519.04761904761904</v>
+      </c>
+      <c r="I77">
+        <f t="shared" si="6"/>
+        <v>25.950000000000045</v>
+      </c>
+      <c r="J77" s="1">
+        <f t="shared" si="7"/>
+        <v>544.99761904761908</v>
+      </c>
+    </row>
+    <row r="78" spans="2:10">
       <c r="B78" t="s">
         <v>40</v>
       </c>
@@ -2797,8 +5792,24 @@
       <c r="D78">
         <v>825</v>
       </c>
-    </row>
-    <row r="79" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F78">
+        <f t="shared" si="4"/>
+        <v>785.71</v>
+      </c>
+      <c r="H78">
+        <f t="shared" si="5"/>
+        <v>785.71428571428567</v>
+      </c>
+      <c r="I78">
+        <f t="shared" si="6"/>
+        <v>39.289999999999964</v>
+      </c>
+      <c r="J78" s="1">
+        <f t="shared" si="7"/>
+        <v>825.00428571428563</v>
+      </c>
+    </row>
+    <row r="79" spans="2:10">
       <c r="B79" t="s">
         <v>48</v>
       </c>
@@ -2808,8 +5819,24 @@
       <c r="D79">
         <v>545</v>
       </c>
-    </row>
-    <row r="80" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F79">
+        <f t="shared" si="4"/>
+        <v>519.04999999999995</v>
+      </c>
+      <c r="H79">
+        <f t="shared" si="5"/>
+        <v>519.04761904761904</v>
+      </c>
+      <c r="I79">
+        <f t="shared" si="6"/>
+        <v>25.950000000000045</v>
+      </c>
+      <c r="J79" s="1">
+        <f t="shared" si="7"/>
+        <v>544.99761904761908</v>
+      </c>
+    </row>
+    <row r="80" spans="2:10">
       <c r="B80" t="s">
         <v>48</v>
       </c>
@@ -2819,8 +5846,24 @@
       <c r="D80">
         <v>545</v>
       </c>
-    </row>
-    <row r="81" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F80">
+        <f t="shared" si="4"/>
+        <v>519.04999999999995</v>
+      </c>
+      <c r="H80">
+        <f t="shared" si="5"/>
+        <v>519.04761904761904</v>
+      </c>
+      <c r="I80">
+        <f t="shared" si="6"/>
+        <v>25.950000000000045</v>
+      </c>
+      <c r="J80" s="1">
+        <f t="shared" si="7"/>
+        <v>544.99761904761908</v>
+      </c>
+    </row>
+    <row r="81" spans="2:10">
       <c r="B81" t="s">
         <v>48</v>
       </c>
@@ -2830,8 +5873,24 @@
       <c r="D81">
         <v>545</v>
       </c>
-    </row>
-    <row r="82" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F81">
+        <f t="shared" si="4"/>
+        <v>519.04999999999995</v>
+      </c>
+      <c r="H81">
+        <f t="shared" si="5"/>
+        <v>519.04761904761904</v>
+      </c>
+      <c r="I81">
+        <f t="shared" si="6"/>
+        <v>25.950000000000045</v>
+      </c>
+      <c r="J81" s="1">
+        <f t="shared" si="7"/>
+        <v>544.99761904761908</v>
+      </c>
+    </row>
+    <row r="82" spans="2:10">
       <c r="B82" t="s">
         <v>40</v>
       </c>
@@ -2841,8 +5900,24 @@
       <c r="D82">
         <v>995</v>
       </c>
-    </row>
-    <row r="83" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F82">
+        <f t="shared" si="4"/>
+        <v>947.62</v>
+      </c>
+      <c r="H82">
+        <f t="shared" si="5"/>
+        <v>947.61904761904759</v>
+      </c>
+      <c r="I82">
+        <f t="shared" si="6"/>
+        <v>47.379999999999995</v>
+      </c>
+      <c r="J82" s="1">
+        <f t="shared" si="7"/>
+        <v>994.99904761904759</v>
+      </c>
+    </row>
+    <row r="83" spans="2:10">
       <c r="B83" t="s">
         <v>40</v>
       </c>
@@ -2852,8 +5927,24 @@
       <c r="D83">
         <v>545</v>
       </c>
-    </row>
-    <row r="84" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F83">
+        <f t="shared" si="4"/>
+        <v>519.04999999999995</v>
+      </c>
+      <c r="H83">
+        <f t="shared" si="5"/>
+        <v>519.04761904761904</v>
+      </c>
+      <c r="I83">
+        <f t="shared" si="6"/>
+        <v>25.950000000000045</v>
+      </c>
+      <c r="J83" s="1">
+        <f t="shared" si="7"/>
+        <v>544.99761904761908</v>
+      </c>
+    </row>
+    <row r="84" spans="2:10">
       <c r="B84" t="s">
         <v>40</v>
       </c>
@@ -2863,8 +5954,24 @@
       <c r="D84">
         <v>485</v>
       </c>
-    </row>
-    <row r="85" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F84">
+        <f t="shared" si="4"/>
+        <v>461.9</v>
+      </c>
+      <c r="H84">
+        <f t="shared" si="5"/>
+        <v>461.90476190476187</v>
+      </c>
+      <c r="I84">
+        <f t="shared" si="6"/>
+        <v>23.100000000000023</v>
+      </c>
+      <c r="J84" s="1">
+        <f t="shared" si="7"/>
+        <v>485.00476190476189</v>
+      </c>
+    </row>
+    <row r="85" spans="2:10">
       <c r="B85" t="s">
         <v>40</v>
       </c>
@@ -2874,8 +5981,24 @@
       <c r="D85">
         <v>485</v>
       </c>
-    </row>
-    <row r="86" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F85">
+        <f t="shared" si="4"/>
+        <v>461.9</v>
+      </c>
+      <c r="H85">
+        <f t="shared" si="5"/>
+        <v>461.90476190476187</v>
+      </c>
+      <c r="I85">
+        <f t="shared" si="6"/>
+        <v>23.100000000000023</v>
+      </c>
+      <c r="J85" s="1">
+        <f t="shared" si="7"/>
+        <v>485.00476190476189</v>
+      </c>
+    </row>
+    <row r="86" spans="2:10">
       <c r="B86" t="s">
         <v>40</v>
       </c>
@@ -2885,8 +6008,24 @@
       <c r="D86">
         <v>825</v>
       </c>
-    </row>
-    <row r="87" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F86">
+        <f t="shared" si="4"/>
+        <v>785.71</v>
+      </c>
+      <c r="H86">
+        <f t="shared" si="5"/>
+        <v>785.71428571428567</v>
+      </c>
+      <c r="I86">
+        <f t="shared" si="6"/>
+        <v>39.289999999999964</v>
+      </c>
+      <c r="J86" s="1">
+        <f t="shared" si="7"/>
+        <v>825.00428571428563</v>
+      </c>
+    </row>
+    <row r="87" spans="2:10">
       <c r="B87" t="s">
         <v>40</v>
       </c>
@@ -2896,8 +6035,24 @@
       <c r="D87">
         <v>995</v>
       </c>
-    </row>
-    <row r="88" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F87">
+        <f t="shared" si="4"/>
+        <v>947.62</v>
+      </c>
+      <c r="H87">
+        <f t="shared" si="5"/>
+        <v>947.61904761904759</v>
+      </c>
+      <c r="I87">
+        <f t="shared" si="6"/>
+        <v>47.379999999999995</v>
+      </c>
+      <c r="J87" s="1">
+        <f t="shared" si="7"/>
+        <v>994.99904761904759</v>
+      </c>
+    </row>
+    <row r="88" spans="2:10">
       <c r="B88" t="s">
         <v>40</v>
       </c>
@@ -2907,8 +6062,24 @@
       <c r="D88">
         <v>825</v>
       </c>
-    </row>
-    <row r="89" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F88">
+        <f t="shared" si="4"/>
+        <v>785.71</v>
+      </c>
+      <c r="H88">
+        <f t="shared" si="5"/>
+        <v>785.71428571428567</v>
+      </c>
+      <c r="I88">
+        <f t="shared" si="6"/>
+        <v>39.289999999999964</v>
+      </c>
+      <c r="J88" s="1">
+        <f t="shared" si="7"/>
+        <v>825.00428571428563</v>
+      </c>
+    </row>
+    <row r="89" spans="2:10">
       <c r="B89" t="s">
         <v>63</v>
       </c>
@@ -2918,8 +6089,24 @@
       <c r="D89">
         <v>685</v>
       </c>
-    </row>
-    <row r="90" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F89">
+        <f t="shared" si="4"/>
+        <v>652.38</v>
+      </c>
+      <c r="H89">
+        <f t="shared" si="5"/>
+        <v>652.38095238095241</v>
+      </c>
+      <c r="I89">
+        <f t="shared" si="6"/>
+        <v>32.620000000000005</v>
+      </c>
+      <c r="J89" s="1">
+        <f t="shared" si="7"/>
+        <v>685.00095238095241</v>
+      </c>
+    </row>
+    <row r="90" spans="2:10">
       <c r="B90" t="s">
         <v>48</v>
       </c>
@@ -2929,8 +6116,24 @@
       <c r="D90">
         <v>545</v>
       </c>
-    </row>
-    <row r="91" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F90">
+        <f t="shared" si="4"/>
+        <v>519.04999999999995</v>
+      </c>
+      <c r="H90">
+        <f t="shared" si="5"/>
+        <v>519.04761904761904</v>
+      </c>
+      <c r="I90">
+        <f t="shared" si="6"/>
+        <v>25.950000000000045</v>
+      </c>
+      <c r="J90" s="1">
+        <f t="shared" si="7"/>
+        <v>544.99761904761908</v>
+      </c>
+    </row>
+    <row r="91" spans="2:10">
       <c r="B91" t="s">
         <v>49</v>
       </c>
@@ -2940,8 +6143,24 @@
       <c r="D91">
         <v>535</v>
       </c>
-    </row>
-    <row r="92" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F91">
+        <f t="shared" si="4"/>
+        <v>509.52</v>
+      </c>
+      <c r="H91">
+        <f t="shared" si="5"/>
+        <v>509.52380952380952</v>
+      </c>
+      <c r="I91">
+        <f t="shared" si="6"/>
+        <v>25.480000000000018</v>
+      </c>
+      <c r="J91" s="1">
+        <f t="shared" si="7"/>
+        <v>535.00380952380954</v>
+      </c>
+    </row>
+    <row r="92" spans="2:10">
       <c r="B92" t="s">
         <v>49</v>
       </c>
@@ -2954,8 +6173,24 @@
       <c r="E92">
         <v>2</v>
       </c>
-    </row>
-    <row r="93" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F92">
+        <f t="shared" si="4"/>
+        <v>804.76</v>
+      </c>
+      <c r="H92">
+        <f t="shared" si="5"/>
+        <v>804.7619047619047</v>
+      </c>
+      <c r="I92">
+        <f t="shared" si="6"/>
+        <v>40.240000000000009</v>
+      </c>
+      <c r="J92" s="1">
+        <f t="shared" si="7"/>
+        <v>845.00190476190471</v>
+      </c>
+    </row>
+    <row r="93" spans="2:10">
       <c r="B93" t="s">
         <v>49</v>
       </c>
@@ -2965,8 +6200,24 @@
       <c r="D93">
         <v>685</v>
       </c>
-    </row>
-    <row r="94" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F93">
+        <f t="shared" si="4"/>
+        <v>652.38</v>
+      </c>
+      <c r="H93">
+        <f t="shared" si="5"/>
+        <v>652.38095238095241</v>
+      </c>
+      <c r="I93">
+        <f t="shared" si="6"/>
+        <v>32.620000000000005</v>
+      </c>
+      <c r="J93" s="1">
+        <f t="shared" si="7"/>
+        <v>685.00095238095241</v>
+      </c>
+    </row>
+    <row r="94" spans="2:10">
       <c r="B94" t="s">
         <v>64</v>
       </c>
@@ -2976,8 +6227,24 @@
       <c r="D94">
         <v>845</v>
       </c>
-    </row>
-    <row r="95" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F94">
+        <f t="shared" si="4"/>
+        <v>804.76</v>
+      </c>
+      <c r="H94">
+        <f t="shared" si="5"/>
+        <v>804.7619047619047</v>
+      </c>
+      <c r="I94">
+        <f t="shared" si="6"/>
+        <v>40.240000000000009</v>
+      </c>
+      <c r="J94" s="1">
+        <f t="shared" si="7"/>
+        <v>845.00190476190471</v>
+      </c>
+    </row>
+    <row r="95" spans="2:10">
       <c r="B95" t="s">
         <v>57</v>
       </c>
@@ -2987,8 +6254,24 @@
       <c r="D95">
         <v>575</v>
       </c>
-    </row>
-    <row r="96" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F95">
+        <f t="shared" si="4"/>
+        <v>547.62</v>
+      </c>
+      <c r="H95">
+        <f t="shared" si="5"/>
+        <v>547.61904761904759</v>
+      </c>
+      <c r="I95">
+        <f t="shared" si="6"/>
+        <v>27.379999999999995</v>
+      </c>
+      <c r="J95" s="1">
+        <f t="shared" si="7"/>
+        <v>574.99904761904759</v>
+      </c>
+    </row>
+    <row r="96" spans="2:10">
       <c r="B96" t="s">
         <v>65</v>
       </c>
@@ -2998,8 +6281,24 @@
       <c r="D96">
         <v>335</v>
       </c>
-    </row>
-    <row r="97" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F96">
+        <f t="shared" si="4"/>
+        <v>319.05</v>
+      </c>
+      <c r="H96">
+        <f t="shared" si="5"/>
+        <v>319.04761904761904</v>
+      </c>
+      <c r="I96">
+        <f t="shared" si="6"/>
+        <v>15.949999999999989</v>
+      </c>
+      <c r="J96" s="1">
+        <f t="shared" si="7"/>
+        <v>334.99761904761903</v>
+      </c>
+    </row>
+    <row r="97" spans="2:10">
       <c r="B97" t="s">
         <v>57</v>
       </c>
@@ -3009,8 +6308,24 @@
       <c r="D97">
         <v>575</v>
       </c>
-    </row>
-    <row r="98" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F97">
+        <f t="shared" si="4"/>
+        <v>547.62</v>
+      </c>
+      <c r="H97">
+        <f t="shared" si="5"/>
+        <v>547.61904761904759</v>
+      </c>
+      <c r="I97">
+        <f t="shared" si="6"/>
+        <v>27.379999999999995</v>
+      </c>
+      <c r="J97" s="1">
+        <f t="shared" si="7"/>
+        <v>574.99904761904759</v>
+      </c>
+    </row>
+    <row r="98" spans="2:10">
       <c r="B98" t="s">
         <v>57</v>
       </c>
@@ -3023,8 +6338,24 @@
       <c r="E98">
         <v>2</v>
       </c>
-    </row>
-    <row r="99" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F98">
+        <f t="shared" si="4"/>
+        <v>404.76</v>
+      </c>
+      <c r="H98">
+        <f t="shared" si="5"/>
+        <v>404.76190476190476</v>
+      </c>
+      <c r="I98">
+        <f t="shared" si="6"/>
+        <v>20.240000000000009</v>
+      </c>
+      <c r="J98" s="1">
+        <f t="shared" si="7"/>
+        <v>425.00190476190477</v>
+      </c>
+    </row>
+    <row r="99" spans="2:10">
       <c r="B99" t="s">
         <v>57</v>
       </c>
@@ -3034,8 +6365,24 @@
       <c r="D99">
         <v>575</v>
       </c>
-    </row>
-    <row r="100" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F99">
+        <f t="shared" si="4"/>
+        <v>547.62</v>
+      </c>
+      <c r="H99">
+        <f t="shared" si="5"/>
+        <v>547.61904761904759</v>
+      </c>
+      <c r="I99">
+        <f t="shared" si="6"/>
+        <v>27.379999999999995</v>
+      </c>
+      <c r="J99" s="1">
+        <f t="shared" si="7"/>
+        <v>574.99904761904759</v>
+      </c>
+    </row>
+    <row r="100" spans="2:10">
       <c r="B100" t="s">
         <v>65</v>
       </c>
@@ -3045,8 +6392,24 @@
       <c r="D100">
         <v>335</v>
       </c>
-    </row>
-    <row r="101" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F100">
+        <f t="shared" si="4"/>
+        <v>319.05</v>
+      </c>
+      <c r="H100">
+        <f t="shared" si="5"/>
+        <v>319.04761904761904</v>
+      </c>
+      <c r="I100">
+        <f t="shared" si="6"/>
+        <v>15.949999999999989</v>
+      </c>
+      <c r="J100" s="1">
+        <f t="shared" si="7"/>
+        <v>334.99761904761903</v>
+      </c>
+    </row>
+    <row r="101" spans="2:10">
       <c r="B101" t="s">
         <v>57</v>
       </c>
@@ -3059,8 +6422,24 @@
       <c r="E101">
         <v>5</v>
       </c>
-    </row>
-    <row r="102" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F101">
+        <f t="shared" si="4"/>
+        <v>547.62</v>
+      </c>
+      <c r="H101">
+        <f t="shared" si="5"/>
+        <v>547.61904761904759</v>
+      </c>
+      <c r="I101">
+        <f t="shared" si="6"/>
+        <v>27.379999999999995</v>
+      </c>
+      <c r="J101" s="1">
+        <f t="shared" si="7"/>
+        <v>574.99904761904759</v>
+      </c>
+    </row>
+    <row r="102" spans="2:10">
       <c r="B102" t="s">
         <v>40</v>
       </c>
@@ -3070,8 +6449,24 @@
       <c r="D102">
         <v>825</v>
       </c>
-    </row>
-    <row r="103" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F102">
+        <f t="shared" si="4"/>
+        <v>785.71</v>
+      </c>
+      <c r="H102">
+        <f t="shared" si="5"/>
+        <v>785.71428571428567</v>
+      </c>
+      <c r="I102">
+        <f t="shared" si="6"/>
+        <v>39.289999999999964</v>
+      </c>
+      <c r="J102" s="1">
+        <f t="shared" si="7"/>
+        <v>825.00428571428563</v>
+      </c>
+    </row>
+    <row r="103" spans="2:10">
       <c r="B103" t="s">
         <v>48</v>
       </c>
@@ -3084,8 +6479,24 @@
       <c r="E103">
         <v>2</v>
       </c>
-    </row>
-    <row r="104" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F103">
+        <f t="shared" si="4"/>
+        <v>519.04999999999995</v>
+      </c>
+      <c r="H103">
+        <f t="shared" si="5"/>
+        <v>519.04761904761904</v>
+      </c>
+      <c r="I103">
+        <f t="shared" si="6"/>
+        <v>25.950000000000045</v>
+      </c>
+      <c r="J103" s="1">
+        <f t="shared" si="7"/>
+        <v>544.99761904761908</v>
+      </c>
+    </row>
+    <row r="104" spans="2:10">
       <c r="B104" t="s">
         <v>65</v>
       </c>
@@ -3094,6 +6505,22 @@
       </c>
       <c r="D104">
         <v>335</v>
+      </c>
+      <c r="F104">
+        <f t="shared" si="4"/>
+        <v>319.05</v>
+      </c>
+      <c r="H104">
+        <f t="shared" si="5"/>
+        <v>319.04761904761904</v>
+      </c>
+      <c r="I104">
+        <f t="shared" si="6"/>
+        <v>15.949999999999989</v>
+      </c>
+      <c r="J104" s="1">
+        <f t="shared" si="7"/>
+        <v>334.99761904761903</v>
       </c>
     </row>
   </sheetData>
@@ -3102,15 +6529,16 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{620FA4DC-917C-41FB-A2E5-405EAC4AFFCB}">
-  <dimension ref="A1:E110"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:J110"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="6.85546875" customWidth="1"/>
     <col min="2" max="2" width="19.28515625" customWidth="1"/>
+    <col min="6" max="6" width="27" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -3126,8 +6554,20 @@
       <c r="E1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F1" t="s">
+        <v>82</v>
+      </c>
+      <c r="H1" t="s">
+        <v>83</v>
+      </c>
+      <c r="I1" t="s">
+        <v>84</v>
+      </c>
+      <c r="J1" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10">
       <c r="B2" t="s">
         <v>35</v>
       </c>
@@ -3137,8 +6577,24 @@
       <c r="D2">
         <v>545</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F2">
+        <f>ROUND(IF(D2&gt;2500, D2/1.18, D2/1.05),2)</f>
+        <v>519.04999999999995</v>
+      </c>
+      <c r="H2">
+        <f>D2/1.05</f>
+        <v>519.04761904761904</v>
+      </c>
+      <c r="I2">
+        <f>D2-H2</f>
+        <v>25.952380952380963</v>
+      </c>
+      <c r="J2">
+        <f>SUM(H2:I2)</f>
+        <v>545</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
       <c r="B3" t="s">
         <v>35</v>
       </c>
@@ -3148,8 +6604,24 @@
       <c r="D3">
         <v>545</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F3">
+        <f t="shared" ref="F3:F66" si="0">ROUND(IF(D3&gt;2500, D3/1.18, D3/1.05),2)</f>
+        <v>519.04999999999995</v>
+      </c>
+      <c r="H3">
+        <f t="shared" ref="H3:H66" si="1">D3/1.05</f>
+        <v>519.04761904761904</v>
+      </c>
+      <c r="I3">
+        <f t="shared" ref="I3:I66" si="2">D3-H3</f>
+        <v>25.952380952380963</v>
+      </c>
+      <c r="J3">
+        <f t="shared" ref="J3:J66" si="3">SUM(H3:I3)</f>
+        <v>545</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
       <c r="B4" t="s">
         <v>35</v>
       </c>
@@ -3159,8 +6631,24 @@
       <c r="D4">
         <v>545</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F4">
+        <f t="shared" si="0"/>
+        <v>519.04999999999995</v>
+      </c>
+      <c r="H4">
+        <f t="shared" si="1"/>
+        <v>519.04761904761904</v>
+      </c>
+      <c r="I4">
+        <f t="shared" si="2"/>
+        <v>25.952380952380963</v>
+      </c>
+      <c r="J4">
+        <f t="shared" si="3"/>
+        <v>545</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
       <c r="B5" t="s">
         <v>35</v>
       </c>
@@ -3170,8 +6658,24 @@
       <c r="D5">
         <v>545</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F5">
+        <f t="shared" si="0"/>
+        <v>519.04999999999995</v>
+      </c>
+      <c r="H5">
+        <f t="shared" si="1"/>
+        <v>519.04761904761904</v>
+      </c>
+      <c r="I5">
+        <f t="shared" si="2"/>
+        <v>25.952380952380963</v>
+      </c>
+      <c r="J5">
+        <f t="shared" si="3"/>
+        <v>545</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
       <c r="B6" t="s">
         <v>35</v>
       </c>
@@ -3181,8 +6685,24 @@
       <c r="D6">
         <v>545</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F6">
+        <f t="shared" si="0"/>
+        <v>519.04999999999995</v>
+      </c>
+      <c r="H6">
+        <f t="shared" si="1"/>
+        <v>519.04761904761904</v>
+      </c>
+      <c r="I6">
+        <f t="shared" si="2"/>
+        <v>25.952380952380963</v>
+      </c>
+      <c r="J6">
+        <f t="shared" si="3"/>
+        <v>545</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
       <c r="B7" t="s">
         <v>61</v>
       </c>
@@ -3192,8 +6712,24 @@
       <c r="D7">
         <v>425</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F7">
+        <f t="shared" si="0"/>
+        <v>404.76</v>
+      </c>
+      <c r="H7">
+        <f t="shared" si="1"/>
+        <v>404.76190476190476</v>
+      </c>
+      <c r="I7">
+        <f t="shared" si="2"/>
+        <v>20.238095238095241</v>
+      </c>
+      <c r="J7">
+        <f t="shared" si="3"/>
+        <v>425</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10">
       <c r="B8" t="s">
         <v>35</v>
       </c>
@@ -3203,8 +6739,24 @@
       <c r="D8">
         <v>545</v>
       </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F8">
+        <f t="shared" si="0"/>
+        <v>519.04999999999995</v>
+      </c>
+      <c r="H8">
+        <f t="shared" si="1"/>
+        <v>519.04761904761904</v>
+      </c>
+      <c r="I8">
+        <f t="shared" si="2"/>
+        <v>25.952380952380963</v>
+      </c>
+      <c r="J8">
+        <f t="shared" si="3"/>
+        <v>545</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
       <c r="B9" t="s">
         <v>35</v>
       </c>
@@ -3214,8 +6766,24 @@
       <c r="D9">
         <v>545</v>
       </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F9">
+        <f t="shared" si="0"/>
+        <v>519.04999999999995</v>
+      </c>
+      <c r="H9">
+        <f t="shared" si="1"/>
+        <v>519.04761904761904</v>
+      </c>
+      <c r="I9">
+        <f t="shared" si="2"/>
+        <v>25.952380952380963</v>
+      </c>
+      <c r="J9">
+        <f t="shared" si="3"/>
+        <v>545</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10">
       <c r="B10" t="s">
         <v>35</v>
       </c>
@@ -3225,8 +6793,24 @@
       <c r="D10">
         <v>545</v>
       </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F10">
+        <f t="shared" si="0"/>
+        <v>519.04999999999995</v>
+      </c>
+      <c r="H10">
+        <f t="shared" si="1"/>
+        <v>519.04761904761904</v>
+      </c>
+      <c r="I10">
+        <f t="shared" si="2"/>
+        <v>25.952380952380963</v>
+      </c>
+      <c r="J10">
+        <f t="shared" si="3"/>
+        <v>545</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10">
       <c r="B11" t="s">
         <v>35</v>
       </c>
@@ -3236,8 +6820,24 @@
       <c r="D11">
         <v>545</v>
       </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F11">
+        <f t="shared" si="0"/>
+        <v>519.04999999999995</v>
+      </c>
+      <c r="H11">
+        <f t="shared" si="1"/>
+        <v>519.04761904761904</v>
+      </c>
+      <c r="I11">
+        <f t="shared" si="2"/>
+        <v>25.952380952380963</v>
+      </c>
+      <c r="J11">
+        <f t="shared" si="3"/>
+        <v>545</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10">
       <c r="B12" t="s">
         <v>35</v>
       </c>
@@ -3247,8 +6847,24 @@
       <c r="D12">
         <v>545</v>
       </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F12">
+        <f t="shared" si="0"/>
+        <v>519.04999999999995</v>
+      </c>
+      <c r="H12">
+        <f t="shared" si="1"/>
+        <v>519.04761904761904</v>
+      </c>
+      <c r="I12">
+        <f t="shared" si="2"/>
+        <v>25.952380952380963</v>
+      </c>
+      <c r="J12">
+        <f t="shared" si="3"/>
+        <v>545</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10">
       <c r="B13" t="s">
         <v>61</v>
       </c>
@@ -3258,8 +6874,24 @@
       <c r="D13">
         <v>425</v>
       </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F13">
+        <f t="shared" si="0"/>
+        <v>404.76</v>
+      </c>
+      <c r="H13">
+        <f t="shared" si="1"/>
+        <v>404.76190476190476</v>
+      </c>
+      <c r="I13">
+        <f t="shared" si="2"/>
+        <v>20.238095238095241</v>
+      </c>
+      <c r="J13">
+        <f t="shared" si="3"/>
+        <v>425</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10">
       <c r="B14" t="s">
         <v>61</v>
       </c>
@@ -3269,8 +6901,24 @@
       <c r="D14">
         <v>575</v>
       </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F14">
+        <f t="shared" si="0"/>
+        <v>547.62</v>
+      </c>
+      <c r="H14">
+        <f t="shared" si="1"/>
+        <v>547.61904761904759</v>
+      </c>
+      <c r="I14">
+        <f t="shared" si="2"/>
+        <v>27.380952380952408</v>
+      </c>
+      <c r="J14">
+        <f t="shared" si="3"/>
+        <v>575</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10">
       <c r="B15" t="s">
         <v>35</v>
       </c>
@@ -3280,8 +6928,24 @@
       <c r="D15">
         <v>545</v>
       </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F15">
+        <f t="shared" si="0"/>
+        <v>519.04999999999995</v>
+      </c>
+      <c r="H15">
+        <f t="shared" si="1"/>
+        <v>519.04761904761904</v>
+      </c>
+      <c r="I15">
+        <f t="shared" si="2"/>
+        <v>25.952380952380963</v>
+      </c>
+      <c r="J15">
+        <f t="shared" si="3"/>
+        <v>545</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10">
       <c r="B16" t="s">
         <v>66</v>
       </c>
@@ -3294,8 +6958,24 @@
       <c r="E16">
         <v>9</v>
       </c>
-    </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F16">
+        <f t="shared" si="0"/>
+        <v>614.29</v>
+      </c>
+      <c r="H16">
+        <f t="shared" si="1"/>
+        <v>614.28571428571422</v>
+      </c>
+      <c r="I16">
+        <f t="shared" si="2"/>
+        <v>30.714285714285779</v>
+      </c>
+      <c r="J16">
+        <f t="shared" si="3"/>
+        <v>645</v>
+      </c>
+    </row>
+    <row r="17" spans="2:10">
       <c r="B17" t="s">
         <v>66</v>
       </c>
@@ -3308,8 +6988,24 @@
       <c r="E17">
         <v>6</v>
       </c>
-    </row>
-    <row r="18" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F17">
+        <f t="shared" si="0"/>
+        <v>614.29</v>
+      </c>
+      <c r="H17">
+        <f t="shared" si="1"/>
+        <v>614.28571428571422</v>
+      </c>
+      <c r="I17">
+        <f t="shared" si="2"/>
+        <v>30.714285714285779</v>
+      </c>
+      <c r="J17">
+        <f t="shared" si="3"/>
+        <v>645</v>
+      </c>
+    </row>
+    <row r="18" spans="2:10">
       <c r="B18" t="s">
         <v>66</v>
       </c>
@@ -3322,8 +7018,24 @@
       <c r="E18">
         <v>5</v>
       </c>
-    </row>
-    <row r="19" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F18">
+        <f t="shared" si="0"/>
+        <v>252.38</v>
+      </c>
+      <c r="H18">
+        <f t="shared" si="1"/>
+        <v>252.38095238095238</v>
+      </c>
+      <c r="I18">
+        <f t="shared" si="2"/>
+        <v>12.61904761904762</v>
+      </c>
+      <c r="J18">
+        <f t="shared" si="3"/>
+        <v>265</v>
+      </c>
+    </row>
+    <row r="19" spans="2:10">
       <c r="B19" t="s">
         <v>66</v>
       </c>
@@ -3336,8 +7048,24 @@
       <c r="E19">
         <v>4</v>
       </c>
-    </row>
-    <row r="20" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F19">
+        <f t="shared" si="0"/>
+        <v>280.95</v>
+      </c>
+      <c r="H19">
+        <f t="shared" si="1"/>
+        <v>280.95238095238096</v>
+      </c>
+      <c r="I19">
+        <f t="shared" si="2"/>
+        <v>14.047619047619037</v>
+      </c>
+      <c r="J19">
+        <f t="shared" si="3"/>
+        <v>295</v>
+      </c>
+    </row>
+    <row r="20" spans="2:10">
       <c r="B20" t="s">
         <v>67</v>
       </c>
@@ -3347,8 +7075,24 @@
       <c r="D20">
         <v>675</v>
       </c>
-    </row>
-    <row r="21" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F20">
+        <f t="shared" si="0"/>
+        <v>642.86</v>
+      </c>
+      <c r="H20">
+        <f t="shared" si="1"/>
+        <v>642.85714285714278</v>
+      </c>
+      <c r="I20">
+        <f t="shared" si="2"/>
+        <v>32.142857142857224</v>
+      </c>
+      <c r="J20">
+        <f t="shared" si="3"/>
+        <v>675</v>
+      </c>
+    </row>
+    <row r="21" spans="2:10">
       <c r="B21" t="s">
         <v>68</v>
       </c>
@@ -3358,8 +7102,24 @@
       <c r="D21">
         <v>425</v>
       </c>
-    </row>
-    <row r="22" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F21">
+        <f t="shared" si="0"/>
+        <v>404.76</v>
+      </c>
+      <c r="H21">
+        <f t="shared" si="1"/>
+        <v>404.76190476190476</v>
+      </c>
+      <c r="I21">
+        <f t="shared" si="2"/>
+        <v>20.238095238095241</v>
+      </c>
+      <c r="J21">
+        <f t="shared" si="3"/>
+        <v>425</v>
+      </c>
+    </row>
+    <row r="22" spans="2:10">
       <c r="B22" t="s">
         <v>66</v>
       </c>
@@ -3369,8 +7129,24 @@
       <c r="D22">
         <v>295</v>
       </c>
-    </row>
-    <row r="23" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F22">
+        <f t="shared" si="0"/>
+        <v>280.95</v>
+      </c>
+      <c r="H22">
+        <f t="shared" si="1"/>
+        <v>280.95238095238096</v>
+      </c>
+      <c r="I22">
+        <f t="shared" si="2"/>
+        <v>14.047619047619037</v>
+      </c>
+      <c r="J22">
+        <f t="shared" si="3"/>
+        <v>295</v>
+      </c>
+    </row>
+    <row r="23" spans="2:10">
       <c r="B23" t="s">
         <v>66</v>
       </c>
@@ -3380,8 +7156,24 @@
       <c r="D23">
         <v>645</v>
       </c>
-    </row>
-    <row r="24" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F23">
+        <f t="shared" si="0"/>
+        <v>614.29</v>
+      </c>
+      <c r="H23">
+        <f t="shared" si="1"/>
+        <v>614.28571428571422</v>
+      </c>
+      <c r="I23">
+        <f t="shared" si="2"/>
+        <v>30.714285714285779</v>
+      </c>
+      <c r="J23">
+        <f t="shared" si="3"/>
+        <v>645</v>
+      </c>
+    </row>
+    <row r="24" spans="2:10">
       <c r="B24" t="s">
         <v>66</v>
       </c>
@@ -3394,8 +7186,24 @@
       <c r="E24">
         <v>2</v>
       </c>
-    </row>
-    <row r="25" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F24">
+        <f t="shared" si="0"/>
+        <v>614.29</v>
+      </c>
+      <c r="H24">
+        <f t="shared" si="1"/>
+        <v>614.28571428571422</v>
+      </c>
+      <c r="I24">
+        <f t="shared" si="2"/>
+        <v>30.714285714285779</v>
+      </c>
+      <c r="J24">
+        <f t="shared" si="3"/>
+        <v>645</v>
+      </c>
+    </row>
+    <row r="25" spans="2:10">
       <c r="B25" t="s">
         <v>66</v>
       </c>
@@ -3405,8 +7213,24 @@
       <c r="D25">
         <v>295</v>
       </c>
-    </row>
-    <row r="26" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F25">
+        <f t="shared" si="0"/>
+        <v>280.95</v>
+      </c>
+      <c r="H25">
+        <f t="shared" si="1"/>
+        <v>280.95238095238096</v>
+      </c>
+      <c r="I25">
+        <f t="shared" si="2"/>
+        <v>14.047619047619037</v>
+      </c>
+      <c r="J25">
+        <f t="shared" si="3"/>
+        <v>295</v>
+      </c>
+    </row>
+    <row r="26" spans="2:10">
       <c r="B26" t="s">
         <v>66</v>
       </c>
@@ -3416,8 +7240,24 @@
       <c r="D26">
         <v>645</v>
       </c>
-    </row>
-    <row r="27" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F26">
+        <f t="shared" si="0"/>
+        <v>614.29</v>
+      </c>
+      <c r="H26">
+        <f t="shared" si="1"/>
+        <v>614.28571428571422</v>
+      </c>
+      <c r="I26">
+        <f t="shared" si="2"/>
+        <v>30.714285714285779</v>
+      </c>
+      <c r="J26">
+        <f t="shared" si="3"/>
+        <v>645</v>
+      </c>
+    </row>
+    <row r="27" spans="2:10">
       <c r="B27" t="s">
         <v>66</v>
       </c>
@@ -3427,8 +7267,24 @@
       <c r="D27">
         <v>295</v>
       </c>
-    </row>
-    <row r="28" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F27">
+        <f t="shared" si="0"/>
+        <v>280.95</v>
+      </c>
+      <c r="H27">
+        <f t="shared" si="1"/>
+        <v>280.95238095238096</v>
+      </c>
+      <c r="I27">
+        <f t="shared" si="2"/>
+        <v>14.047619047619037</v>
+      </c>
+      <c r="J27">
+        <f t="shared" si="3"/>
+        <v>295</v>
+      </c>
+    </row>
+    <row r="28" spans="2:10">
       <c r="B28" t="s">
         <v>66</v>
       </c>
@@ -3438,8 +7294,24 @@
       <c r="D28">
         <v>295</v>
       </c>
-    </row>
-    <row r="29" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F28">
+        <f t="shared" si="0"/>
+        <v>280.95</v>
+      </c>
+      <c r="H28">
+        <f t="shared" si="1"/>
+        <v>280.95238095238096</v>
+      </c>
+      <c r="I28">
+        <f t="shared" si="2"/>
+        <v>14.047619047619037</v>
+      </c>
+      <c r="J28">
+        <f t="shared" si="3"/>
+        <v>295</v>
+      </c>
+    </row>
+    <row r="29" spans="2:10">
       <c r="B29" t="s">
         <v>66</v>
       </c>
@@ -3449,8 +7321,24 @@
       <c r="D29">
         <v>295</v>
       </c>
-    </row>
-    <row r="30" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F29">
+        <f t="shared" si="0"/>
+        <v>280.95</v>
+      </c>
+      <c r="H29">
+        <f t="shared" si="1"/>
+        <v>280.95238095238096</v>
+      </c>
+      <c r="I29">
+        <f t="shared" si="2"/>
+        <v>14.047619047619037</v>
+      </c>
+      <c r="J29">
+        <f t="shared" si="3"/>
+        <v>295</v>
+      </c>
+    </row>
+    <row r="30" spans="2:10">
       <c r="B30" t="s">
         <v>35</v>
       </c>
@@ -3463,8 +7351,24 @@
       <c r="E30">
         <v>2</v>
       </c>
-    </row>
-    <row r="31" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F30">
+        <f t="shared" si="0"/>
+        <v>347.62</v>
+      </c>
+      <c r="H30">
+        <f t="shared" si="1"/>
+        <v>347.61904761904759</v>
+      </c>
+      <c r="I30">
+        <f t="shared" si="2"/>
+        <v>17.380952380952408</v>
+      </c>
+      <c r="J30">
+        <f t="shared" si="3"/>
+        <v>365</v>
+      </c>
+    </row>
+    <row r="31" spans="2:10">
       <c r="B31" t="s">
         <v>68</v>
       </c>
@@ -3474,8 +7378,24 @@
       <c r="D31">
         <v>425</v>
       </c>
-    </row>
-    <row r="32" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F31">
+        <f t="shared" si="0"/>
+        <v>404.76</v>
+      </c>
+      <c r="H31">
+        <f t="shared" si="1"/>
+        <v>404.76190476190476</v>
+      </c>
+      <c r="I31">
+        <f t="shared" si="2"/>
+        <v>20.238095238095241</v>
+      </c>
+      <c r="J31">
+        <f t="shared" si="3"/>
+        <v>425</v>
+      </c>
+    </row>
+    <row r="32" spans="2:10">
       <c r="B32" t="s">
         <v>67</v>
       </c>
@@ -3485,8 +7405,24 @@
       <c r="D32">
         <v>375</v>
       </c>
-    </row>
-    <row r="33" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F32">
+        <f t="shared" si="0"/>
+        <v>357.14</v>
+      </c>
+      <c r="H32">
+        <f t="shared" si="1"/>
+        <v>357.14285714285711</v>
+      </c>
+      <c r="I32">
+        <f t="shared" si="2"/>
+        <v>17.85714285714289</v>
+      </c>
+      <c r="J32">
+        <f t="shared" si="3"/>
+        <v>375</v>
+      </c>
+    </row>
+    <row r="33" spans="2:10">
       <c r="B33" t="s">
         <v>69</v>
       </c>
@@ -3496,8 +7432,24 @@
       <c r="D33">
         <v>365</v>
       </c>
-    </row>
-    <row r="34" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F33">
+        <f t="shared" si="0"/>
+        <v>347.62</v>
+      </c>
+      <c r="H33">
+        <f t="shared" si="1"/>
+        <v>347.61904761904759</v>
+      </c>
+      <c r="I33">
+        <f t="shared" si="2"/>
+        <v>17.380952380952408</v>
+      </c>
+      <c r="J33">
+        <f t="shared" si="3"/>
+        <v>365</v>
+      </c>
+    </row>
+    <row r="34" spans="2:10">
       <c r="B34" t="s">
         <v>35</v>
       </c>
@@ -3507,8 +7459,24 @@
       <c r="D34">
         <v>355</v>
       </c>
-    </row>
-    <row r="35" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F34">
+        <f t="shared" si="0"/>
+        <v>338.1</v>
+      </c>
+      <c r="H34">
+        <f t="shared" si="1"/>
+        <v>338.09523809523807</v>
+      </c>
+      <c r="I34">
+        <f t="shared" si="2"/>
+        <v>16.904761904761926</v>
+      </c>
+      <c r="J34">
+        <f t="shared" si="3"/>
+        <v>355</v>
+      </c>
+    </row>
+    <row r="35" spans="2:10">
       <c r="B35" t="s">
         <v>35</v>
       </c>
@@ -3518,8 +7486,24 @@
       <c r="D35">
         <v>365</v>
       </c>
-    </row>
-    <row r="36" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F35">
+        <f t="shared" si="0"/>
+        <v>347.62</v>
+      </c>
+      <c r="H35">
+        <f t="shared" si="1"/>
+        <v>347.61904761904759</v>
+      </c>
+      <c r="I35">
+        <f t="shared" si="2"/>
+        <v>17.380952380952408</v>
+      </c>
+      <c r="J35">
+        <f t="shared" si="3"/>
+        <v>365</v>
+      </c>
+    </row>
+    <row r="36" spans="2:10">
       <c r="B36" t="s">
         <v>15</v>
       </c>
@@ -3529,8 +7513,24 @@
       <c r="D36">
         <v>365</v>
       </c>
-    </row>
-    <row r="37" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F36">
+        <f t="shared" si="0"/>
+        <v>347.62</v>
+      </c>
+      <c r="H36">
+        <f t="shared" si="1"/>
+        <v>347.61904761904759</v>
+      </c>
+      <c r="I36">
+        <f t="shared" si="2"/>
+        <v>17.380952380952408</v>
+      </c>
+      <c r="J36">
+        <f t="shared" si="3"/>
+        <v>365</v>
+      </c>
+    </row>
+    <row r="37" spans="2:10">
       <c r="B37" t="s">
         <v>68</v>
       </c>
@@ -3540,8 +7540,24 @@
       <c r="D37">
         <v>395</v>
       </c>
-    </row>
-    <row r="38" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F37">
+        <f t="shared" si="0"/>
+        <v>376.19</v>
+      </c>
+      <c r="H37">
+        <f t="shared" si="1"/>
+        <v>376.19047619047615</v>
+      </c>
+      <c r="I37">
+        <f t="shared" si="2"/>
+        <v>18.809523809523853</v>
+      </c>
+      <c r="J37">
+        <f t="shared" si="3"/>
+        <v>395</v>
+      </c>
+    </row>
+    <row r="38" spans="2:10">
       <c r="B38" t="s">
         <v>33</v>
       </c>
@@ -3551,8 +7567,24 @@
       <c r="D38">
         <v>375</v>
       </c>
-    </row>
-    <row r="39" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F38">
+        <f t="shared" si="0"/>
+        <v>357.14</v>
+      </c>
+      <c r="H38">
+        <f t="shared" si="1"/>
+        <v>357.14285714285711</v>
+      </c>
+      <c r="I38">
+        <f t="shared" si="2"/>
+        <v>17.85714285714289</v>
+      </c>
+      <c r="J38">
+        <f t="shared" si="3"/>
+        <v>375</v>
+      </c>
+    </row>
+    <row r="39" spans="2:10">
       <c r="B39" t="s">
         <v>33</v>
       </c>
@@ -3562,8 +7594,24 @@
       <c r="D39">
         <v>355</v>
       </c>
-    </row>
-    <row r="40" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F39">
+        <f t="shared" si="0"/>
+        <v>338.1</v>
+      </c>
+      <c r="H39">
+        <f t="shared" si="1"/>
+        <v>338.09523809523807</v>
+      </c>
+      <c r="I39">
+        <f t="shared" si="2"/>
+        <v>16.904761904761926</v>
+      </c>
+      <c r="J39">
+        <f t="shared" si="3"/>
+        <v>355</v>
+      </c>
+    </row>
+    <row r="40" spans="2:10">
       <c r="B40" t="s">
         <v>70</v>
       </c>
@@ -3573,8 +7621,24 @@
       <c r="D40">
         <v>350</v>
       </c>
-    </row>
-    <row r="41" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F40">
+        <f t="shared" si="0"/>
+        <v>333.33</v>
+      </c>
+      <c r="H40">
+        <f t="shared" si="1"/>
+        <v>333.33333333333331</v>
+      </c>
+      <c r="I40">
+        <f t="shared" si="2"/>
+        <v>16.666666666666686</v>
+      </c>
+      <c r="J40">
+        <f t="shared" si="3"/>
+        <v>350</v>
+      </c>
+    </row>
+    <row r="41" spans="2:10">
       <c r="B41" t="s">
         <v>33</v>
       </c>
@@ -3584,8 +7648,24 @@
       <c r="D41">
         <v>355</v>
       </c>
-    </row>
-    <row r="42" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F41">
+        <f t="shared" si="0"/>
+        <v>338.1</v>
+      </c>
+      <c r="H41">
+        <f t="shared" si="1"/>
+        <v>338.09523809523807</v>
+      </c>
+      <c r="I41">
+        <f t="shared" si="2"/>
+        <v>16.904761904761926</v>
+      </c>
+      <c r="J41">
+        <f t="shared" si="3"/>
+        <v>355</v>
+      </c>
+    </row>
+    <row r="42" spans="2:10">
       <c r="B42" t="s">
         <v>35</v>
       </c>
@@ -3595,8 +7675,24 @@
       <c r="D42">
         <v>355</v>
       </c>
-    </row>
-    <row r="43" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F42">
+        <f t="shared" si="0"/>
+        <v>338.1</v>
+      </c>
+      <c r="H42">
+        <f t="shared" si="1"/>
+        <v>338.09523809523807</v>
+      </c>
+      <c r="I42">
+        <f t="shared" si="2"/>
+        <v>16.904761904761926</v>
+      </c>
+      <c r="J42">
+        <f t="shared" si="3"/>
+        <v>355</v>
+      </c>
+    </row>
+    <row r="43" spans="2:10">
       <c r="B43" t="s">
         <v>71</v>
       </c>
@@ -3606,8 +7702,24 @@
       <c r="D43">
         <v>675</v>
       </c>
-    </row>
-    <row r="44" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F43">
+        <f t="shared" si="0"/>
+        <v>642.86</v>
+      </c>
+      <c r="H43">
+        <f t="shared" si="1"/>
+        <v>642.85714285714278</v>
+      </c>
+      <c r="I43">
+        <f t="shared" si="2"/>
+        <v>32.142857142857224</v>
+      </c>
+      <c r="J43">
+        <f t="shared" si="3"/>
+        <v>675</v>
+      </c>
+    </row>
+    <row r="44" spans="2:10">
       <c r="B44" t="s">
         <v>68</v>
       </c>
@@ -3620,8 +7732,24 @@
       <c r="E44">
         <v>2</v>
       </c>
-    </row>
-    <row r="45" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F44">
+        <f t="shared" si="0"/>
+        <v>376.19</v>
+      </c>
+      <c r="H44">
+        <f t="shared" si="1"/>
+        <v>376.19047619047615</v>
+      </c>
+      <c r="I44">
+        <f t="shared" si="2"/>
+        <v>18.809523809523853</v>
+      </c>
+      <c r="J44">
+        <f t="shared" si="3"/>
+        <v>395</v>
+      </c>
+    </row>
+    <row r="45" spans="2:10">
       <c r="B45" t="s">
         <v>68</v>
       </c>
@@ -3631,8 +7759,24 @@
       <c r="D45">
         <v>425</v>
       </c>
-    </row>
-    <row r="46" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F45">
+        <f t="shared" si="0"/>
+        <v>404.76</v>
+      </c>
+      <c r="H45">
+        <f t="shared" si="1"/>
+        <v>404.76190476190476</v>
+      </c>
+      <c r="I45">
+        <f t="shared" si="2"/>
+        <v>20.238095238095241</v>
+      </c>
+      <c r="J45">
+        <f t="shared" si="3"/>
+        <v>425</v>
+      </c>
+    </row>
+    <row r="46" spans="2:10">
       <c r="B46" t="s">
         <v>68</v>
       </c>
@@ -3642,8 +7786,24 @@
       <c r="D46">
         <v>395</v>
       </c>
-    </row>
-    <row r="47" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F46">
+        <f t="shared" si="0"/>
+        <v>376.19</v>
+      </c>
+      <c r="H46">
+        <f t="shared" si="1"/>
+        <v>376.19047619047615</v>
+      </c>
+      <c r="I46">
+        <f t="shared" si="2"/>
+        <v>18.809523809523853</v>
+      </c>
+      <c r="J46">
+        <f t="shared" si="3"/>
+        <v>395</v>
+      </c>
+    </row>
+    <row r="47" spans="2:10">
       <c r="B47" t="s">
         <v>72</v>
       </c>
@@ -3653,8 +7813,24 @@
       <c r="D47">
         <v>325</v>
       </c>
-    </row>
-    <row r="48" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F47">
+        <f t="shared" si="0"/>
+        <v>309.52</v>
+      </c>
+      <c r="H47">
+        <f t="shared" si="1"/>
+        <v>309.52380952380952</v>
+      </c>
+      <c r="I47">
+        <f t="shared" si="2"/>
+        <v>15.476190476190482</v>
+      </c>
+      <c r="J47">
+        <f t="shared" si="3"/>
+        <v>325</v>
+      </c>
+    </row>
+    <row r="48" spans="2:10">
       <c r="B48" t="s">
         <v>35</v>
       </c>
@@ -3664,8 +7840,24 @@
       <c r="D48">
         <v>365</v>
       </c>
-    </row>
-    <row r="49" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F48">
+        <f t="shared" si="0"/>
+        <v>347.62</v>
+      </c>
+      <c r="H48">
+        <f t="shared" si="1"/>
+        <v>347.61904761904759</v>
+      </c>
+      <c r="I48">
+        <f t="shared" si="2"/>
+        <v>17.380952380952408</v>
+      </c>
+      <c r="J48">
+        <f t="shared" si="3"/>
+        <v>365</v>
+      </c>
+    </row>
+    <row r="49" spans="2:10">
       <c r="B49" t="s">
         <v>33</v>
       </c>
@@ -3675,8 +7867,24 @@
       <c r="D49">
         <v>375</v>
       </c>
-    </row>
-    <row r="50" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F49">
+        <f t="shared" si="0"/>
+        <v>357.14</v>
+      </c>
+      <c r="H49">
+        <f t="shared" si="1"/>
+        <v>357.14285714285711</v>
+      </c>
+      <c r="I49">
+        <f t="shared" si="2"/>
+        <v>17.85714285714289</v>
+      </c>
+      <c r="J49">
+        <f t="shared" si="3"/>
+        <v>375</v>
+      </c>
+    </row>
+    <row r="50" spans="2:10">
       <c r="B50" t="s">
         <v>73</v>
       </c>
@@ -3686,8 +7894,24 @@
       <c r="D50">
         <v>375</v>
       </c>
-    </row>
-    <row r="51" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F50">
+        <f t="shared" si="0"/>
+        <v>357.14</v>
+      </c>
+      <c r="H50">
+        <f t="shared" si="1"/>
+        <v>357.14285714285711</v>
+      </c>
+      <c r="I50">
+        <f t="shared" si="2"/>
+        <v>17.85714285714289</v>
+      </c>
+      <c r="J50">
+        <f t="shared" si="3"/>
+        <v>375</v>
+      </c>
+    </row>
+    <row r="51" spans="2:10">
       <c r="B51" t="s">
         <v>68</v>
       </c>
@@ -3697,8 +7921,24 @@
       <c r="D51">
         <v>395</v>
       </c>
-    </row>
-    <row r="52" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F51">
+        <f t="shared" si="0"/>
+        <v>376.19</v>
+      </c>
+      <c r="H51">
+        <f t="shared" si="1"/>
+        <v>376.19047619047615</v>
+      </c>
+      <c r="I51">
+        <f t="shared" si="2"/>
+        <v>18.809523809523853</v>
+      </c>
+      <c r="J51">
+        <f t="shared" si="3"/>
+        <v>395</v>
+      </c>
+    </row>
+    <row r="52" spans="2:10">
       <c r="B52" t="s">
         <v>16</v>
       </c>
@@ -3708,8 +7948,24 @@
       <c r="D52">
         <v>375</v>
       </c>
-    </row>
-    <row r="53" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F52">
+        <f t="shared" si="0"/>
+        <v>357.14</v>
+      </c>
+      <c r="H52">
+        <f t="shared" si="1"/>
+        <v>357.14285714285711</v>
+      </c>
+      <c r="I52">
+        <f t="shared" si="2"/>
+        <v>17.85714285714289</v>
+      </c>
+      <c r="J52">
+        <f t="shared" si="3"/>
+        <v>375</v>
+      </c>
+    </row>
+    <row r="53" spans="2:10">
       <c r="B53" t="s">
         <v>16</v>
       </c>
@@ -3719,8 +7975,24 @@
       <c r="D53">
         <v>675</v>
       </c>
-    </row>
-    <row r="54" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F53">
+        <f t="shared" si="0"/>
+        <v>642.86</v>
+      </c>
+      <c r="H53">
+        <f t="shared" si="1"/>
+        <v>642.85714285714278</v>
+      </c>
+      <c r="I53">
+        <f t="shared" si="2"/>
+        <v>32.142857142857224</v>
+      </c>
+      <c r="J53">
+        <f t="shared" si="3"/>
+        <v>675</v>
+      </c>
+    </row>
+    <row r="54" spans="2:10">
       <c r="B54" t="s">
         <v>68</v>
       </c>
@@ -3730,8 +8002,24 @@
       <c r="D54">
         <v>425</v>
       </c>
-    </row>
-    <row r="55" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F54">
+        <f t="shared" si="0"/>
+        <v>404.76</v>
+      </c>
+      <c r="H54">
+        <f t="shared" si="1"/>
+        <v>404.76190476190476</v>
+      </c>
+      <c r="I54">
+        <f t="shared" si="2"/>
+        <v>20.238095238095241</v>
+      </c>
+      <c r="J54">
+        <f t="shared" si="3"/>
+        <v>425</v>
+      </c>
+    </row>
+    <row r="55" spans="2:10">
       <c r="B55" t="s">
         <v>68</v>
       </c>
@@ -3741,8 +8029,24 @@
       <c r="D55">
         <v>395</v>
       </c>
-    </row>
-    <row r="56" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F55">
+        <f t="shared" si="0"/>
+        <v>376.19</v>
+      </c>
+      <c r="H55">
+        <f t="shared" si="1"/>
+        <v>376.19047619047615</v>
+      </c>
+      <c r="I55">
+        <f t="shared" si="2"/>
+        <v>18.809523809523853</v>
+      </c>
+      <c r="J55">
+        <f t="shared" si="3"/>
+        <v>395</v>
+      </c>
+    </row>
+    <row r="56" spans="2:10">
       <c r="B56" t="s">
         <v>33</v>
       </c>
@@ -3752,8 +8056,24 @@
       <c r="D56">
         <v>375</v>
       </c>
-    </row>
-    <row r="57" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F56">
+        <f t="shared" si="0"/>
+        <v>357.14</v>
+      </c>
+      <c r="H56">
+        <f t="shared" si="1"/>
+        <v>357.14285714285711</v>
+      </c>
+      <c r="I56">
+        <f t="shared" si="2"/>
+        <v>17.85714285714289</v>
+      </c>
+      <c r="J56">
+        <f t="shared" si="3"/>
+        <v>375</v>
+      </c>
+    </row>
+    <row r="57" spans="2:10">
       <c r="B57" t="s">
         <v>73</v>
       </c>
@@ -3763,8 +8083,24 @@
       <c r="D57">
         <v>375</v>
       </c>
-    </row>
-    <row r="58" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F57">
+        <f t="shared" si="0"/>
+        <v>357.14</v>
+      </c>
+      <c r="H57">
+        <f t="shared" si="1"/>
+        <v>357.14285714285711</v>
+      </c>
+      <c r="I57">
+        <f t="shared" si="2"/>
+        <v>17.85714285714289</v>
+      </c>
+      <c r="J57">
+        <f t="shared" si="3"/>
+        <v>375</v>
+      </c>
+    </row>
+    <row r="58" spans="2:10">
       <c r="B58" t="s">
         <v>74</v>
       </c>
@@ -3774,8 +8110,24 @@
       <c r="D58">
         <v>595</v>
       </c>
-    </row>
-    <row r="59" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F58">
+        <f t="shared" si="0"/>
+        <v>566.66999999999996</v>
+      </c>
+      <c r="H58">
+        <f t="shared" si="1"/>
+        <v>566.66666666666663</v>
+      </c>
+      <c r="I58">
+        <f t="shared" si="2"/>
+        <v>28.333333333333371</v>
+      </c>
+      <c r="J58">
+        <f t="shared" si="3"/>
+        <v>595</v>
+      </c>
+    </row>
+    <row r="59" spans="2:10">
       <c r="B59" t="s">
         <v>75</v>
       </c>
@@ -3785,8 +8137,24 @@
       <c r="D59">
         <v>375</v>
       </c>
-    </row>
-    <row r="60" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F59">
+        <f t="shared" si="0"/>
+        <v>357.14</v>
+      </c>
+      <c r="H59">
+        <f t="shared" si="1"/>
+        <v>357.14285714285711</v>
+      </c>
+      <c r="I59">
+        <f t="shared" si="2"/>
+        <v>17.85714285714289</v>
+      </c>
+      <c r="J59">
+        <f t="shared" si="3"/>
+        <v>375</v>
+      </c>
+    </row>
+    <row r="60" spans="2:10">
       <c r="B60" t="s">
         <v>68</v>
       </c>
@@ -3799,8 +8167,24 @@
       <c r="E60">
         <v>2</v>
       </c>
-    </row>
-    <row r="61" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F60">
+        <f t="shared" si="0"/>
+        <v>404.76</v>
+      </c>
+      <c r="H60">
+        <f t="shared" si="1"/>
+        <v>404.76190476190476</v>
+      </c>
+      <c r="I60">
+        <f t="shared" si="2"/>
+        <v>20.238095238095241</v>
+      </c>
+      <c r="J60">
+        <f t="shared" si="3"/>
+        <v>425</v>
+      </c>
+    </row>
+    <row r="61" spans="2:10">
       <c r="B61" t="s">
         <v>76</v>
       </c>
@@ -3810,8 +8194,24 @@
       <c r="D61">
         <v>350</v>
       </c>
-    </row>
-    <row r="62" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F61">
+        <f t="shared" si="0"/>
+        <v>333.33</v>
+      </c>
+      <c r="H61">
+        <f t="shared" si="1"/>
+        <v>333.33333333333331</v>
+      </c>
+      <c r="I61">
+        <f t="shared" si="2"/>
+        <v>16.666666666666686</v>
+      </c>
+      <c r="J61">
+        <f t="shared" si="3"/>
+        <v>350</v>
+      </c>
+    </row>
+    <row r="62" spans="2:10">
       <c r="B62" t="s">
         <v>68</v>
       </c>
@@ -3824,8 +8224,24 @@
       <c r="E62">
         <v>4</v>
       </c>
-    </row>
-    <row r="63" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F62">
+        <f t="shared" si="0"/>
+        <v>376.19</v>
+      </c>
+      <c r="H62">
+        <f t="shared" si="1"/>
+        <v>376.19047619047615</v>
+      </c>
+      <c r="I62">
+        <f t="shared" si="2"/>
+        <v>18.809523809523853</v>
+      </c>
+      <c r="J62">
+        <f t="shared" si="3"/>
+        <v>395</v>
+      </c>
+    </row>
+    <row r="63" spans="2:10">
       <c r="B63" t="s">
         <v>35</v>
       </c>
@@ -3835,8 +8251,24 @@
       <c r="D63">
         <v>355</v>
       </c>
-    </row>
-    <row r="64" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F63">
+        <f t="shared" si="0"/>
+        <v>338.1</v>
+      </c>
+      <c r="H63">
+        <f t="shared" si="1"/>
+        <v>338.09523809523807</v>
+      </c>
+      <c r="I63">
+        <f t="shared" si="2"/>
+        <v>16.904761904761926</v>
+      </c>
+      <c r="J63">
+        <f t="shared" si="3"/>
+        <v>355</v>
+      </c>
+    </row>
+    <row r="64" spans="2:10">
       <c r="B64" t="s">
         <v>35</v>
       </c>
@@ -3846,8 +8278,24 @@
       <c r="D64">
         <v>365</v>
       </c>
-    </row>
-    <row r="65" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="F64">
+        <f t="shared" si="0"/>
+        <v>347.62</v>
+      </c>
+      <c r="H64">
+        <f t="shared" si="1"/>
+        <v>347.61904761904759</v>
+      </c>
+      <c r="I64">
+        <f t="shared" si="2"/>
+        <v>17.380952380952408</v>
+      </c>
+      <c r="J64">
+        <f t="shared" si="3"/>
+        <v>365</v>
+      </c>
+    </row>
+    <row r="65" spans="2:10">
       <c r="B65" t="s">
         <v>77</v>
       </c>
@@ -3857,8 +8305,24 @@
       <c r="D65">
         <v>350</v>
       </c>
-    </row>
-    <row r="66" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="F65">
+        <f t="shared" si="0"/>
+        <v>333.33</v>
+      </c>
+      <c r="H65">
+        <f t="shared" si="1"/>
+        <v>333.33333333333331</v>
+      </c>
+      <c r="I65">
+        <f t="shared" si="2"/>
+        <v>16.666666666666686</v>
+      </c>
+      <c r="J65">
+        <f t="shared" si="3"/>
+        <v>350</v>
+      </c>
+    </row>
+    <row r="66" spans="2:10">
       <c r="B66" t="s">
         <v>78</v>
       </c>
@@ -3868,8 +8332,24 @@
       <c r="D66">
         <v>325</v>
       </c>
-    </row>
-    <row r="67" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="F66">
+        <f t="shared" si="0"/>
+        <v>309.52</v>
+      </c>
+      <c r="H66">
+        <f t="shared" si="1"/>
+        <v>309.52380952380952</v>
+      </c>
+      <c r="I66">
+        <f t="shared" si="2"/>
+        <v>15.476190476190482</v>
+      </c>
+      <c r="J66">
+        <f t="shared" si="3"/>
+        <v>325</v>
+      </c>
+    </row>
+    <row r="67" spans="2:10">
       <c r="B67" t="s">
         <v>72</v>
       </c>
@@ -3879,8 +8359,24 @@
       <c r="D67">
         <v>365</v>
       </c>
-    </row>
-    <row r="68" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="F67">
+        <f t="shared" ref="F67:F110" si="4">ROUND(IF(D67&gt;2500, D67/1.18, D67/1.05),2)</f>
+        <v>347.62</v>
+      </c>
+      <c r="H67">
+        <f t="shared" ref="H67:H110" si="5">D67/1.05</f>
+        <v>347.61904761904759</v>
+      </c>
+      <c r="I67">
+        <f t="shared" ref="I67:I110" si="6">D67-H67</f>
+        <v>17.380952380952408</v>
+      </c>
+      <c r="J67">
+        <f t="shared" ref="J67:J110" si="7">SUM(H67:I67)</f>
+        <v>365</v>
+      </c>
+    </row>
+    <row r="68" spans="2:10">
       <c r="B68" t="s">
         <v>15</v>
       </c>
@@ -3890,8 +8386,24 @@
       <c r="D68">
         <v>365</v>
       </c>
-    </row>
-    <row r="69" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="F68">
+        <f t="shared" si="4"/>
+        <v>347.62</v>
+      </c>
+      <c r="H68">
+        <f t="shared" si="5"/>
+        <v>347.61904761904759</v>
+      </c>
+      <c r="I68">
+        <f t="shared" si="6"/>
+        <v>17.380952380952408</v>
+      </c>
+      <c r="J68">
+        <f t="shared" si="7"/>
+        <v>365</v>
+      </c>
+    </row>
+    <row r="69" spans="2:10">
       <c r="B69" t="s">
         <v>68</v>
       </c>
@@ -3901,8 +8413,24 @@
       <c r="D69">
         <v>395</v>
       </c>
-    </row>
-    <row r="70" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="F69">
+        <f t="shared" si="4"/>
+        <v>376.19</v>
+      </c>
+      <c r="H69">
+        <f t="shared" si="5"/>
+        <v>376.19047619047615</v>
+      </c>
+      <c r="I69">
+        <f t="shared" si="6"/>
+        <v>18.809523809523853</v>
+      </c>
+      <c r="J69">
+        <f t="shared" si="7"/>
+        <v>395</v>
+      </c>
+    </row>
+    <row r="70" spans="2:10">
       <c r="B70" t="s">
         <v>35</v>
       </c>
@@ -3912,8 +8440,24 @@
       <c r="D70">
         <v>545</v>
       </c>
-    </row>
-    <row r="71" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="F70">
+        <f t="shared" si="4"/>
+        <v>519.04999999999995</v>
+      </c>
+      <c r="H70">
+        <f t="shared" si="5"/>
+        <v>519.04761904761904</v>
+      </c>
+      <c r="I70">
+        <f t="shared" si="6"/>
+        <v>25.952380952380963</v>
+      </c>
+      <c r="J70">
+        <f t="shared" si="7"/>
+        <v>545</v>
+      </c>
+    </row>
+    <row r="71" spans="2:10">
       <c r="B71" t="s">
         <v>68</v>
       </c>
@@ -3923,8 +8467,24 @@
       <c r="D71">
         <v>395</v>
       </c>
-    </row>
-    <row r="72" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="F71">
+        <f t="shared" si="4"/>
+        <v>376.19</v>
+      </c>
+      <c r="H71">
+        <f t="shared" si="5"/>
+        <v>376.19047619047615</v>
+      </c>
+      <c r="I71">
+        <f t="shared" si="6"/>
+        <v>18.809523809523853</v>
+      </c>
+      <c r="J71">
+        <f t="shared" si="7"/>
+        <v>395</v>
+      </c>
+    </row>
+    <row r="72" spans="2:10">
       <c r="B72" t="s">
         <v>35</v>
       </c>
@@ -3934,8 +8494,24 @@
       <c r="D72">
         <v>365</v>
       </c>
-    </row>
-    <row r="73" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="F72">
+        <f t="shared" si="4"/>
+        <v>347.62</v>
+      </c>
+      <c r="H72">
+        <f t="shared" si="5"/>
+        <v>347.61904761904759</v>
+      </c>
+      <c r="I72">
+        <f t="shared" si="6"/>
+        <v>17.380952380952408</v>
+      </c>
+      <c r="J72">
+        <f t="shared" si="7"/>
+        <v>365</v>
+      </c>
+    </row>
+    <row r="73" spans="2:10">
       <c r="B73" t="s">
         <v>68</v>
       </c>
@@ -3945,8 +8521,24 @@
       <c r="D73">
         <v>395</v>
       </c>
-    </row>
-    <row r="74" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="F73">
+        <f t="shared" si="4"/>
+        <v>376.19</v>
+      </c>
+      <c r="H73">
+        <f t="shared" si="5"/>
+        <v>376.19047619047615</v>
+      </c>
+      <c r="I73">
+        <f t="shared" si="6"/>
+        <v>18.809523809523853</v>
+      </c>
+      <c r="J73">
+        <f t="shared" si="7"/>
+        <v>395</v>
+      </c>
+    </row>
+    <row r="74" spans="2:10">
       <c r="B74" t="s">
         <v>16</v>
       </c>
@@ -3956,8 +8548,24 @@
       <c r="D74">
         <v>375</v>
       </c>
-    </row>
-    <row r="75" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="F74">
+        <f t="shared" si="4"/>
+        <v>357.14</v>
+      </c>
+      <c r="H74">
+        <f t="shared" si="5"/>
+        <v>357.14285714285711</v>
+      </c>
+      <c r="I74">
+        <f t="shared" si="6"/>
+        <v>17.85714285714289</v>
+      </c>
+      <c r="J74">
+        <f t="shared" si="7"/>
+        <v>375</v>
+      </c>
+    </row>
+    <row r="75" spans="2:10">
       <c r="B75" t="s">
         <v>16</v>
       </c>
@@ -3967,8 +8575,24 @@
       <c r="D75">
         <v>305</v>
       </c>
-    </row>
-    <row r="76" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="F75">
+        <f t="shared" si="4"/>
+        <v>290.48</v>
+      </c>
+      <c r="H75">
+        <f t="shared" si="5"/>
+        <v>290.47619047619048</v>
+      </c>
+      <c r="I75">
+        <f t="shared" si="6"/>
+        <v>14.523809523809518</v>
+      </c>
+      <c r="J75">
+        <f t="shared" si="7"/>
+        <v>305</v>
+      </c>
+    </row>
+    <row r="76" spans="2:10">
       <c r="B76" t="s">
         <v>16</v>
       </c>
@@ -3978,8 +8602,24 @@
       <c r="D76">
         <v>375</v>
       </c>
-    </row>
-    <row r="77" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="F76">
+        <f t="shared" si="4"/>
+        <v>357.14</v>
+      </c>
+      <c r="H76">
+        <f t="shared" si="5"/>
+        <v>357.14285714285711</v>
+      </c>
+      <c r="I76">
+        <f t="shared" si="6"/>
+        <v>17.85714285714289</v>
+      </c>
+      <c r="J76">
+        <f t="shared" si="7"/>
+        <v>375</v>
+      </c>
+    </row>
+    <row r="77" spans="2:10">
       <c r="B77" t="s">
         <v>35</v>
       </c>
@@ -3989,8 +8629,24 @@
       <c r="D77">
         <v>355</v>
       </c>
-    </row>
-    <row r="78" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="F77">
+        <f t="shared" si="4"/>
+        <v>338.1</v>
+      </c>
+      <c r="H77">
+        <f t="shared" si="5"/>
+        <v>338.09523809523807</v>
+      </c>
+      <c r="I77">
+        <f t="shared" si="6"/>
+        <v>16.904761904761926</v>
+      </c>
+      <c r="J77">
+        <f t="shared" si="7"/>
+        <v>355</v>
+      </c>
+    </row>
+    <row r="78" spans="2:10">
       <c r="B78" t="s">
         <v>16</v>
       </c>
@@ -4000,8 +8656,24 @@
       <c r="D78">
         <v>375</v>
       </c>
-    </row>
-    <row r="79" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="F78">
+        <f t="shared" si="4"/>
+        <v>357.14</v>
+      </c>
+      <c r="H78">
+        <f t="shared" si="5"/>
+        <v>357.14285714285711</v>
+      </c>
+      <c r="I78">
+        <f t="shared" si="6"/>
+        <v>17.85714285714289</v>
+      </c>
+      <c r="J78">
+        <f t="shared" si="7"/>
+        <v>375</v>
+      </c>
+    </row>
+    <row r="79" spans="2:10">
       <c r="B79" t="s">
         <v>35</v>
       </c>
@@ -4011,8 +8683,24 @@
       <c r="D79">
         <v>365</v>
       </c>
-    </row>
-    <row r="80" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="F79">
+        <f t="shared" si="4"/>
+        <v>347.62</v>
+      </c>
+      <c r="H79">
+        <f t="shared" si="5"/>
+        <v>347.61904761904759</v>
+      </c>
+      <c r="I79">
+        <f t="shared" si="6"/>
+        <v>17.380952380952408</v>
+      </c>
+      <c r="J79">
+        <f t="shared" si="7"/>
+        <v>365</v>
+      </c>
+    </row>
+    <row r="80" spans="2:10">
       <c r="B80" t="s">
         <v>15</v>
       </c>
@@ -4022,8 +8710,24 @@
       <c r="D80">
         <v>365</v>
       </c>
-    </row>
-    <row r="81" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F80">
+        <f t="shared" si="4"/>
+        <v>347.62</v>
+      </c>
+      <c r="H80">
+        <f t="shared" si="5"/>
+        <v>347.61904761904759</v>
+      </c>
+      <c r="I80">
+        <f t="shared" si="6"/>
+        <v>17.380952380952408</v>
+      </c>
+      <c r="J80">
+        <f t="shared" si="7"/>
+        <v>365</v>
+      </c>
+    </row>
+    <row r="81" spans="2:10">
       <c r="B81" t="s">
         <v>35</v>
       </c>
@@ -4033,8 +8737,24 @@
       <c r="D81">
         <v>355</v>
       </c>
-    </row>
-    <row r="82" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F81">
+        <f t="shared" si="4"/>
+        <v>338.1</v>
+      </c>
+      <c r="H81">
+        <f t="shared" si="5"/>
+        <v>338.09523809523807</v>
+      </c>
+      <c r="I81">
+        <f t="shared" si="6"/>
+        <v>16.904761904761926</v>
+      </c>
+      <c r="J81">
+        <f t="shared" si="7"/>
+        <v>355</v>
+      </c>
+    </row>
+    <row r="82" spans="2:10">
       <c r="B82" t="s">
         <v>68</v>
       </c>
@@ -4044,8 +8764,24 @@
       <c r="D82">
         <v>395</v>
       </c>
-    </row>
-    <row r="83" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F82">
+        <f t="shared" si="4"/>
+        <v>376.19</v>
+      </c>
+      <c r="H82">
+        <f t="shared" si="5"/>
+        <v>376.19047619047615</v>
+      </c>
+      <c r="I82">
+        <f t="shared" si="6"/>
+        <v>18.809523809523853</v>
+      </c>
+      <c r="J82">
+        <f t="shared" si="7"/>
+        <v>395</v>
+      </c>
+    </row>
+    <row r="83" spans="2:10">
       <c r="B83" t="s">
         <v>15</v>
       </c>
@@ -4055,8 +8791,24 @@
       <c r="D83">
         <v>365</v>
       </c>
-    </row>
-    <row r="84" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F83">
+        <f t="shared" si="4"/>
+        <v>347.62</v>
+      </c>
+      <c r="H83">
+        <f t="shared" si="5"/>
+        <v>347.61904761904759</v>
+      </c>
+      <c r="I83">
+        <f t="shared" si="6"/>
+        <v>17.380952380952408</v>
+      </c>
+      <c r="J83">
+        <f t="shared" si="7"/>
+        <v>365</v>
+      </c>
+    </row>
+    <row r="84" spans="2:10">
       <c r="B84" t="s">
         <v>16</v>
       </c>
@@ -4066,8 +8818,24 @@
       <c r="D84">
         <v>375</v>
       </c>
-    </row>
-    <row r="85" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F84">
+        <f t="shared" si="4"/>
+        <v>357.14</v>
+      </c>
+      <c r="H84">
+        <f t="shared" si="5"/>
+        <v>357.14285714285711</v>
+      </c>
+      <c r="I84">
+        <f t="shared" si="6"/>
+        <v>17.85714285714289</v>
+      </c>
+      <c r="J84">
+        <f t="shared" si="7"/>
+        <v>375</v>
+      </c>
+    </row>
+    <row r="85" spans="2:10">
       <c r="B85" t="s">
         <v>35</v>
       </c>
@@ -4077,8 +8845,24 @@
       <c r="D85">
         <v>375</v>
       </c>
-    </row>
-    <row r="86" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F85">
+        <f t="shared" si="4"/>
+        <v>357.14</v>
+      </c>
+      <c r="H85">
+        <f t="shared" si="5"/>
+        <v>357.14285714285711</v>
+      </c>
+      <c r="I85">
+        <f t="shared" si="6"/>
+        <v>17.85714285714289</v>
+      </c>
+      <c r="J85">
+        <f t="shared" si="7"/>
+        <v>375</v>
+      </c>
+    </row>
+    <row r="86" spans="2:10">
       <c r="B86" t="s">
         <v>16</v>
       </c>
@@ -4088,8 +8872,24 @@
       <c r="D86">
         <v>375</v>
       </c>
-    </row>
-    <row r="87" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F86">
+        <f t="shared" si="4"/>
+        <v>357.14</v>
+      </c>
+      <c r="H86">
+        <f t="shared" si="5"/>
+        <v>357.14285714285711</v>
+      </c>
+      <c r="I86">
+        <f t="shared" si="6"/>
+        <v>17.85714285714289</v>
+      </c>
+      <c r="J86">
+        <f t="shared" si="7"/>
+        <v>375</v>
+      </c>
+    </row>
+    <row r="87" spans="2:10">
       <c r="B87" t="s">
         <v>35</v>
       </c>
@@ -4099,8 +8899,24 @@
       <c r="D87">
         <v>350</v>
       </c>
-    </row>
-    <row r="88" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F87">
+        <f t="shared" si="4"/>
+        <v>333.33</v>
+      </c>
+      <c r="H87">
+        <f t="shared" si="5"/>
+        <v>333.33333333333331</v>
+      </c>
+      <c r="I87">
+        <f t="shared" si="6"/>
+        <v>16.666666666666686</v>
+      </c>
+      <c r="J87">
+        <f t="shared" si="7"/>
+        <v>350</v>
+      </c>
+    </row>
+    <row r="88" spans="2:10">
       <c r="B88" t="s">
         <v>73</v>
       </c>
@@ -4110,8 +8926,24 @@
       <c r="D88">
         <v>305</v>
       </c>
-    </row>
-    <row r="89" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F88">
+        <f t="shared" si="4"/>
+        <v>290.48</v>
+      </c>
+      <c r="H88">
+        <f t="shared" si="5"/>
+        <v>290.47619047619048</v>
+      </c>
+      <c r="I88">
+        <f t="shared" si="6"/>
+        <v>14.523809523809518</v>
+      </c>
+      <c r="J88">
+        <f t="shared" si="7"/>
+        <v>305</v>
+      </c>
+    </row>
+    <row r="89" spans="2:10">
       <c r="B89" t="s">
         <v>68</v>
       </c>
@@ -4124,8 +8956,24 @@
       <c r="E89">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F89">
+        <f t="shared" si="4"/>
+        <v>376.19</v>
+      </c>
+      <c r="H89">
+        <f t="shared" si="5"/>
+        <v>376.19047619047615</v>
+      </c>
+      <c r="I89">
+        <f t="shared" si="6"/>
+        <v>18.809523809523853</v>
+      </c>
+      <c r="J89">
+        <f t="shared" si="7"/>
+        <v>395</v>
+      </c>
+    </row>
+    <row r="90" spans="2:10">
       <c r="B90" t="s">
         <v>35</v>
       </c>
@@ -4135,8 +8983,24 @@
       <c r="D90">
         <v>355</v>
       </c>
-    </row>
-    <row r="91" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F90">
+        <f t="shared" si="4"/>
+        <v>338.1</v>
+      </c>
+      <c r="H90">
+        <f t="shared" si="5"/>
+        <v>338.09523809523807</v>
+      </c>
+      <c r="I90">
+        <f t="shared" si="6"/>
+        <v>16.904761904761926</v>
+      </c>
+      <c r="J90">
+        <f t="shared" si="7"/>
+        <v>355</v>
+      </c>
+    </row>
+    <row r="91" spans="2:10">
       <c r="B91" t="s">
         <v>35</v>
       </c>
@@ -4146,8 +9010,24 @@
       <c r="D91">
         <v>355</v>
       </c>
-    </row>
-    <row r="92" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F91">
+        <f t="shared" si="4"/>
+        <v>338.1</v>
+      </c>
+      <c r="H91">
+        <f t="shared" si="5"/>
+        <v>338.09523809523807</v>
+      </c>
+      <c r="I91">
+        <f t="shared" si="6"/>
+        <v>16.904761904761926</v>
+      </c>
+      <c r="J91">
+        <f t="shared" si="7"/>
+        <v>355</v>
+      </c>
+    </row>
+    <row r="92" spans="2:10">
       <c r="B92" t="s">
         <v>15</v>
       </c>
@@ -4157,8 +9037,24 @@
       <c r="D92">
         <v>365</v>
       </c>
-    </row>
-    <row r="93" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F92">
+        <f t="shared" si="4"/>
+        <v>347.62</v>
+      </c>
+      <c r="H92">
+        <f t="shared" si="5"/>
+        <v>347.61904761904759</v>
+      </c>
+      <c r="I92">
+        <f t="shared" si="6"/>
+        <v>17.380952380952408</v>
+      </c>
+      <c r="J92">
+        <f t="shared" si="7"/>
+        <v>365</v>
+      </c>
+    </row>
+    <row r="93" spans="2:10">
       <c r="B93" t="s">
         <v>35</v>
       </c>
@@ -4168,8 +9064,24 @@
       <c r="D93">
         <v>355</v>
       </c>
-    </row>
-    <row r="94" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F93">
+        <f t="shared" si="4"/>
+        <v>338.1</v>
+      </c>
+      <c r="H93">
+        <f t="shared" si="5"/>
+        <v>338.09523809523807</v>
+      </c>
+      <c r="I93">
+        <f t="shared" si="6"/>
+        <v>16.904761904761926</v>
+      </c>
+      <c r="J93">
+        <f t="shared" si="7"/>
+        <v>355</v>
+      </c>
+    </row>
+    <row r="94" spans="2:10">
       <c r="B94" t="s">
         <v>35</v>
       </c>
@@ -4179,8 +9091,24 @@
       <c r="D94">
         <v>365</v>
       </c>
-    </row>
-    <row r="95" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F94">
+        <f t="shared" si="4"/>
+        <v>347.62</v>
+      </c>
+      <c r="H94">
+        <f t="shared" si="5"/>
+        <v>347.61904761904759</v>
+      </c>
+      <c r="I94">
+        <f t="shared" si="6"/>
+        <v>17.380952380952408</v>
+      </c>
+      <c r="J94">
+        <f t="shared" si="7"/>
+        <v>365</v>
+      </c>
+    </row>
+    <row r="95" spans="2:10">
       <c r="B95" t="s">
         <v>16</v>
       </c>
@@ -4190,8 +9118,24 @@
       <c r="D95">
         <v>275</v>
       </c>
-    </row>
-    <row r="96" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F95">
+        <f t="shared" si="4"/>
+        <v>261.89999999999998</v>
+      </c>
+      <c r="H95">
+        <f t="shared" si="5"/>
+        <v>261.90476190476187</v>
+      </c>
+      <c r="I95">
+        <f t="shared" si="6"/>
+        <v>13.09523809523813</v>
+      </c>
+      <c r="J95">
+        <f t="shared" si="7"/>
+        <v>275</v>
+      </c>
+    </row>
+    <row r="96" spans="2:10">
       <c r="B96" t="s">
         <v>68</v>
       </c>
@@ -4201,8 +9145,24 @@
       <c r="D96">
         <v>395</v>
       </c>
-    </row>
-    <row r="97" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F96">
+        <f t="shared" si="4"/>
+        <v>376.19</v>
+      </c>
+      <c r="H96">
+        <f t="shared" si="5"/>
+        <v>376.19047619047615</v>
+      </c>
+      <c r="I96">
+        <f t="shared" si="6"/>
+        <v>18.809523809523853</v>
+      </c>
+      <c r="J96">
+        <f t="shared" si="7"/>
+        <v>395</v>
+      </c>
+    </row>
+    <row r="97" spans="2:10">
       <c r="B97" t="s">
         <v>73</v>
       </c>
@@ -4212,8 +9172,24 @@
       <c r="D97">
         <v>325</v>
       </c>
-    </row>
-    <row r="98" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F97">
+        <f t="shared" si="4"/>
+        <v>309.52</v>
+      </c>
+      <c r="H97">
+        <f t="shared" si="5"/>
+        <v>309.52380952380952</v>
+      </c>
+      <c r="I97">
+        <f t="shared" si="6"/>
+        <v>15.476190476190482</v>
+      </c>
+      <c r="J97">
+        <f t="shared" si="7"/>
+        <v>325</v>
+      </c>
+    </row>
+    <row r="98" spans="2:10">
       <c r="B98" t="s">
         <v>16</v>
       </c>
@@ -4223,8 +9199,24 @@
       <c r="D98">
         <v>675</v>
       </c>
-    </row>
-    <row r="99" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F98">
+        <f t="shared" si="4"/>
+        <v>642.86</v>
+      </c>
+      <c r="H98">
+        <f t="shared" si="5"/>
+        <v>642.85714285714278</v>
+      </c>
+      <c r="I98">
+        <f t="shared" si="6"/>
+        <v>32.142857142857224</v>
+      </c>
+      <c r="J98">
+        <f t="shared" si="7"/>
+        <v>675</v>
+      </c>
+    </row>
+    <row r="99" spans="2:10">
       <c r="B99" t="s">
         <v>35</v>
       </c>
@@ -4234,8 +9226,24 @@
       <c r="D99">
         <v>365</v>
       </c>
-    </row>
-    <row r="100" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F99">
+        <f t="shared" si="4"/>
+        <v>347.62</v>
+      </c>
+      <c r="H99">
+        <f t="shared" si="5"/>
+        <v>347.61904761904759</v>
+      </c>
+      <c r="I99">
+        <f t="shared" si="6"/>
+        <v>17.380952380952408</v>
+      </c>
+      <c r="J99">
+        <f t="shared" si="7"/>
+        <v>365</v>
+      </c>
+    </row>
+    <row r="100" spans="2:10">
       <c r="B100" t="s">
         <v>78</v>
       </c>
@@ -4245,8 +9253,24 @@
       <c r="D100">
         <v>325</v>
       </c>
-    </row>
-    <row r="101" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F100">
+        <f t="shared" si="4"/>
+        <v>309.52</v>
+      </c>
+      <c r="H100">
+        <f t="shared" si="5"/>
+        <v>309.52380952380952</v>
+      </c>
+      <c r="I100">
+        <f t="shared" si="6"/>
+        <v>15.476190476190482</v>
+      </c>
+      <c r="J100">
+        <f t="shared" si="7"/>
+        <v>325</v>
+      </c>
+    </row>
+    <row r="101" spans="2:10">
       <c r="B101" t="s">
         <v>15</v>
       </c>
@@ -4256,8 +9280,24 @@
       <c r="D101">
         <v>365</v>
       </c>
-    </row>
-    <row r="102" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F101">
+        <f t="shared" si="4"/>
+        <v>347.62</v>
+      </c>
+      <c r="H101">
+        <f t="shared" si="5"/>
+        <v>347.61904761904759</v>
+      </c>
+      <c r="I101">
+        <f t="shared" si="6"/>
+        <v>17.380952380952408</v>
+      </c>
+      <c r="J101">
+        <f t="shared" si="7"/>
+        <v>365</v>
+      </c>
+    </row>
+    <row r="102" spans="2:10">
       <c r="B102" t="s">
         <v>69</v>
       </c>
@@ -4267,8 +9307,24 @@
       <c r="D102">
         <v>365</v>
       </c>
-    </row>
-    <row r="103" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F102">
+        <f t="shared" si="4"/>
+        <v>347.62</v>
+      </c>
+      <c r="H102">
+        <f t="shared" si="5"/>
+        <v>347.61904761904759</v>
+      </c>
+      <c r="I102">
+        <f t="shared" si="6"/>
+        <v>17.380952380952408</v>
+      </c>
+      <c r="J102">
+        <f t="shared" si="7"/>
+        <v>365</v>
+      </c>
+    </row>
+    <row r="103" spans="2:10">
       <c r="B103" t="s">
         <v>33</v>
       </c>
@@ -4278,8 +9334,24 @@
       <c r="D103">
         <v>375</v>
       </c>
-    </row>
-    <row r="104" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F103">
+        <f t="shared" si="4"/>
+        <v>357.14</v>
+      </c>
+      <c r="H103">
+        <f t="shared" si="5"/>
+        <v>357.14285714285711</v>
+      </c>
+      <c r="I103">
+        <f t="shared" si="6"/>
+        <v>17.85714285714289</v>
+      </c>
+      <c r="J103">
+        <f t="shared" si="7"/>
+        <v>375</v>
+      </c>
+    </row>
+    <row r="104" spans="2:10">
       <c r="B104" t="s">
         <v>68</v>
       </c>
@@ -4292,8 +9364,24 @@
       <c r="E104">
         <v>2</v>
       </c>
-    </row>
-    <row r="105" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F104">
+        <f t="shared" si="4"/>
+        <v>376.19</v>
+      </c>
+      <c r="H104">
+        <f t="shared" si="5"/>
+        <v>376.19047619047615</v>
+      </c>
+      <c r="I104">
+        <f t="shared" si="6"/>
+        <v>18.809523809523853</v>
+      </c>
+      <c r="J104">
+        <f t="shared" si="7"/>
+        <v>395</v>
+      </c>
+    </row>
+    <row r="105" spans="2:10">
       <c r="B105" t="s">
         <v>35</v>
       </c>
@@ -4303,8 +9391,24 @@
       <c r="D105">
         <v>355</v>
       </c>
-    </row>
-    <row r="106" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F105">
+        <f t="shared" si="4"/>
+        <v>338.1</v>
+      </c>
+      <c r="H105">
+        <f t="shared" si="5"/>
+        <v>338.09523809523807</v>
+      </c>
+      <c r="I105">
+        <f t="shared" si="6"/>
+        <v>16.904761904761926</v>
+      </c>
+      <c r="J105">
+        <f t="shared" si="7"/>
+        <v>355</v>
+      </c>
+    </row>
+    <row r="106" spans="2:10">
       <c r="B106" t="s">
         <v>68</v>
       </c>
@@ -4314,8 +9418,24 @@
       <c r="D106">
         <v>395</v>
       </c>
-    </row>
-    <row r="107" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F106">
+        <f t="shared" si="4"/>
+        <v>376.19</v>
+      </c>
+      <c r="H106">
+        <f t="shared" si="5"/>
+        <v>376.19047619047615</v>
+      </c>
+      <c r="I106">
+        <f t="shared" si="6"/>
+        <v>18.809523809523853</v>
+      </c>
+      <c r="J106">
+        <f t="shared" si="7"/>
+        <v>395</v>
+      </c>
+    </row>
+    <row r="107" spans="2:10">
       <c r="B107" t="s">
         <v>76</v>
       </c>
@@ -4325,8 +9445,24 @@
       <c r="D107">
         <v>350</v>
       </c>
-    </row>
-    <row r="108" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F107">
+        <f t="shared" si="4"/>
+        <v>333.33</v>
+      </c>
+      <c r="H107">
+        <f t="shared" si="5"/>
+        <v>333.33333333333331</v>
+      </c>
+      <c r="I107">
+        <f t="shared" si="6"/>
+        <v>16.666666666666686</v>
+      </c>
+      <c r="J107">
+        <f t="shared" si="7"/>
+        <v>350</v>
+      </c>
+    </row>
+    <row r="108" spans="2:10">
       <c r="B108" t="s">
         <v>68</v>
       </c>
@@ -4336,8 +9472,24 @@
       <c r="D108">
         <v>395</v>
       </c>
-    </row>
-    <row r="109" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F108">
+        <f t="shared" si="4"/>
+        <v>376.19</v>
+      </c>
+      <c r="H108">
+        <f t="shared" si="5"/>
+        <v>376.19047619047615</v>
+      </c>
+      <c r="I108">
+        <f t="shared" si="6"/>
+        <v>18.809523809523853</v>
+      </c>
+      <c r="J108">
+        <f t="shared" si="7"/>
+        <v>395</v>
+      </c>
+    </row>
+    <row r="109" spans="2:10">
       <c r="B109" t="s">
         <v>35</v>
       </c>
@@ -4347,8 +9499,24 @@
       <c r="D109">
         <v>365</v>
       </c>
-    </row>
-    <row r="110" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F109">
+        <f t="shared" si="4"/>
+        <v>347.62</v>
+      </c>
+      <c r="H109">
+        <f t="shared" si="5"/>
+        <v>347.61904761904759</v>
+      </c>
+      <c r="I109">
+        <f t="shared" si="6"/>
+        <v>17.380952380952408</v>
+      </c>
+      <c r="J109">
+        <f t="shared" si="7"/>
+        <v>365</v>
+      </c>
+    </row>
+    <row r="110" spans="2:10">
       <c r="B110" t="s">
         <v>15</v>
       </c>
@@ -4356,6 +9524,22 @@
         <v>4223</v>
       </c>
       <c r="D110">
+        <v>975</v>
+      </c>
+      <c r="F110">
+        <f t="shared" si="4"/>
+        <v>928.57</v>
+      </c>
+      <c r="H110">
+        <f t="shared" si="5"/>
+        <v>928.57142857142856</v>
+      </c>
+      <c r="I110">
+        <f t="shared" si="6"/>
+        <v>46.428571428571445</v>
+      </c>
+      <c r="J110">
+        <f t="shared" si="7"/>
         <v>975</v>
       </c>
     </row>
@@ -4365,252 +9549,585 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B6EA3588-AA57-40AD-BC31-AB6393E744F0}">
-  <dimension ref="A1:E21"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A3:J23"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="6.85546875" customWidth="1"/>
     <col min="2" max="2" width="20.42578125" customWidth="1"/>
     <col min="3" max="3" width="10.140625" customWidth="1"/>
+    <col min="6" max="6" width="27.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+    <row r="3" spans="1:10">
+      <c r="A3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C2">
-        <v>4221</v>
-      </c>
-      <c r="D2">
-        <v>675</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B3" t="s">
-        <v>35</v>
-      </c>
-      <c r="C3">
-        <v>4236</v>
-      </c>
-      <c r="D3">
-        <v>365</v>
-      </c>
-      <c r="E3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F3" t="s">
+        <v>82</v>
+      </c>
+      <c r="H3" t="s">
+        <v>83</v>
+      </c>
+      <c r="I3" t="s">
+        <v>84</v>
+      </c>
+      <c r="J3" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
       <c r="B4" t="s">
         <v>16</v>
       </c>
       <c r="C4">
-        <v>4230</v>
+        <v>4221</v>
       </c>
       <c r="D4">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+        <v>675</v>
+      </c>
+      <c r="F4">
+        <f>ROUND(IF(D4&gt;2500, D4/1.18, D4/1.05),2)</f>
+        <v>642.86</v>
+      </c>
+      <c r="H4">
+        <f>D4/1.05</f>
+        <v>642.85714285714278</v>
+      </c>
+      <c r="I4">
+        <f>D4-H4</f>
+        <v>32.142857142857224</v>
+      </c>
+      <c r="J4">
+        <f>H4+I4</f>
+        <v>675</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
       <c r="B5" t="s">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="C5">
         <v>4236</v>
       </c>
       <c r="D5">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+        <v>365</v>
+      </c>
+      <c r="E5">
+        <v>2</v>
+      </c>
+      <c r="F5">
+        <f t="shared" ref="F5:F23" si="0">ROUND(IF(D5&gt;2500, D5/1.18, D5/1.05),2)</f>
+        <v>347.62</v>
+      </c>
+      <c r="H5">
+        <f t="shared" ref="H5:H23" si="1">D5/1.05</f>
+        <v>347.61904761904759</v>
+      </c>
+      <c r="I5">
+        <f t="shared" ref="I5:I23" si="2">D5-H5</f>
+        <v>17.380952380952408</v>
+      </c>
+      <c r="J5">
+        <f t="shared" ref="J5:J23" si="3">H5+I5</f>
+        <v>365</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
       <c r="B6" t="s">
         <v>16</v>
       </c>
       <c r="C6">
-        <v>4236</v>
+        <v>4230</v>
       </c>
       <c r="D6">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+        <v>375</v>
+      </c>
+      <c r="F6">
+        <f t="shared" si="0"/>
+        <v>357.14</v>
+      </c>
+      <c r="H6">
+        <f t="shared" si="1"/>
+        <v>357.14285714285711</v>
+      </c>
+      <c r="I6">
+        <f t="shared" si="2"/>
+        <v>17.85714285714289</v>
+      </c>
+      <c r="J6">
+        <f t="shared" si="3"/>
+        <v>375</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
       <c r="B7" t="s">
         <v>16</v>
       </c>
       <c r="C7">
-        <v>4219</v>
+        <v>4236</v>
       </c>
       <c r="D7">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+        <v>375</v>
+      </c>
+      <c r="F7">
+        <f t="shared" si="0"/>
+        <v>357.14</v>
+      </c>
+      <c r="H7">
+        <f t="shared" si="1"/>
+        <v>357.14285714285711</v>
+      </c>
+      <c r="I7">
+        <f t="shared" si="2"/>
+        <v>17.85714285714289</v>
+      </c>
+      <c r="J7">
+        <f t="shared" si="3"/>
+        <v>375</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10">
       <c r="B8" t="s">
-        <v>79</v>
+        <v>16</v>
       </c>
       <c r="C8">
-        <v>4234</v>
+        <v>4236</v>
       </c>
       <c r="D8">
         <v>365</v>
       </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F8">
+        <f t="shared" si="0"/>
+        <v>347.62</v>
+      </c>
+      <c r="H8">
+        <f t="shared" si="1"/>
+        <v>347.61904761904759</v>
+      </c>
+      <c r="I8">
+        <f t="shared" si="2"/>
+        <v>17.380952380952408</v>
+      </c>
+      <c r="J8">
+        <f t="shared" si="3"/>
+        <v>365</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
       <c r="B9" t="s">
-        <v>80</v>
+        <v>16</v>
       </c>
       <c r="C9">
-        <v>4228</v>
+        <v>4219</v>
       </c>
       <c r="D9">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+        <v>395</v>
+      </c>
+      <c r="F9">
+        <f t="shared" si="0"/>
+        <v>376.19</v>
+      </c>
+      <c r="H9">
+        <f t="shared" si="1"/>
+        <v>376.19047619047615</v>
+      </c>
+      <c r="I9">
+        <f t="shared" si="2"/>
+        <v>18.809523809523853</v>
+      </c>
+      <c r="J9">
+        <f t="shared" si="3"/>
+        <v>395</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10">
       <c r="B10" t="s">
-        <v>35</v>
+        <v>79</v>
       </c>
       <c r="C10">
-        <v>4236</v>
+        <v>4234</v>
       </c>
       <c r="D10">
         <v>365</v>
       </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F10">
+        <f t="shared" si="0"/>
+        <v>347.62</v>
+      </c>
+      <c r="H10">
+        <f t="shared" si="1"/>
+        <v>347.61904761904759</v>
+      </c>
+      <c r="I10">
+        <f t="shared" si="2"/>
+        <v>17.380952380952408</v>
+      </c>
+      <c r="J10">
+        <f t="shared" si="3"/>
+        <v>365</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10">
       <c r="B11" t="s">
-        <v>35</v>
+        <v>80</v>
       </c>
       <c r="C11">
-        <v>4236</v>
+        <v>4228</v>
       </c>
       <c r="D11">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+        <v>350</v>
+      </c>
+      <c r="F11">
+        <f t="shared" si="0"/>
+        <v>333.33</v>
+      </c>
+      <c r="H11">
+        <f t="shared" si="1"/>
+        <v>333.33333333333331</v>
+      </c>
+      <c r="I11">
+        <f t="shared" si="2"/>
+        <v>16.666666666666686</v>
+      </c>
+      <c r="J11">
+        <f t="shared" si="3"/>
+        <v>350</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10">
       <c r="B12" t="s">
         <v>35</v>
       </c>
       <c r="C12">
+        <v>4236</v>
+      </c>
+      <c r="D12">
+        <v>365</v>
+      </c>
+      <c r="F12">
+        <f t="shared" si="0"/>
+        <v>347.62</v>
+      </c>
+      <c r="H12">
+        <f t="shared" si="1"/>
+        <v>347.61904761904759</v>
+      </c>
+      <c r="I12">
+        <f t="shared" si="2"/>
+        <v>17.380952380952408</v>
+      </c>
+      <c r="J12">
+        <f t="shared" si="3"/>
+        <v>365</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10">
+      <c r="B13" t="s">
+        <v>35</v>
+      </c>
+      <c r="C13">
+        <v>4236</v>
+      </c>
+      <c r="D13">
+        <v>365</v>
+      </c>
+      <c r="F13">
+        <f t="shared" si="0"/>
+        <v>347.62</v>
+      </c>
+      <c r="H13">
+        <f t="shared" si="1"/>
+        <v>347.61904761904759</v>
+      </c>
+      <c r="I13">
+        <f t="shared" si="2"/>
+        <v>17.380952380952408</v>
+      </c>
+      <c r="J13">
+        <f t="shared" si="3"/>
+        <v>365</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10">
+      <c r="B14" t="s">
+        <v>35</v>
+      </c>
+      <c r="C14">
         <v>4232</v>
       </c>
-      <c r="D12">
+      <c r="D14">
         <v>355</v>
       </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B13" t="s">
+      <c r="F14">
+        <f t="shared" si="0"/>
+        <v>338.1</v>
+      </c>
+      <c r="H14">
+        <f t="shared" si="1"/>
+        <v>338.09523809523807</v>
+      </c>
+      <c r="I14">
+        <f t="shared" si="2"/>
+        <v>16.904761904761926</v>
+      </c>
+      <c r="J14">
+        <f t="shared" si="3"/>
+        <v>355</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10">
+      <c r="B15" t="s">
         <v>15</v>
       </c>
-      <c r="C13">
+      <c r="C15">
         <v>4223</v>
       </c>
-      <c r="D13">
+      <c r="D15">
         <v>975</v>
       </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B14" t="s">
+      <c r="F15">
+        <f t="shared" si="0"/>
+        <v>928.57</v>
+      </c>
+      <c r="H15">
+        <f t="shared" si="1"/>
+        <v>928.57142857142856</v>
+      </c>
+      <c r="I15">
+        <f t="shared" si="2"/>
+        <v>46.428571428571445</v>
+      </c>
+      <c r="J15">
+        <f t="shared" si="3"/>
+        <v>975</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10">
+      <c r="B16" t="s">
         <v>68</v>
       </c>
-      <c r="C14">
+      <c r="C16">
         <v>4219</v>
       </c>
-      <c r="D14">
+      <c r="D16">
         <v>395</v>
       </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B15" t="s">
+      <c r="F16">
+        <f t="shared" si="0"/>
+        <v>376.19</v>
+      </c>
+      <c r="H16">
+        <f t="shared" si="1"/>
+        <v>376.19047619047615</v>
+      </c>
+      <c r="I16">
+        <f t="shared" si="2"/>
+        <v>18.809523809523853</v>
+      </c>
+      <c r="J16">
+        <f t="shared" si="3"/>
+        <v>395</v>
+      </c>
+    </row>
+    <row r="17" spans="2:10">
+      <c r="B17" t="s">
         <v>81</v>
       </c>
-      <c r="C15">
+      <c r="C17">
         <v>601</v>
       </c>
-      <c r="D15">
+      <c r="D17">
         <v>325</v>
       </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B16" t="s">
-        <v>35</v>
-      </c>
-      <c r="C16">
-        <v>4232</v>
-      </c>
-      <c r="D16">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="17" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B17" t="s">
-        <v>16</v>
-      </c>
-      <c r="C17">
-        <v>990</v>
-      </c>
-      <c r="D17">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="18" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="F17">
+        <f t="shared" si="0"/>
+        <v>309.52</v>
+      </c>
+      <c r="H17">
+        <f t="shared" si="1"/>
+        <v>309.52380952380952</v>
+      </c>
+      <c r="I17">
+        <f t="shared" si="2"/>
+        <v>15.476190476190482</v>
+      </c>
+      <c r="J17">
+        <f t="shared" si="3"/>
+        <v>325</v>
+      </c>
+    </row>
+    <row r="18" spans="2:10">
       <c r="B18" t="s">
         <v>35</v>
       </c>
       <c r="C18">
-        <v>4236</v>
+        <v>4232</v>
       </c>
       <c r="D18">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="19" spans="2:4" x14ac:dyDescent="0.25">
+        <v>355</v>
+      </c>
+      <c r="F18">
+        <f t="shared" si="0"/>
+        <v>338.1</v>
+      </c>
+      <c r="H18">
+        <f t="shared" si="1"/>
+        <v>338.09523809523807</v>
+      </c>
+      <c r="I18">
+        <f t="shared" si="2"/>
+        <v>16.904761904761926</v>
+      </c>
+      <c r="J18">
+        <f t="shared" si="3"/>
+        <v>355</v>
+      </c>
+    </row>
+    <row r="19" spans="2:10">
       <c r="B19" t="s">
         <v>16</v>
       </c>
       <c r="C19">
+        <v>990</v>
+      </c>
+      <c r="D19">
+        <v>305</v>
+      </c>
+      <c r="F19">
+        <f t="shared" si="0"/>
+        <v>290.48</v>
+      </c>
+      <c r="H19">
+        <f t="shared" si="1"/>
+        <v>290.47619047619048</v>
+      </c>
+      <c r="I19">
+        <f t="shared" si="2"/>
+        <v>14.523809523809518</v>
+      </c>
+      <c r="J19">
+        <f t="shared" si="3"/>
+        <v>305</v>
+      </c>
+    </row>
+    <row r="20" spans="2:10">
+      <c r="B20" t="s">
+        <v>35</v>
+      </c>
+      <c r="C20">
+        <v>4236</v>
+      </c>
+      <c r="D20">
+        <v>365</v>
+      </c>
+      <c r="F20">
+        <f t="shared" si="0"/>
+        <v>347.62</v>
+      </c>
+      <c r="H20">
+        <f t="shared" si="1"/>
+        <v>347.61904761904759</v>
+      </c>
+      <c r="I20">
+        <f t="shared" si="2"/>
+        <v>17.380952380952408</v>
+      </c>
+      <c r="J20">
+        <f t="shared" si="3"/>
+        <v>365</v>
+      </c>
+    </row>
+    <row r="21" spans="2:10">
+      <c r="B21" t="s">
+        <v>16</v>
+      </c>
+      <c r="C21">
         <v>4235</v>
       </c>
-      <c r="D19">
+      <c r="D21">
         <v>350</v>
       </c>
-    </row>
-    <row r="20" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B20" t="s">
+      <c r="F21">
+        <f t="shared" si="0"/>
+        <v>333.33</v>
+      </c>
+      <c r="H21">
+        <f t="shared" si="1"/>
+        <v>333.33333333333331</v>
+      </c>
+      <c r="I21">
+        <f t="shared" si="2"/>
+        <v>16.666666666666686</v>
+      </c>
+      <c r="J21">
+        <f t="shared" si="3"/>
+        <v>350</v>
+      </c>
+    </row>
+    <row r="22" spans="2:10">
+      <c r="B22" t="s">
         <v>68</v>
       </c>
-      <c r="C20">
+      <c r="C22">
         <v>4219</v>
       </c>
-      <c r="D20">
+      <c r="D22">
         <v>395</v>
       </c>
-    </row>
-    <row r="21" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B21" t="s">
+      <c r="F22">
+        <f t="shared" si="0"/>
+        <v>376.19</v>
+      </c>
+      <c r="H22">
+        <f t="shared" si="1"/>
+        <v>376.19047619047615</v>
+      </c>
+      <c r="I22">
+        <f t="shared" si="2"/>
+        <v>18.809523809523853</v>
+      </c>
+      <c r="J22">
+        <f t="shared" si="3"/>
+        <v>395</v>
+      </c>
+    </row>
+    <row r="23" spans="2:10">
+      <c r="B23" t="s">
         <v>35</v>
       </c>
-      <c r="C21">
+      <c r="C23">
         <v>4224</v>
       </c>
-      <c r="D21">
+      <c r="D23">
+        <v>595</v>
+      </c>
+      <c r="F23">
+        <f t="shared" si="0"/>
+        <v>566.66999999999996</v>
+      </c>
+      <c r="H23">
+        <f t="shared" si="1"/>
+        <v>566.66666666666663</v>
+      </c>
+      <c r="I23">
+        <f t="shared" si="2"/>
+        <v>28.333333333333371</v>
+      </c>
+      <c r="J23">
+        <f t="shared" si="3"/>
         <v>595</v>
       </c>
     </row>
